--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767A6E4-AC79-B542-B372-5842F282EE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63FE59E-599E-EB4C-BE5C-EBF97C552282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4017,7 +4017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="474">
+  <cellXfs count="473">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4977,30 +4977,30 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5010,6 +5010,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5019,19 +5028,9 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5415,7 +5414,7 @@
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.18043592891736998</v>
+        <v>0.17676784240120927</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -5432,13 +5431,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="457" t="s">
+      <c r="B12" s="455" t="s">
         <v>360</v>
       </c>
-      <c r="C12" s="457"/>
-      <c r="D12" s="457"/>
-      <c r="E12" s="457"/>
-      <c r="F12" s="457"/>
+      <c r="C12" s="455"/>
+      <c r="D12" s="455"/>
+      <c r="E12" s="455"/>
+      <c r="F12" s="455"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
@@ -5497,7 +5496,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.6241471996115449</v>
+        <v>3.600088840982079</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>352</v>
@@ -5547,7 +5546,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>2.1938365978664169</v>
+        <v>2.1806358523907154</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>414</v>
@@ -5562,7 +5561,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.548702207751389</v>
+        <v>2.5333048582285307</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>415</v>
@@ -5577,7 +5576,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>3.1725868773100352</v>
+        <v>3.1533183438974275</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>416</v>
@@ -5592,7 +5591,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.4219467384415752</v>
+        <v>3.4011282561229459</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>417</v>
@@ -5616,22 +5615,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="457" t="s">
+      <c r="B29" s="455" t="s">
         <v>361</v>
       </c>
-      <c r="C29" s="457"/>
-      <c r="D29" s="457"/>
-      <c r="E29" s="457"/>
-      <c r="F29" s="457"/>
+      <c r="C29" s="455"/>
+      <c r="D29" s="455"/>
+      <c r="E29" s="455"/>
+      <c r="F29" s="455"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="457" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="457"/>
+      <c r="D30" s="457"/>
+      <c r="E30" s="457"/>
+      <c r="F30" s="457"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="193" t="s">
@@ -5643,13 +5642,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="458" t="s">
+      <c r="B33" s="456" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="458"/>
-      <c r="D33" s="458"/>
-      <c r="E33" s="458"/>
-      <c r="F33" s="458"/>
+      <c r="C33" s="456"/>
+      <c r="D33" s="456"/>
+      <c r="E33" s="456"/>
+      <c r="F33" s="456"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
@@ -5669,13 +5668,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="458" t="s">
+      <c r="B36" s="456" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="458"/>
-      <c r="D36" s="458"/>
-      <c r="E36" s="458"/>
-      <c r="F36" s="458"/>
+      <c r="C36" s="456"/>
+      <c r="D36" s="456"/>
+      <c r="E36" s="456"/>
+      <c r="F36" s="456"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
@@ -5683,7 +5682,7 @@
       </c>
       <c r="C37" s="293">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>173178.99999999997</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5696,7 +5695,7 @@
       </c>
       <c r="C38" s="293">
         <f>Normalized_FCF!C16</f>
-        <v>0</v>
+        <v>-173178.99999999997</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5704,13 +5703,13 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="458" t="s">
+      <c r="B40" s="456" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="458"/>
-      <c r="D40" s="458"/>
-      <c r="E40" s="458"/>
-      <c r="F40" s="458"/>
+      <c r="C40" s="456"/>
+      <c r="D40" s="456"/>
+      <c r="E40" s="456"/>
+      <c r="F40" s="456"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
@@ -5726,13 +5725,13 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="458" t="s">
+      <c r="B43" s="456" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="458"/>
-      <c r="D43" s="458"/>
-      <c r="E43" s="458"/>
-      <c r="F43" s="458"/>
+      <c r="C43" s="456"/>
+      <c r="D43" s="456"/>
+      <c r="E43" s="456"/>
+      <c r="F43" s="456"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
@@ -5740,7 +5739,7 @@
       </c>
       <c r="C44" s="294">
         <f>Normalized_FCF!C46</f>
-        <v>6060.7417839120008</v>
+        <v>3636.4450703472003</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5755,7 +5754,7 @@
       </c>
       <c r="C45" s="294">
         <f>Normalized_FCF!C45</f>
-        <v>-5392.16</v>
+        <v>-8088.24</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5770,7 +5769,7 @@
       </c>
       <c r="C46" s="293">
         <f>Normalized_FCF!C10</f>
-        <v>668.5817839120009</v>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5796,13 +5795,13 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="458" t="s">
+      <c r="B51" s="456" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="458"/>
-      <c r="D51" s="458"/>
-      <c r="E51" s="458"/>
-      <c r="F51" s="458"/>
+      <c r="C51" s="456"/>
+      <c r="D51" s="456"/>
+      <c r="E51" s="456"/>
+      <c r="F51" s="456"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
@@ -5810,7 +5809,7 @@
       </c>
       <c r="C52" s="293">
         <f>Normalized_FCF!C12</f>
-        <v>-152320.82044597794</v>
+        <v>-151040.72626758672</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5818,7 +5817,7 @@
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="458" t="s">
+      <c r="B54" s="456" t="s">
         <v>267</v>
       </c>
       <c r="C54" s="459"/>
@@ -5840,22 +5839,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="457" t="s">
+      <c r="B57" s="455" t="s">
         <v>272</v>
       </c>
-      <c r="C57" s="457"/>
-      <c r="D57" s="457"/>
-      <c r="E57" s="457"/>
-      <c r="F57" s="457"/>
+      <c r="C57" s="455"/>
+      <c r="D57" s="455"/>
+      <c r="E57" s="455"/>
+      <c r="F57" s="455"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="457" t="s">
+      <c r="B58" s="455" t="s">
         <v>285</v>
       </c>
-      <c r="C58" s="457"/>
-      <c r="D58" s="457"/>
-      <c r="E58" s="457"/>
-      <c r="F58" s="457"/>
+      <c r="C58" s="455"/>
+      <c r="D58" s="455"/>
+      <c r="E58" s="455"/>
+      <c r="F58" s="455"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
@@ -5863,7 +5862,7 @@
       </c>
       <c r="C60" s="293">
         <f>Normalized_FCF!G19</f>
-        <v>625446</v>
+        <v>631699.59365518577</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5876,7 +5875,7 @@
       </c>
       <c r="C61" s="293">
         <f>Normalized_FCF!C19</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5889,7 +5888,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.7852042199054821E-2</v>
+        <v>5.7218927498279393E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5906,7 +5905,7 @@
       </c>
       <c r="F63" s="265">
         <f>Normalized_FCF!C90</f>
-        <v>1.0524609889200147</v>
+        <v>1.0641062355754669</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -5926,11 +5925,11 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.12522184312454268</v>
+        <v>0.12416948697308672</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.21843436133977279</v>
+        <v>0.21971961985098865</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -5940,11 +5939,11 @@
       </c>
       <c r="C67" s="270">
         <f>Normalized_FCF!C116</f>
-        <v>0.4189705857001696</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D67" s="270">
         <f>Normalized_FCF!G116</f>
-        <v>0.51159046230921634</v>
+        <v>0.51460063887624929</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -5990,13 +5989,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="192"/>
-      <c r="B73" s="457" t="s">
+      <c r="B73" s="455" t="s">
         <v>487</v>
       </c>
-      <c r="C73" s="457"/>
-      <c r="D73" s="457"/>
-      <c r="E73" s="457"/>
-      <c r="F73" s="457"/>
+      <c r="C73" s="455"/>
+      <c r="D73" s="455"/>
+      <c r="E73" s="455"/>
+      <c r="F73" s="455"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="192"/>
@@ -6015,13 +6014,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="192"/>
-      <c r="B77" s="457" t="s">
+      <c r="B77" s="455" t="s">
         <v>273</v>
       </c>
-      <c r="C77" s="457"/>
-      <c r="D77" s="457"/>
-      <c r="E77" s="457"/>
-      <c r="F77" s="457"/>
+      <c r="C77" s="455"/>
+      <c r="D77" s="455"/>
+      <c r="E77" s="455"/>
+      <c r="F77" s="455"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="192"/>
@@ -6190,31 +6189,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="457" t="s">
+      <c r="B96" s="455" t="s">
         <v>494</v>
       </c>
-      <c r="C96" s="457"/>
-      <c r="D96" s="457"/>
-      <c r="E96" s="457"/>
-      <c r="F96" s="457"/>
+      <c r="C96" s="455"/>
+      <c r="D96" s="455"/>
+      <c r="E96" s="455"/>
+      <c r="F96" s="455"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="457" t="s">
         <v>493</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="457"/>
+      <c r="D97" s="457"/>
+      <c r="E97" s="457"/>
+      <c r="F97" s="457"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="457" t="s">
         <v>492</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="457"/>
+      <c r="D98" s="457"/>
+      <c r="E98" s="457"/>
+      <c r="F98" s="457"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="193" t="s">
@@ -6264,22 +6263,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="457" t="s">
+      <c r="B107" s="455" t="s">
         <v>286</v>
       </c>
-      <c r="C107" s="457"/>
-      <c r="D107" s="457"/>
-      <c r="E107" s="457"/>
-      <c r="F107" s="457"/>
+      <c r="C107" s="455"/>
+      <c r="D107" s="455"/>
+      <c r="E107" s="455"/>
+      <c r="F107" s="455"/>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="457" t="s">
+      <c r="B108" s="455" t="s">
         <v>287</v>
       </c>
-      <c r="C108" s="457"/>
-      <c r="D108" s="457"/>
-      <c r="E108" s="457"/>
-      <c r="F108" s="457"/>
+      <c r="C108" s="455"/>
+      <c r="D108" s="455"/>
+      <c r="E108" s="455"/>
+      <c r="F108" s="455"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="193" t="s">
@@ -6305,7 +6304,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6313,13 +6312,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="457" t="s">
+      <c r="B114" s="455" t="s">
         <v>500</v>
       </c>
-      <c r="C114" s="457"/>
-      <c r="D114" s="457"/>
-      <c r="E114" s="457"/>
-      <c r="F114" s="457"/>
+      <c r="C114" s="455"/>
+      <c r="D114" s="455"/>
+      <c r="E114" s="455"/>
+      <c r="F114" s="455"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="193" t="s">
@@ -6358,7 +6357,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.5 HKD</v>
+        <v>4.48 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6380,7 +6379,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.77 HKD</v>
+        <v>3.75 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6402,7 +6401,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.64 HKD</v>
+        <v>3.62 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6424,7 +6423,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.52 HKD</v>
+        <v>3.49 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6446,7 +6445,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.41 HKD</v>
+        <v>2.38 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6454,13 +6453,13 @@
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="458" t="s">
+      <c r="B124" s="456" t="s">
         <v>362</v>
       </c>
-      <c r="C124" s="458"/>
-      <c r="D124" s="458"/>
-      <c r="E124" s="458"/>
-      <c r="F124" s="458"/>
+      <c r="C124" s="456"/>
+      <c r="D124" s="456"/>
+      <c r="E124" s="456"/>
+      <c r="F124" s="456"/>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="194" t="s">
@@ -6468,7 +6467,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.6241471996115449</v>
+        <v>3.600088840982079</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6495,22 +6494,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="458" t="s">
         <v>288</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="458"/>
+      <c r="D131" s="458"/>
+      <c r="E131" s="458"/>
+      <c r="F131" s="458"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="457" t="s">
+      <c r="B132" s="455" t="s">
         <v>364</v>
       </c>
-      <c r="C132" s="457"/>
-      <c r="D132" s="457"/>
-      <c r="E132" s="457"/>
-      <c r="F132" s="457"/>
+      <c r="C132" s="455"/>
+      <c r="D132" s="455"/>
+      <c r="E132" s="455"/>
+      <c r="F132" s="455"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="193" t="s">
@@ -6575,11 +6574,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>1.9885581342175827</v>
+        <v>1.9753573887418812</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>2.1938365978664169</v>
+        <v>2.1806358523907154</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6596,11 +6595,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.3194542077513889</v>
+        <v>2.3040568582285306</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.548702207751389</v>
+        <v>2.5333048582285307</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6643,11 +6642,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>2.9026087142285588</v>
+        <v>2.8833401808159511</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>3.1725868773100352</v>
+        <v>3.1533183438974275</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6664,11 +6663,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>3.1360927633198878</v>
+        <v>3.1152742810012586</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.4219467384415752</v>
+        <v>3.4011282561229459</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6686,13 +6685,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="456" t="s">
+      <c r="B149" s="462" t="s">
         <v>365</v>
       </c>
-      <c r="C149" s="457"/>
-      <c r="D149" s="457"/>
-      <c r="E149" s="457"/>
-      <c r="F149" s="457"/>
+      <c r="C149" s="455"/>
+      <c r="D149" s="455"/>
+      <c r="E149" s="455"/>
+      <c r="F149" s="455"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="193" t="s">
@@ -6729,13 +6728,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="458" t="s">
+      <c r="B158" s="456" t="s">
         <v>447</v>
       </c>
-      <c r="C158" s="458"/>
-      <c r="D158" s="458"/>
-      <c r="E158" s="458"/>
-      <c r="F158" s="458"/>
+      <c r="C158" s="456"/>
+      <c r="D158" s="456"/>
+      <c r="E158" s="456"/>
+      <c r="F158" s="456"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
@@ -6743,22 +6742,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="455" t="s">
+      <c r="B161" s="461" t="s">
         <v>297</v>
       </c>
-      <c r="C161" s="455"/>
-      <c r="D161" s="455"/>
-      <c r="E161" s="455"/>
-      <c r="F161" s="455"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="455" t="s">
+      <c r="B162" s="461" t="s">
         <v>298</v>
       </c>
-      <c r="C162" s="455"/>
-      <c r="D162" s="455"/>
-      <c r="E162" s="455"/>
-      <c r="F162" s="455"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
@@ -6782,6 +6781,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6798,18 +6809,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7186,8 +7185,12 @@
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="295"/>
-      <c r="D13" s="295"/>
+      <c r="C13" s="295">
+        <v>21811</v>
+      </c>
+      <c r="D13" s="295">
+        <v>17341</v>
+      </c>
       <c r="E13" s="295"/>
       <c r="F13" s="295"/>
       <c r="G13" s="295"/>
@@ -7316,8 +7319,12 @@
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="295"/>
-      <c r="D19" s="295"/>
+      <c r="C19" s="295">
+        <v>173179</v>
+      </c>
+      <c r="D19" s="295">
+        <v>166609</v>
+      </c>
       <c r="E19" s="295"/>
       <c r="F19" s="295"/>
       <c r="G19" s="295"/>
@@ -8107,11 +8114,11 @@
       </c>
       <c r="C44" s="298">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
-        <v>-255110</v>
+        <v>-276921</v>
       </c>
       <c r="D44" s="298">
         <f t="shared" si="18"/>
-        <v>-271351</v>
+        <v>-288692</v>
       </c>
       <c r="E44" s="298">
         <f t="shared" si="18"/>
@@ -8156,11 +8163,11 @@
       </c>
       <c r="C45" s="293">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
-        <v>-16422</v>
+        <v>5389</v>
       </c>
       <c r="D45" s="293">
         <f t="shared" si="19"/>
-        <v>-7392</v>
+        <v>9949</v>
       </c>
       <c r="E45" s="293">
         <f t="shared" si="19"/>
@@ -8406,11 +8413,11 @@
       </c>
       <c r="C52" s="278">
         <f>IF(C$4="","",C13)</f>
-        <v>0</v>
+        <v>21811</v>
       </c>
       <c r="D52" s="278">
         <f t="shared" ref="D52:M52" si="24">IF(D$4="","",D13)</f>
-        <v>0</v>
+        <v>17341</v>
       </c>
       <c r="E52" s="278">
         <f t="shared" si="24"/>
@@ -8607,11 +8614,11 @@
       </c>
       <c r="C58" s="293">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
-        <v>-252312</v>
+        <v>-274123</v>
       </c>
       <c r="D58" s="293">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
-        <v>-252915</v>
+        <v>-270256</v>
       </c>
       <c r="E58" s="293">
         <f t="shared" si="28"/>
@@ -8662,11 +8669,11 @@
       </c>
       <c r="C61" s="278">
         <f>IF(C$4="","",-C19)</f>
-        <v>0</v>
+        <v>-173179</v>
       </c>
       <c r="D61" s="278">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
-        <v>0</v>
+        <v>-166609</v>
       </c>
       <c r="E61" s="278">
         <f t="shared" si="29"/>
@@ -8711,11 +8718,11 @@
       </c>
       <c r="C62" s="278">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
-        <v>0</v>
+        <v>-173179</v>
       </c>
       <c r="D62" s="278">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
-        <v>0</v>
+        <v>-166609</v>
       </c>
       <c r="E62" s="278">
         <f t="shared" si="30"/>
@@ -9061,11 +9068,11 @@
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
-        <v>-5.9852368334739836E-2</v>
+        <v>-4.0773557978745489E-2</v>
       </c>
       <c r="D71" s="98">
         <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D44/E44-1)</f>
-        <v>2.0846557839214261</v>
+        <v>2.2817842851946164</v>
       </c>
       <c r="E71" s="98">
         <f t="shared" si="37"/>
@@ -10335,7 +10342,7 @@
       <c r="C58" s="95"/>
       <c r="D58" s="22">
         <f>Normalized_FCF!G15/BS!$G$39</f>
-        <v>0</v>
+        <v>6.4713105320271552E-2</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -11167,16 +11174,16 @@
       </c>
       <c r="C10" s="274">
         <f>C48</f>
-        <v>668.5817839120009</v>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="E10" s="242"/>
       <c r="G10" s="274">
         <f>G48</f>
-        <v>-16422</v>
+        <v>-10168.406344814284</v>
       </c>
       <c r="H10" s="274">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-7392</v>
+        <v>-2420.0332137648202</v>
       </c>
       <c r="I10" s="274">
         <f t="shared" si="6"/>
@@ -11222,51 +11229,51 @@
       </c>
       <c r="C11" s="275">
         <f>SUM(C8:C10)</f>
-        <v>609283.28178391175</v>
+        <v>604162.9050703469</v>
       </c>
       <c r="E11" s="242"/>
       <c r="G11" s="275">
-        <f>IF(G$4="","",SUM(G8:G10))</f>
-        <v>1062821</v>
+        <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
+        <v>1069074.5936551858</v>
       </c>
       <c r="H11" s="275">
-        <f>IF(H$4="","",SUM(H8:H10))</f>
-        <v>1684469</v>
+        <f t="shared" si="7"/>
+        <v>1689440.9667862351</v>
       </c>
       <c r="I11" s="275">
-        <f>IF(I$4="","",SUM(I8:I10))</f>
+        <f t="shared" si="7"/>
         <v>1172766</v>
       </c>
       <c r="J11" s="275">
-        <f>IF(J$4="","",SUM(J8:J10))</f>
+        <f t="shared" si="7"/>
         <v>1267983</v>
       </c>
       <c r="K11" s="275">
-        <f>IF(K$4="","",SUM(K8:K10))</f>
+        <f t="shared" si="7"/>
         <v>1051788</v>
       </c>
       <c r="L11" s="275">
-        <f>IF(L$4="","",SUM(L8:L10))</f>
+        <f t="shared" si="7"/>
         <v>997076</v>
       </c>
       <c r="M11" s="275">
-        <f>IF(M$4="","",SUM(M8:M10))</f>
+        <f t="shared" si="7"/>
         <v>873594</v>
       </c>
       <c r="N11" s="275">
-        <f>IF(N$4="","",SUM(N8:N10))</f>
+        <f t="shared" si="7"/>
         <v>625979</v>
       </c>
       <c r="O11" s="275">
-        <f>IF(O$4="","",SUM(O8:O10))</f>
+        <f t="shared" si="7"/>
         <v>498190</v>
       </c>
       <c r="P11" s="275">
-        <f>IF(P$4="","",SUM(P8:P10))</f>
+        <f t="shared" si="7"/>
         <v>396423</v>
       </c>
       <c r="Q11" s="275" t="str">
-        <f>IF(Q$4="","",SUM(Q8:Q10))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -11277,7 +11284,7 @@
       </c>
       <c r="C12" s="274">
         <f>-C11*C41</f>
-        <v>-152320.82044597794</v>
+        <v>-151040.72626758672</v>
       </c>
       <c r="E12" s="242"/>
       <c r="G12" s="274">
@@ -11389,53 +11396,53 @@
       </c>
       <c r="C14" s="277">
         <f>SUM(C11:C13)</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="250"/>
       <c r="F14" s="58"/>
       <c r="G14" s="275">
-        <f>IF(G$4="","",SUM(G11:G13))</f>
-        <v>625446</v>
+        <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
+        <v>631699.59365518577</v>
       </c>
       <c r="H14" s="275">
-        <f>IF(H$4="","",SUM(H11:H13))</f>
-        <v>1044155</v>
+        <f t="shared" si="8"/>
+        <v>1049126.9667862351</v>
       </c>
       <c r="I14" s="275">
-        <f>IF(I$4="","",SUM(I11:I13))</f>
+        <f t="shared" si="8"/>
         <v>739157</v>
       </c>
       <c r="J14" s="275">
-        <f>IF(J$4="","",SUM(J11:J13))</f>
+        <f t="shared" si="8"/>
         <v>808781</v>
       </c>
       <c r="K14" s="275">
-        <f>IF(K$4="","",SUM(K11:K13))</f>
+        <f t="shared" si="8"/>
         <v>691763</v>
       </c>
       <c r="L14" s="275">
-        <f>IF(L$4="","",SUM(L11:L13))</f>
+        <f t="shared" si="8"/>
         <v>628986</v>
       </c>
       <c r="M14" s="275">
-        <f>IF(M$4="","",SUM(M11:M13))</f>
+        <f t="shared" si="8"/>
         <v>587185</v>
       </c>
       <c r="N14" s="275">
-        <f>IF(N$4="","",SUM(N11:N13))</f>
+        <f t="shared" si="8"/>
         <v>358545</v>
       </c>
       <c r="O14" s="275">
-        <f>IF(O$4="","",SUM(O11:O13))</f>
+        <f t="shared" si="8"/>
         <v>280151</v>
       </c>
       <c r="P14" s="275">
-        <f>IF(P$4="","",SUM(P11:P13))</f>
+        <f t="shared" si="8"/>
         <v>221261</v>
       </c>
       <c r="Q14" s="275" t="str">
-        <f>IF(Q$4="","",SUM(Q11:Q13))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -11446,16 +11453,16 @@
       </c>
       <c r="C15" s="274">
         <f>BS!$G$39*BS!D58</f>
-        <v>0</v>
+        <v>173178.99999999997</v>
       </c>
       <c r="E15" s="242"/>
       <c r="G15" s="274">
         <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>0</v>
+        <v>173179</v>
       </c>
       <c r="H15" s="274">
         <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>0</v>
+        <v>166609</v>
       </c>
       <c r="I15" s="274">
         <f>IF(Data!E61="","",-Data!E61)</f>
@@ -11501,16 +11508,16 @@
       </c>
       <c r="C16" s="274">
         <f>-C4*C82</f>
-        <v>0</v>
+        <v>-173178.99999999997</v>
       </c>
       <c r="E16" s="242"/>
       <c r="G16" s="274">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-173179</v>
       </c>
       <c r="H16" s="274">
         <f>Data!D62</f>
-        <v>0</v>
+        <v>-166609</v>
       </c>
       <c r="I16" s="274">
         <f>Data!E62</f>
@@ -11607,53 +11614,53 @@
       </c>
       <c r="C19" s="275">
         <f>C14+C17</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="239"/>
       <c r="F19" s="26"/>
       <c r="G19" s="279">
-        <f>IF(G$4="","",G14+G17)</f>
-        <v>625446</v>
+        <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
+        <v>631699.59365518577</v>
       </c>
       <c r="H19" s="279">
-        <f>IF(H$4="","",H14+H17)</f>
-        <v>1044155</v>
+        <f t="shared" si="9"/>
+        <v>1049126.9667862351</v>
       </c>
       <c r="I19" s="279">
-        <f>IF(I$4="","",I14+I17)</f>
+        <f t="shared" si="9"/>
         <v>739157</v>
       </c>
       <c r="J19" s="279">
-        <f>IF(J$4="","",J14+J17)</f>
+        <f t="shared" si="9"/>
         <v>808781</v>
       </c>
       <c r="K19" s="279">
-        <f>IF(K$4="","",K14+K17)</f>
+        <f t="shared" si="9"/>
         <v>691763</v>
       </c>
       <c r="L19" s="279">
-        <f>IF(L$4="","",L14+L17)</f>
+        <f t="shared" si="9"/>
         <v>628986</v>
       </c>
       <c r="M19" s="279">
-        <f>IF(M$4="","",M14+M17)</f>
+        <f t="shared" si="9"/>
         <v>587185</v>
       </c>
       <c r="N19" s="279">
-        <f>IF(N$4="","",N14+N17)</f>
+        <f t="shared" si="9"/>
         <v>358545</v>
       </c>
       <c r="O19" s="279">
-        <f>IF(O$4="","",O14+O17)</f>
+        <f t="shared" si="9"/>
         <v>280151</v>
       </c>
       <c r="P19" s="279">
-        <f>IF(P$4="","",P14+P17)</f>
+        <f t="shared" si="9"/>
         <v>221261</v>
       </c>
       <c r="Q19" s="279" t="str">
-        <f>IF(Q$4="","",Q14+Q17)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -11908,43 +11915,43 @@
         <v>-508723</v>
       </c>
       <c r="H26" s="275">
-        <f t="shared" ref="H26:Q26" si="7">IF(H$4="","",SUM(H23:H25))</f>
+        <f t="shared" ref="H26:Q26" si="10">IF(H$4="","",SUM(H23:H25))</f>
         <v>-411372</v>
       </c>
       <c r="I26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-522821</v>
       </c>
       <c r="J26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-569426</v>
       </c>
       <c r="K26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-445423</v>
       </c>
       <c r="L26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-426069</v>
       </c>
       <c r="M26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-368220</v>
       </c>
       <c r="N26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-543146</v>
       </c>
       <c r="O26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-482820</v>
       </c>
       <c r="P26" s="275">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>-453603</v>
       </c>
       <c r="Q26" s="275" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -11972,47 +11979,47 @@
       <c r="E29" s="240"/>
       <c r="F29" s="25"/>
       <c r="G29" s="13">
-        <f t="shared" ref="G29:Q29" si="8">IF(G$4="","",ABS(G23/G$4))</f>
+        <f t="shared" ref="G29:Q29" si="11">IF(G$4="","",ABS(G23/G$4))</f>
         <v>0.22485179187902291</v>
       </c>
       <c r="H29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.13792579914452999</v>
       </c>
       <c r="I29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.22087873326254154</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.22198527160846282</v>
       </c>
       <c r="K29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.21629748850352729</v>
       </c>
       <c r="L29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.20933937254062793</v>
       </c>
       <c r="M29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.1964174870813826</v>
       </c>
       <c r="N29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.19788411652252086</v>
       </c>
       <c r="O29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.2092864383448178</v>
       </c>
       <c r="P29" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0.22398010758511139</v>
       </c>
       <c r="Q29" s="13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -12030,47 +12037,47 @@
       <c r="E30" s="240"/>
       <c r="F30" s="25"/>
       <c r="G30" s="13">
-        <f t="shared" ref="G30:Q30" si="9">IF(G$4="","",ABS(G24/G$4))</f>
+        <f t="shared" ref="G30:Q30" si="12">IF(G$4="","",ABS(G24/G$4))</f>
         <v>2.0022777552077417E-2</v>
       </c>
       <c r="H30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.8606720093271422E-2</v>
       </c>
       <c r="I30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.9872206355974739E-2</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.2839841640554328E-2</v>
       </c>
       <c r="K30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.9060129339611327E-2</v>
       </c>
       <c r="L30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.0896759599994381E-2</v>
       </c>
       <c r="M30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>2.6570596845271511E-2</v>
       </c>
       <c r="N30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.16980005523934341</v>
       </c>
       <c r="O30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.17159006196480903</v>
       </c>
       <c r="P30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0.18542366150402542</v>
       </c>
       <c r="Q30" s="13" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -12087,47 +12094,47 @@
       <c r="E31" s="239"/>
       <c r="F31" s="26"/>
       <c r="G31" s="13">
-        <f t="shared" ref="G31:Q31" si="10">IF(G$4="","",ABS(G25/G$4))</f>
+        <f t="shared" ref="G31:Q31" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0</v>
       </c>
       <c r="H31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="O31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -12142,47 +12149,47 @@
       </c>
       <c r="E32" s="242"/>
       <c r="G32" s="29">
-        <f t="shared" ref="G32:Q32" si="11">IF(G$4="","",ABS(G26/G$4))</f>
+        <f t="shared" ref="G32:Q32" si="14">IF(G$4="","",ABS(G26/G$4))</f>
         <v>0.24487456943110031</v>
       </c>
       <c r="H32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.1565325192378014</v>
       </c>
       <c r="I32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.24075093961851626</v>
       </c>
       <c r="J32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.24482511324901712</v>
       </c>
       <c r="K32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.23535761784313861</v>
       </c>
       <c r="L32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.2302361321406223</v>
       </c>
       <c r="M32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.22298808392665412</v>
       </c>
       <c r="N32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.3676841717618643</v>
       </c>
       <c r="O32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.38087650030962683</v>
       </c>
       <c r="P32" s="29">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0.40940376908913678</v>
       </c>
       <c r="Q32" s="29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -12276,47 +12283,47 @@
       </c>
       <c r="E38" s="242"/>
       <c r="G38" s="29">
-        <f t="shared" ref="G38:Q38" si="12">IF(G$4="","",ABS(G35/G$4))</f>
+        <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.23428339279628627</v>
       </c>
       <c r="H38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.19267671703774958</v>
       </c>
       <c r="I38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.21349164174678328</v>
       </c>
       <c r="J38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.20191173283894734</v>
       </c>
       <c r="K38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.20385598802031346</v>
       </c>
       <c r="L38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.22486266423282722</v>
       </c>
       <c r="M38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.24295539451062467</v>
       </c>
       <c r="N38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.1982767491104841</v>
       </c>
       <c r="O38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.21999203253251082</v>
       </c>
       <c r="P38" s="29">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.22576176035235929</v>
       </c>
       <c r="Q38" s="29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -12345,47 +12352,47 @@
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
-        <f>IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>0.29466956336015188</v>
+        <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
+        <v>0.29294588222251955</v>
       </c>
       <c r="H41" s="6">
-        <f>IF(H$4="","",-H12/SUM(H8+H9,H10))</f>
-        <v>0.27049355019296883</v>
+        <f t="shared" si="16"/>
+        <v>0.2696974969576737</v>
       </c>
       <c r="I41" s="6">
-        <f>IF(I$4="","",-I12/SUM(I8+I9,I10))</f>
+        <f t="shared" si="16"/>
         <v>0.24001036864984149</v>
       </c>
       <c r="J41" s="6">
-        <f>IF(J$4="","",-J12/SUM(J8+J9,J10))</f>
+        <f t="shared" si="16"/>
         <v>0.22838713137321243</v>
       </c>
       <c r="K41" s="6">
-        <f>IF(K$4="","",-K12/SUM(K8+K9,K10))</f>
+        <f t="shared" si="16"/>
         <v>0.21181454817891057</v>
       </c>
       <c r="L41" s="6">
-        <f>IF(L$4="","",-L12/SUM(L8+L9,L10))</f>
+        <f t="shared" si="16"/>
         <v>0.21196979969430615</v>
       </c>
       <c r="M41" s="6">
-        <f>IF(M$4="","",-M12/SUM(M8+M9,M10))</f>
+        <f t="shared" si="16"/>
         <v>0.18216700206274311</v>
       </c>
       <c r="N41" s="6">
-        <f>IF(N$4="","",-N12/SUM(N8+N9,N10))</f>
+        <f t="shared" si="16"/>
         <v>0.21504076015329587</v>
       </c>
       <c r="O41" s="6">
-        <f>IF(O$4="","",-O12/SUM(O8+O9,O10))</f>
+        <f t="shared" si="16"/>
         <v>0.21780445211666233</v>
       </c>
       <c r="P41" s="6">
-        <f>IF(P$4="","",-P12/SUM(P8+P9,P10))</f>
+        <f t="shared" si="16"/>
         <v>0.23822280745567234</v>
       </c>
       <c r="Q41" s="6" t="str">
-        <f>IF(Q$4="","",-Q12/SUM(Q8+Q9,Q10))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -12429,7 +12436,7 @@
       </c>
       <c r="C45" s="274">
         <f>-BS!G31*Normalized_FCF!C52</f>
-        <v>-5392.16</v>
+        <v>-8088.24</v>
       </c>
       <c r="E45" s="242"/>
       <c r="G45" s="274">
@@ -12484,51 +12491,51 @@
       </c>
       <c r="C46" s="274">
         <f>BS!D75*C51</f>
-        <v>6060.7417839120008</v>
+        <v>3636.4450703472003</v>
       </c>
       <c r="E46" s="242"/>
       <c r="G46" s="282">
-        <f>IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>0</v>
+        <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
+        <v>6253.5936551857167</v>
       </c>
       <c r="H46" s="282">
-        <f>IFERROR(IF(H$4="","",($C$46/$C$47)*H47),0)</f>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>4971.9667862351798</v>
       </c>
       <c r="I46" s="282">
-        <f>IFERROR(IF(I$4="","",($C$46/$C$47)*I47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J46" s="282">
-        <f>IFERROR(IF(J$4="","",($C$46/$C$47)*J47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K46" s="282">
-        <f>IFERROR(IF(K$4="","",($C$46/$C$47)*K47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L46" s="282">
-        <f>IFERROR(IF(L$4="","",($C$46/$C$47)*L47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M46" s="282">
-        <f>IFERROR(IF(M$4="","",($C$46/$C$47)*M47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N46" s="282">
-        <f>IFERROR(IF(N$4="","",($C$46/$C$47)*N47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O46" s="282">
-        <f>IFERROR(IF(O$4="","",($C$46/$C$47)*O47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P46" s="282">
-        <f>IFERROR(IF(P$4="","",($C$46/$C$47)*P47),0)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q46" s="282" t="str">
-        <f>IFERROR(IF(Q$4="","",($C$46/$C$47)*Q47),0)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -12539,18 +12546,18 @@
       </c>
       <c r="C47" s="286">
         <f>BS!$C$66*C51</f>
-        <v>21138.38</v>
+        <v>12683.028</v>
       </c>
       <c r="D47" s="253"/>
       <c r="E47" s="254"/>
       <c r="F47" s="253"/>
       <c r="G47" s="286">
         <f>Data!C52</f>
-        <v>0</v>
+        <v>21811</v>
       </c>
       <c r="H47" s="286">
         <f>Data!D52</f>
-        <v>0</v>
+        <v>17341</v>
       </c>
       <c r="I47" s="286">
         <f>Data!E52</f>
@@ -12596,51 +12603,51 @@
       </c>
       <c r="C48" s="275">
         <f>C45+C46</f>
-        <v>668.5817839120009</v>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="E48" s="242"/>
       <c r="G48" s="275">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-16422</v>
+        <v>-10168.406344814284</v>
       </c>
       <c r="H48" s="275">
-        <f t="shared" ref="H48:Q48" si="13">IF(H$4="","",(H45+H46))</f>
-        <v>-7392</v>
+        <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
+        <v>-2420.0332137648202</v>
       </c>
       <c r="I48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-5008</v>
       </c>
       <c r="J48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-7246</v>
       </c>
       <c r="K48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-9525</v>
       </c>
       <c r="L48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-11128</v>
       </c>
       <c r="M48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-8293</v>
       </c>
       <c r="N48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-15585</v>
       </c>
       <c r="O48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-8256</v>
       </c>
       <c r="P48" s="275">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>-7799</v>
       </c>
       <c r="Q48" s="275" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -12664,12 +12671,12 @@
         <v>85</v>
       </c>
       <c r="C51" s="84">
-        <v>0.01</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E51" s="239"/>
       <c r="G51" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G47/BS!$C$66)</f>
-        <v>0</v>
+        <v>1.0318198461755348E-2</v>
       </c>
       <c r="H51" s="152"/>
       <c r="I51" s="152"/>
@@ -12688,7 +12695,7 @@
         <v>84</v>
       </c>
       <c r="C52" s="79">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E52" s="239"/>
       <c r="G52" s="22">
@@ -12713,51 +12720,51 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>113.38919839173907</v>
+        <v>75.592798927826053</v>
       </c>
       <c r="E53" s="242"/>
       <c r="G53" s="40">
-        <f>IF(G4="","",-G8/G45)</f>
+        <f t="shared" ref="G53:Q53" si="19">IF(G4="","",-G8/G45)</f>
         <v>65.889721105833644</v>
       </c>
       <c r="H53" s="40">
-        <f>IF(H4="","",-H8/H45)</f>
+        <f t="shared" si="19"/>
         <v>231.37134740259739</v>
       </c>
       <c r="I53" s="40">
-        <f>IF(I4="","",-I8/I45)</f>
+        <f t="shared" si="19"/>
         <v>236.65754792332268</v>
       </c>
       <c r="J53" s="40">
-        <f>IF(J4="","",-J8/J45)</f>
+        <f t="shared" si="19"/>
         <v>177.58846260005521</v>
       </c>
       <c r="K53" s="40">
-        <f>IF(K4="","",-K8/K45)</f>
+        <f t="shared" si="19"/>
         <v>111.42351706036746</v>
       </c>
       <c r="L53" s="40">
-        <f>IF(L4="","",-L8/L45)</f>
+        <f t="shared" si="19"/>
         <v>90.616462976276054</v>
       </c>
       <c r="M53" s="40">
-        <f>IF(M4="","",-M8/M45)</f>
+        <f t="shared" si="19"/>
         <v>106.3411310744001</v>
       </c>
       <c r="N53" s="40">
-        <f>IF(N4="","",-N8/N45)</f>
+        <f t="shared" si="19"/>
         <v>41.139942252165547</v>
       </c>
       <c r="O53" s="40">
-        <f>IF(O4="","",-O8/O45)</f>
+        <f t="shared" si="19"/>
         <v>61.284035852713181</v>
       </c>
       <c r="P53" s="40">
-        <f>IF(P4="","",-P8/P45)</f>
+        <f t="shared" si="19"/>
         <v>51.829978202333635</v>
       </c>
       <c r="Q53" s="40" t="str">
-        <f>IF(Q4="","",-Q8/Q45)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -12951,47 +12958,47 @@
       </c>
       <c r="E59" s="242"/>
       <c r="G59" s="275">
-        <f>IF(G4="","",SUM(G56:G58))</f>
+        <f t="shared" ref="G59:Q59" si="20">IF(G4="","",SUM(G56:G58))</f>
         <v>-2798</v>
       </c>
       <c r="H59" s="275">
-        <f>IF(H4="","",SUM(H56:H58))</f>
+        <f t="shared" si="20"/>
         <v>-18436</v>
       </c>
       <c r="I59" s="275">
-        <f>IF(I4="","",SUM(I56:I58))</f>
+        <f t="shared" si="20"/>
         <v>-7407</v>
       </c>
       <c r="J59" s="275">
-        <f>IF(J4="","",SUM(J56:J58))</f>
+        <f t="shared" si="20"/>
         <v>-11577</v>
       </c>
       <c r="K59" s="275">
-        <f>IF(K4="","",SUM(K56:K58))</f>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="L59" s="275">
-        <f>IF(L4="","",SUM(L56:L58))</f>
+        <f t="shared" si="20"/>
         <v>-176</v>
       </c>
       <c r="M59" s="275">
-        <f>IF(M4="","",SUM(M56:M58))</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N59" s="275">
-        <f>IF(N4="","",SUM(N56:N58))</f>
+        <f t="shared" si="20"/>
         <v>398</v>
       </c>
       <c r="O59" s="275">
-        <f>IF(O4="","",SUM(O56:O58))</f>
+        <f t="shared" si="20"/>
         <v>485</v>
       </c>
       <c r="P59" s="275">
-        <f>IF(P4="","",SUM(P56:P58))</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q59" s="275" t="str">
-        <f>IF(Q4="","",SUM(Q56:Q58))</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -13008,11 +13015,11 @@
       </c>
       <c r="G60" s="274">
         <f>Data!C58</f>
-        <v>-252312</v>
+        <v>-274123</v>
       </c>
       <c r="H60" s="274">
         <f>Data!D58</f>
-        <v>-252915</v>
+        <v>-270256</v>
       </c>
       <c r="I60" s="274">
         <f>Data!E58</f>
@@ -13062,47 +13069,47 @@
       </c>
       <c r="E61" s="242"/>
       <c r="G61" s="275">
-        <f>IF(G4="","",G59+G60)</f>
-        <v>-255110</v>
+        <f t="shared" ref="G61:Q61" si="21">IF(G4="","",G59+G60)</f>
+        <v>-276921</v>
       </c>
       <c r="H61" s="275">
-        <f>IF(H4="","",H59+H60)</f>
-        <v>-271351</v>
+        <f t="shared" si="21"/>
+        <v>-288692</v>
       </c>
       <c r="I61" s="275">
-        <f>IF(I4="","",I59+I60)</f>
+        <f t="shared" si="21"/>
         <v>-87968</v>
       </c>
       <c r="J61" s="275">
-        <f>IF(J4="","",J59+J60)</f>
+        <f t="shared" si="21"/>
         <v>-100325</v>
       </c>
       <c r="K61" s="275">
-        <f>IF(K4="","",K59+K60)</f>
+        <f t="shared" si="21"/>
         <v>-71695</v>
       </c>
       <c r="L61" s="275">
-        <f>IF(L4="","",L59+L60)</f>
+        <f t="shared" si="21"/>
         <v>-50583</v>
       </c>
       <c r="M61" s="275">
-        <f>IF(M4="","",M59+M60)</f>
+        <f t="shared" si="21"/>
         <v>-98821</v>
       </c>
       <c r="N61" s="275">
-        <f>IF(N4="","",N59+N60)</f>
+        <f t="shared" si="21"/>
         <v>59203</v>
       </c>
       <c r="O61" s="275">
-        <f>IF(O4="","",O59+O60)</f>
+        <f t="shared" si="21"/>
         <v>59308</v>
       </c>
       <c r="P61" s="275">
-        <f>IF(P4="","",P59+P60)</f>
+        <f t="shared" si="21"/>
         <v>63183</v>
       </c>
       <c r="Q61" s="275" t="str">
-        <f>IF(Q4="","",Q59+Q60)</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -13275,54 +13282,54 @@
         <v>43</v>
       </c>
       <c r="C71" s="74">
-        <f>ABS(C5/C$4)</f>
+        <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
         <v>0.24487456943110034</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="239"/>
       <c r="F71" s="26"/>
       <c r="G71" s="6">
-        <f>IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G71:Q71" si="23">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.24487456943110031</v>
       </c>
       <c r="H71" s="6">
-        <f>IF(H$4="","",ABS(H5/H$4))</f>
+        <f t="shared" si="23"/>
         <v>0.1565325192378014</v>
       </c>
       <c r="I71" s="6">
-        <f>IF(I$4="","",ABS(I5/I$4))</f>
+        <f t="shared" si="23"/>
         <v>0.24075093961851626</v>
       </c>
       <c r="J71" s="6">
-        <f>IF(J$4="","",ABS(J5/J$4))</f>
+        <f t="shared" si="23"/>
         <v>0.24482511324901712</v>
       </c>
       <c r="K71" s="6">
-        <f>IF(K$4="","",ABS(K5/K$4))</f>
+        <f t="shared" si="23"/>
         <v>0.23535761784313861</v>
       </c>
       <c r="L71" s="6">
-        <f>IF(L$4="","",ABS(L5/L$4))</f>
+        <f t="shared" si="23"/>
         <v>0.2302361321406223</v>
       </c>
       <c r="M71" s="6">
-        <f>IF(M$4="","",ABS(M5/M$4))</f>
+        <f t="shared" si="23"/>
         <v>0.22298808392665412</v>
       </c>
       <c r="N71" s="6">
-        <f>IF(N$4="","",ABS(N5/N$4))</f>
+        <f t="shared" si="23"/>
         <v>0.3676841717618643</v>
       </c>
       <c r="O71" s="6">
-        <f>IF(O$4="","",ABS(O5/O$4))</f>
+        <f t="shared" si="23"/>
         <v>0.38087650030962683</v>
       </c>
       <c r="P71" s="6">
-        <f>IF(P$4="","",ABS(P5/P$4))</f>
+        <f t="shared" si="23"/>
         <v>0.40940376908913678</v>
       </c>
       <c r="Q71" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q5/Q$4))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -13332,54 +13339,54 @@
         <v>45</v>
       </c>
       <c r="C72" s="75">
-        <f>ABS(C6/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.75512543056889958</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="239"/>
       <c r="F72" s="26"/>
       <c r="G72" s="62">
-        <f>IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G72:Q72" si="24">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.75512543056889969</v>
       </c>
       <c r="H72" s="62">
-        <f>IF(H$4="","",ABS(H6/H$4))</f>
+        <f t="shared" si="24"/>
         <v>0.84346748076219857</v>
       </c>
       <c r="I72" s="62">
-        <f>IF(I$4="","",ABS(I6/I$4))</f>
+        <f t="shared" si="24"/>
         <v>0.75924906038148376</v>
       </c>
       <c r="J72" s="62">
-        <f>IF(J$4="","",ABS(J6/J$4))</f>
+        <f t="shared" si="24"/>
         <v>0.75517488675098288</v>
       </c>
       <c r="K72" s="62">
-        <f>IF(K$4="","",ABS(K6/K$4))</f>
+        <f t="shared" si="24"/>
         <v>0.76464238215686142</v>
       </c>
       <c r="L72" s="62">
-        <f>IF(L$4="","",ABS(L6/L$4))</f>
+        <f t="shared" si="24"/>
         <v>0.76976386785937767</v>
       </c>
       <c r="M72" s="62">
-        <f>IF(M$4="","",ABS(M6/M$4))</f>
+        <f t="shared" si="24"/>
         <v>0.77701191607334585</v>
       </c>
       <c r="N72" s="62">
-        <f>IF(N$4="","",ABS(N6/N$4))</f>
+        <f t="shared" si="24"/>
         <v>0.6323158282381357</v>
       </c>
       <c r="O72" s="62">
-        <f>IF(O$4="","",ABS(O6/O$4))</f>
+        <f t="shared" si="24"/>
         <v>0.61912349969037317</v>
       </c>
       <c r="P72" s="62">
-        <f>IF(P$4="","",ABS(P6/P$4))</f>
+        <f t="shared" si="24"/>
         <v>0.59059623091086322</v>
       </c>
       <c r="Q72" s="62" t="str">
-        <f>IF(Q$4="","",ABS(Q6/Q$4))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -13389,54 +13396,54 @@
         <v>42</v>
       </c>
       <c r="C73" s="74">
-        <f>ABS(C7/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.33469056113755186</v>
       </c>
       <c r="D73" s="26"/>
       <c r="E73" s="239"/>
       <c r="F73" s="26"/>
       <c r="G73" s="6">
-        <f>IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="25">IF(G$4="","",ABS(G7/G$4))</f>
         <v>0.23428339279628627</v>
       </c>
       <c r="H73" s="6">
-        <f>IF(H$4="","",ABS(H7/H$4))</f>
+        <f t="shared" si="25"/>
         <v>0.19267671703774958</v>
       </c>
       <c r="I73" s="6">
-        <f>IF(I$4="","",ABS(I7/I$4))</f>
+        <f t="shared" si="25"/>
         <v>0.21349164174678328</v>
       </c>
       <c r="J73" s="6">
-        <f>IF(J$4="","",ABS(J7/J$4))</f>
+        <f t="shared" si="25"/>
         <v>0.20191173283894734</v>
       </c>
       <c r="K73" s="6">
-        <f>IF(K$4="","",ABS(K7/K$4))</f>
+        <f t="shared" si="25"/>
         <v>0.20385598802031346</v>
       </c>
       <c r="L73" s="6">
-        <f>IF(L$4="","",ABS(L7/L$4))</f>
+        <f t="shared" si="25"/>
         <v>0.22486266423282722</v>
       </c>
       <c r="M73" s="6">
-        <f>IF(M$4="","",ABS(M7/M$4))</f>
+        <f t="shared" si="25"/>
         <v>0.24295539451062467</v>
       </c>
       <c r="N73" s="6">
-        <f>IF(N$4="","",ABS(N7/N$4))</f>
+        <f t="shared" si="25"/>
         <v>0.1982767491104841</v>
       </c>
       <c r="O73" s="6">
-        <f>IF(O$4="","",ABS(O7/O$4))</f>
+        <f t="shared" si="25"/>
         <v>0.21999203253251082</v>
       </c>
       <c r="P73" s="6">
-        <f>IF(P$4="","",ABS(P7/P$4))</f>
+        <f t="shared" si="25"/>
         <v>0.22576176035235929</v>
       </c>
       <c r="Q73" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q7/Q$4))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -13446,54 +13453,54 @@
         <v>127</v>
       </c>
       <c r="C74" s="75">
-        <f>ABS(C8/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.42043486943134772</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="239"/>
       <c r="F74" s="26"/>
       <c r="G74" s="62">
-        <f>IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="26">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.5208420377726134</v>
       </c>
       <c r="H74" s="62">
-        <f>IF(H$4="","",ABS(H8/H$4))</f>
+        <f t="shared" si="26"/>
         <v>0.650790763724449</v>
       </c>
       <c r="I74" s="62">
-        <f>IF(I$4="","",ABS(I8/I$4))</f>
+        <f t="shared" si="26"/>
         <v>0.5457574186347004</v>
       </c>
       <c r="J74" s="62">
-        <f>IF(J$4="","",ABS(J8/J$4))</f>
+        <f t="shared" si="26"/>
         <v>0.55326315391203551</v>
       </c>
       <c r="K74" s="62">
-        <f>IF(K$4="","",ABS(K8/K$4))</f>
+        <f t="shared" si="26"/>
         <v>0.56078639413654796</v>
       </c>
       <c r="L74" s="62">
-        <f>IF(L$4="","",ABS(L8/L$4))</f>
+        <f t="shared" si="26"/>
         <v>0.54490120362655048</v>
       </c>
       <c r="M74" s="62">
-        <f>IF(M$4="","",ABS(M8/M$4))</f>
+        <f t="shared" si="26"/>
         <v>0.53405652156272121</v>
       </c>
       <c r="N74" s="62">
-        <f>IF(N$4="","",ABS(N8/N$4))</f>
+        <f t="shared" si="26"/>
         <v>0.43403907912765161</v>
       </c>
       <c r="O74" s="62">
-        <f>IF(O$4="","",ABS(O8/O$4))</f>
+        <f t="shared" si="26"/>
         <v>0.39913146715786235</v>
       </c>
       <c r="P74" s="62">
-        <f>IF(P$4="","",ABS(P8/P$4))</f>
+        <f t="shared" si="26"/>
         <v>0.36483447055850393</v>
       </c>
       <c r="Q74" s="62" t="str">
-        <f>IF(Q$4="","",ABS(Q8/Q$4))</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -13503,54 +13510,54 @@
         <v>128</v>
       </c>
       <c r="C75" s="74">
-        <f>ABS(C9/C$4)</f>
+        <f t="shared" si="22"/>
         <v>1.9240306337583624E-3</v>
       </c>
       <c r="D75" s="26"/>
       <c r="E75" s="239"/>
       <c r="F75" s="26"/>
       <c r="G75" s="6">
-        <f>IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G75:Q75" si="27">IF(G$4="","",G9/G$4)</f>
         <v>-1.3468214436308534E-3</v>
       </c>
       <c r="H75" s="6">
-        <f>IF(H$4="","",H9/H$4)</f>
+        <f t="shared" si="27"/>
         <v>-7.0151432879926364E-3</v>
       </c>
       <c r="I75" s="6">
-        <f>IF(I$4="","",I9/I$4)</f>
+        <f t="shared" si="27"/>
         <v>-3.4108083067710556E-3</v>
       </c>
       <c r="J75" s="6">
-        <f>IF(J$4="","",J9/J$4)</f>
+        <f t="shared" si="27"/>
         <v>-4.9775393748860627E-3</v>
       </c>
       <c r="K75" s="6">
-        <f>IF(K$4="","",K9/K$4)</f>
+        <f t="shared" si="27"/>
         <v>2.1135650188080867E-6</v>
       </c>
       <c r="L75" s="6">
-        <f>IF(L$4="","",L9/L$4)</f>
+        <f t="shared" si="27"/>
         <v>-9.5105626686638853E-5</v>
       </c>
       <c r="M75" s="6">
-        <f>IF(M$4="","",M9/M$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N75" s="6">
-        <f>IF(N$4="","",N9/N$4)</f>
+        <f t="shared" si="27"/>
         <v>2.6942718967132588E-4</v>
       </c>
       <c r="O75" s="6">
-        <f>IF(O$4="","",O9/O$4)</f>
+        <f t="shared" si="27"/>
         <v>3.825962111142227E-4</v>
       </c>
       <c r="P75" s="6">
-        <f>IF(P$4="","",P9/P$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Q75" s="6" t="str">
-        <f>IF(Q$4="","",Q9/Q$4)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -13560,54 +13567,54 @@
         <v>65</v>
       </c>
       <c r="C76" s="74">
-        <f>ABS(C10/C$4)</f>
-        <v>4.5974690258023714E-4</v>
+        <f t="shared" si="22"/>
+        <v>3.0612544030958326E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="239"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
-        <f>IF(G$4="","",ABS(G10/G$4))</f>
-        <v>7.9047540197662164E-3</v>
+        <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
+        <v>4.8945774527333471E-3</v>
       </c>
       <c r="H76" s="6">
-        <f>IF(H$4="","",ABS(H10/H$4))</f>
-        <v>2.8127543493622026E-3</v>
+        <f t="shared" si="28"/>
+        <v>9.2085483598728182E-4</v>
       </c>
       <c r="I76" s="6">
-        <f>IF(I$4="","",ABS(I10/I$4))</f>
+        <f t="shared" si="28"/>
         <v>2.3061061158781483E-3</v>
       </c>
       <c r="J76" s="6">
-        <f>IF(J$4="","",ABS(J10/J$4))</f>
+        <f t="shared" si="28"/>
         <v>3.115422847924714E-3</v>
       </c>
       <c r="K76" s="6">
-        <f>IF(K$4="","",ABS(K10/K$4))</f>
+        <f t="shared" si="28"/>
         <v>5.0329267010367565E-3</v>
       </c>
       <c r="L76" s="6">
-        <f>IF(L$4="","",ABS(L10/L$4))</f>
+        <f t="shared" si="28"/>
         <v>6.0132693964143015E-3</v>
       </c>
       <c r="M76" s="6">
-        <f>IF(M$4="","",ABS(M10/M$4))</f>
+        <f t="shared" si="28"/>
         <v>5.022106838313352E-3</v>
       </c>
       <c r="N76" s="6">
-        <f>IF(N$4="","",ABS(N10/N$4))</f>
+        <f t="shared" si="28"/>
         <v>1.0550308419667373E-2</v>
       </c>
       <c r="O76" s="6">
-        <f>IF(O$4="","",ABS(O10/O$4))</f>
+        <f t="shared" si="28"/>
         <v>6.5128130287814903E-3</v>
       </c>
       <c r="P76" s="6">
-        <f>IF(P$4="","",ABS(P10/P$4))</f>
+        <f t="shared" si="28"/>
         <v>7.0390627820498932E-3</v>
       </c>
       <c r="Q76" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q10/Q$4))</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -13618,53 +13625,53 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.4189705857001696</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="239"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
-        <f>IF(G$4="","",G11/G$4)</f>
-        <v>0.51159046230921634</v>
+        <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
+        <v>0.51460063887624929</v>
       </c>
       <c r="H77" s="62">
-        <f>IF(H$4="","",H11/H$4)</f>
-        <v>0.64096286608709419</v>
+        <f t="shared" si="29"/>
+        <v>0.64285476560046906</v>
       </c>
       <c r="I77" s="62">
-        <f>IF(I$4="","",I11/I$4)</f>
+        <f t="shared" si="29"/>
         <v>0.5400405042120513</v>
       </c>
       <c r="J77" s="62">
-        <f>IF(J$4="","",J11/J$4)</f>
+        <f t="shared" si="29"/>
         <v>0.54517019168922476</v>
       </c>
       <c r="K77" s="62">
-        <f>IF(K$4="","",K11/K$4)</f>
+        <f t="shared" si="29"/>
         <v>0.55575558100053002</v>
       </c>
       <c r="L77" s="62">
-        <f>IF(L$4="","",L11/L$4)</f>
+        <f t="shared" si="29"/>
         <v>0.53879282860344957</v>
       </c>
       <c r="M77" s="62">
-        <f>IF(M$4="","",M11/M$4)</f>
+        <f t="shared" si="29"/>
         <v>0.52903441472440782</v>
       </c>
       <c r="N77" s="62">
-        <f>IF(N$4="","",N11/N$4)</f>
+        <f t="shared" si="29"/>
         <v>0.42375819789765556</v>
       </c>
       <c r="O77" s="62">
-        <f>IF(O$4="","",O11/O$4)</f>
+        <f t="shared" si="29"/>
         <v>0.39300125034019506</v>
       </c>
       <c r="P77" s="62">
-        <f>IF(P$4="","",P11/P$4)</f>
+        <f t="shared" si="29"/>
         <v>0.35779540777645402</v>
       </c>
       <c r="Q77" s="62" t="str">
-        <f>IF(Q$4="","",Q11/Q$4)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -13675,53 +13682,53 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>0.1047426464250424</v>
+        <v>0.10386239609862338</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="239"/>
       <c r="F78" s="26"/>
       <c r="G78" s="6">
-        <f>IF(G$4="","",ABS(G12/G$4))</f>
+        <f t="shared" ref="G78:Q78" si="30">IF(G$4="","",ABS(G12/G$4))</f>
         <v>0.15075013814787502</v>
       </c>
       <c r="H78" s="6">
-        <f>IF(H$4="","",ABS(H12/H$4))</f>
+        <f t="shared" si="30"/>
         <v>0.17337632118975857</v>
       </c>
       <c r="I78" s="6">
-        <f>IF(I$4="","",ABS(I12/I$4))</f>
+        <f t="shared" si="30"/>
         <v>0.12961532050178071</v>
       </c>
       <c r="J78" s="6">
-        <f>IF(J$4="","",ABS(J12/J$4))</f>
+        <f t="shared" si="30"/>
         <v>0.12450985619008637</v>
       </c>
       <c r="K78" s="6">
-        <f>IF(K$4="","",ABS(K12/K$4))</f>
+        <f t="shared" si="30"/>
         <v>0.1177171172875352</v>
       </c>
       <c r="L78" s="6">
-        <f>IF(L$4="","",ABS(L12/L$4))</f>
+        <f t="shared" si="30"/>
         <v>0.11420780795580182</v>
       </c>
       <c r="M78" s="6">
-        <f>IF(M$4="","",ABS(M12/M$4))</f>
+        <f t="shared" si="30"/>
         <v>9.6372613318363304E-2</v>
       </c>
       <c r="N78" s="6">
-        <f>IF(N$4="","",ABS(N12/N$4))</f>
+        <f t="shared" si="30"/>
         <v>9.1125284997102637E-2</v>
       </c>
       <c r="O78" s="6">
-        <f>IF(O$4="","",ABS(O12/O$4))</f>
+        <f t="shared" si="30"/>
         <v>8.5597422011509439E-2</v>
       </c>
       <c r="P78" s="6">
-        <f>IF(P$4="","",ABS(P12/P$4))</f>
+        <f t="shared" si="30"/>
         <v>8.5235026535253985E-2</v>
       </c>
       <c r="Q78" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q12/Q$4))</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -13739,47 +13746,47 @@
       <c r="E79" s="239"/>
       <c r="F79" s="26"/>
       <c r="G79" s="6">
-        <f>IF(G$4="","",-G13/G$4)</f>
+        <f t="shared" ref="G79:Q79" si="31">IF(G$4="","",-G13/G$4)</f>
         <v>5.9780965822119447E-2</v>
       </c>
       <c r="H79" s="6">
-        <f>IF(H$4="","",-H13/H$4)</f>
+        <f t="shared" si="31"/>
         <v>7.0271675084255164E-2</v>
       </c>
       <c r="I79" s="6">
-        <f>IF(I$4="","",-I13/I$4)</f>
+        <f t="shared" si="31"/>
         <v>7.0054880536519634E-2</v>
       </c>
       <c r="J79" s="6">
-        <f>IF(J$4="","",-J13/J$4)</f>
+        <f t="shared" si="31"/>
         <v>7.2924369950228912E-2</v>
       </c>
       <c r="K79" s="6">
-        <f>IF(K$4="","",-K13/K$4)</f>
+        <f t="shared" si="31"/>
         <v>7.2516944186560156E-2</v>
       </c>
       <c r="L79" s="6">
-        <f>IF(L$4="","",-L13/L$4)</f>
+        <f t="shared" si="31"/>
         <v>8.4698045038998707E-2</v>
       </c>
       <c r="M79" s="6">
-        <f>IF(M$4="","",-M13/M$4)</f>
+        <f t="shared" si="31"/>
         <v>7.7072050549294821E-2</v>
       </c>
       <c r="N79" s="6">
-        <f>IF(N$4="","",-N13/N$4)</f>
+        <f t="shared" si="31"/>
         <v>8.9914893501795282E-2</v>
       </c>
       <c r="O79" s="6">
-        <f>IF(O$4="","",-O13/O$4)</f>
+        <f t="shared" si="31"/>
         <v>8.6404423916601913E-2</v>
       </c>
       <c r="P79" s="6">
-        <f>IF(P$4="","",-P13/P$4)</f>
+        <f t="shared" si="31"/>
         <v>7.2859128488393085E-2</v>
       </c>
       <c r="Q79" s="6" t="str">
-        <f>IF(Q$4="","",-Q13/Q$4)</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -13790,53 +13797,53 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>0.24130356932489827</v>
+        <v>0.23866281834564124</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="239"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
-        <f>IF(G$4="","",ABS(G14/G$4))</f>
-        <v>0.30105935833922187</v>
+        <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
+        <v>0.30406953490625477</v>
       </c>
       <c r="H80" s="62">
-        <f>IF(H$4="","",ABS(H14/H$4))</f>
-        <v>0.39731486981308045</v>
+        <f t="shared" si="32"/>
+        <v>0.39920676932645532</v>
       </c>
       <c r="I80" s="62">
-        <f>IF(I$4="","",ABS(I14/I$4))</f>
+        <f t="shared" si="32"/>
         <v>0.34037030317375089</v>
       </c>
       <c r="J80" s="62">
-        <f>IF(J$4="","",ABS(J14/J$4))</f>
+        <f t="shared" si="32"/>
         <v>0.34773596554890945</v>
       </c>
       <c r="K80" s="62">
-        <f>IF(K$4="","",ABS(K14/K$4))</f>
+        <f t="shared" si="32"/>
         <v>0.36552151952643464</v>
       </c>
       <c r="L80" s="62">
-        <f>IF(L$4="","",ABS(L14/L$4))</f>
+        <f t="shared" si="32"/>
         <v>0.339886975608649</v>
       </c>
       <c r="M80" s="62">
-        <f>IF(M$4="","",ABS(M14/M$4))</f>
+        <f t="shared" si="32"/>
         <v>0.35558975085674976</v>
       </c>
       <c r="N80" s="62">
-        <f>IF(N$4="","",ABS(N14/N$4))</f>
+        <f t="shared" si="32"/>
         <v>0.24271801939875765</v>
       </c>
       <c r="O80" s="62">
-        <f>IF(O$4="","",ABS(O14/O$4))</f>
+        <f t="shared" si="32"/>
         <v>0.22099940441208374</v>
       </c>
       <c r="P80" s="62">
-        <f>IF(P$4="","",ABS(P14/P$4))</f>
+        <f t="shared" si="32"/>
         <v>0.19970125275280695</v>
       </c>
       <c r="Q80" s="62" t="str">
-        <f>IF(Q$4="","",ABS(Q14/Q$4))</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -13847,53 +13854,53 @@
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
-        <v>0</v>
+        <v>0.11908566873611129</v>
       </c>
       <c r="D81" s="26"/>
       <c r="E81" s="239"/>
       <c r="F81" s="26"/>
       <c r="G81" s="6">
-        <f>IF(G$4="","",G15/G$4)</f>
-        <v>0</v>
+        <f t="shared" ref="G81:Q81" si="33">IF(G$4="","",G15/G$4)</f>
+        <v>8.3359968115277905E-2</v>
       </c>
       <c r="H81" s="6">
-        <f>IF(H$4="","",H15/H$4)</f>
-        <v>0</v>
+        <f t="shared" si="33"/>
+        <v>6.3396941205747723E-2</v>
       </c>
       <c r="I81" s="6">
-        <f>IF(I$4="","",I15/I$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="J81" s="6">
-        <f>IF(J$4="","",J15/J$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K81" s="6">
-        <f>IF(K$4="","",K15/K$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L81" s="6">
-        <f>IF(L$4="","",L15/L$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M81" s="6">
-        <f>IF(M$4="","",M15/M$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="N81" s="6">
-        <f>IF(N$4="","",N15/N$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="O81" s="6">
-        <f>IF(O$4="","",O15/O$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P81" s="6">
-        <f>IF(P$4="","",P15/P$4)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="Q81" s="6" t="str">
-        <f>IF(Q$4="","",Q15/Q$4)</f>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -13904,7 +13911,7 @@
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
-        <v>0</v>
+        <v>0.11908566873611129</v>
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="240" t="s">
@@ -13912,47 +13919,47 @@
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
-        <f>IF(G$4="","",-G16/G$4)</f>
-        <v>0</v>
+        <f t="shared" ref="G82:Q82" si="34">IF(G$4="","",-G16/G$4)</f>
+        <v>8.3359968115277905E-2</v>
       </c>
       <c r="H82" s="6">
-        <f>IF(H$4="","",-H16/H$4)</f>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>6.3396941205747723E-2</v>
       </c>
       <c r="I82" s="6">
-        <f>IF(I$4="","",-I16/I$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J82" s="6">
-        <f>IF(J$4="","",-J16/J$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K82" s="6">
-        <f>IF(K$4="","",-K16/K$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L82" s="6">
-        <f>IF(L$4="","",-L16/L$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M82" s="6">
-        <f>IF(M$4="","",-M16/M$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="N82" s="6">
-        <f>IF(N$4="","",-N16/N$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O82" s="6">
-        <f>IF(O$4="","",-O16/O$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="P82" s="6">
-        <f>IF(P$4="","",-P16/P$4)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q82" s="6" t="str">
-        <f>IF(Q$4="","",-Q16/Q$4)</f>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -14013,53 +14020,53 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>0.24130356932489827</v>
+        <v>0.23866281834564124</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="239"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
-        <f>IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.30105935833922187</v>
+        <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>0.30406953490625477</v>
       </c>
       <c r="H85" s="62">
-        <f>IF(H$4="","",ABS(H19/H$4))</f>
-        <v>0.39731486981308045</v>
+        <f t="shared" si="35"/>
+        <v>0.39920676932645532</v>
       </c>
       <c r="I85" s="62">
-        <f>IF(I$4="","",ABS(I19/I$4))</f>
+        <f t="shared" si="35"/>
         <v>0.34037030317375089</v>
       </c>
       <c r="J85" s="62">
-        <f>IF(J$4="","",ABS(J19/J$4))</f>
+        <f t="shared" si="35"/>
         <v>0.34773596554890945</v>
       </c>
       <c r="K85" s="62">
-        <f>IF(K$4="","",ABS(K19/K$4))</f>
+        <f t="shared" si="35"/>
         <v>0.36552151952643464</v>
       </c>
       <c r="L85" s="62">
-        <f>IF(L$4="","",ABS(L19/L$4))</f>
+        <f t="shared" si="35"/>
         <v>0.339886975608649</v>
       </c>
       <c r="M85" s="62">
-        <f>IF(M$4="","",ABS(M19/M$4))</f>
+        <f t="shared" si="35"/>
         <v>0.35558975085674976</v>
       </c>
       <c r="N85" s="62">
-        <f>IF(N$4="","",ABS(N19/N$4))</f>
+        <f t="shared" si="35"/>
         <v>0.24271801939875765</v>
       </c>
       <c r="O85" s="62">
-        <f>IF(O$4="","",ABS(O19/O$4))</f>
+        <f t="shared" si="35"/>
         <v>0.22099940441208374</v>
       </c>
       <c r="P85" s="62">
-        <f>IF(P$4="","",ABS(P19/P$4))</f>
+        <f t="shared" si="35"/>
         <v>0.19970125275280695</v>
       </c>
       <c r="Q85" s="62" t="str">
-        <f>IF(Q$4="","",ABS(Q19/Q$4))</f>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -14142,47 +14149,47 @@
       </c>
       <c r="E89" s="242"/>
       <c r="G89" s="71">
-        <f t="shared" ref="G89:Q89" si="14">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
+        <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
         <v>369322.25678240001</v>
       </c>
       <c r="H89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>369322.25678240001</v>
       </c>
       <c r="I89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="J89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="K89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="P89" s="71">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q89" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -14193,51 +14200,51 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>1.0524609889200147</v>
+        <v>1.0641062355754669</v>
       </c>
       <c r="E90" s="242"/>
       <c r="G90" s="153">
-        <f>IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.59049423416633895</v>
+        <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
+        <v>0.58464855841587759</v>
       </c>
       <c r="H90" s="153">
-        <f>IF(H$4="","",H88/(H19*scaling_factor/Common_Shares))</f>
-        <v>0.35370443735115958</v>
+        <f t="shared" si="37"/>
+        <v>0.35202818007217546</v>
       </c>
       <c r="I90" s="153">
-        <f>IF(I$4="","",I88/(I19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J90" s="153">
-        <f>IF(J$4="","",J88/(J19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K90" s="153">
-        <f>IF(K$4="","",K88/(K19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L90" s="153">
-        <f>IF(L$4="","",L88/(L19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M90" s="153">
-        <f>IF(M$4="","",M88/(M19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N90" s="153">
-        <f>IF(N$4="","",N88/(N19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O90" s="153">
-        <f>IF(O$4="","",O88/(O19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P90" s="153">
-        <f>IF(P$4="","",P88/(P19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Q90" s="153" t="str">
-        <f>IF(Q$4="","",Q88/(Q19*scaling_factor/Common_Shares))</f>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -14273,47 +14280,47 @@
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
-        <f t="shared" ref="G92:Q92" si="15">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
         <v>5.5859649122807019E-2</v>
       </c>
       <c r="H92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>5.5859649122807019E-2</v>
       </c>
       <c r="I92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="K92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="N92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="O92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="P92" s="22">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="Q92" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -14355,47 +14362,47 @@
       <c r="E95" s="239"/>
       <c r="F95" s="26"/>
       <c r="G95" s="6">
-        <f>IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
         <v>-0.20948969741201484</v>
       </c>
       <c r="H95" s="6">
-        <f>IF(I4="","",H4/I4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.21016648354735112</v>
       </c>
       <c r="I95" s="6">
-        <f>IF(J4="","",I4/J4-1)</f>
+        <f t="shared" si="39"/>
         <v>-6.6307858467105296E-2</v>
       </c>
       <c r="J95" s="6">
-        <f>IF(K4="","",J4/K4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.22895774296618776</v>
       </c>
       <c r="K95" s="6">
-        <f>IF(L4="","",K4/L4-1)</f>
+        <f t="shared" si="39"/>
         <v>2.2675667117337595E-2</v>
       </c>
       <c r="L95" s="6">
-        <f>IF(M4="","",L4/M4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.12067772099419916</v>
       </c>
       <c r="M95" s="6">
-        <f>IF(N4="","",M4/N4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.11785137908811749</v>
       </c>
       <c r="N95" s="6">
-        <f>IF(O4="","",N4/O4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.16530759552086338</v>
       </c>
       <c r="O95" s="6">
-        <f>IF(P4="","",O4/P4-1)</f>
+        <f t="shared" si="39"/>
         <v>0.14413426477490154</v>
       </c>
       <c r="P95" s="6" t="str">
-        <f>IF(Q4="","",P4/Q4-1)</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q95" s="6" t="str">
-        <f>IF(R4="","",Q4/R4-1)</f>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -14406,53 +14413,53 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>-0.42673010621364116</v>
+        <v>-0.43487301199002137</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="239"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
-        <f>IF(H5="","",G11/H11-1)</f>
-        <v>-0.36904686283926869</v>
+        <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
+        <v>-0.36720216055323363</v>
       </c>
       <c r="H96" s="6">
-        <f>IF(I5="","",H11/I11-1)</f>
-        <v>0.43632148271692728</v>
+        <f t="shared" si="40"/>
+        <v>0.44056100431478673</v>
       </c>
       <c r="I96" s="6">
-        <f>IF(J5="","",I11/J11-1)</f>
+        <f t="shared" si="40"/>
         <v>-7.5093278064453539E-2</v>
       </c>
       <c r="J96" s="6">
-        <f>IF(K5="","",J11/K11-1)</f>
+        <f t="shared" si="40"/>
         <v>0.20554997775217054</v>
       </c>
       <c r="K96" s="6">
-        <f>IF(L5="","",K11/L11-1)</f>
+        <f t="shared" si="40"/>
         <v>5.4872447035130723E-2</v>
       </c>
       <c r="L96" s="6">
-        <f>IF(M5="","",L11/M11-1)</f>
+        <f t="shared" si="40"/>
         <v>0.14134941402985834</v>
       </c>
       <c r="M96" s="6">
-        <f>IF(N5="","",M11/N11-1)</f>
+        <f t="shared" si="40"/>
         <v>0.39556438794272641</v>
       </c>
       <c r="N96" s="6">
-        <f>IF(O5="","",N11/O11-1)</f>
+        <f t="shared" si="40"/>
         <v>0.25650655372448261</v>
       </c>
       <c r="O96" s="6">
-        <f>IF(P5="","",O11/P11-1)</f>
+        <f t="shared" si="40"/>
         <v>0.25671315741014022</v>
       </c>
       <c r="P96" s="6" t="str">
-        <f>IF(Q5="","",P11/Q11-1)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f>IF(R5="","",Q11/R11-1)</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -14505,47 +14512,47 @@
       <c r="E100" s="243"/>
       <c r="F100" s="25"/>
       <c r="G100" s="278">
-        <f t="shared" ref="G100:Q100" si="16">IF(G$4="","",G104+G103)</f>
+        <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
         <v>7238279</v>
       </c>
       <c r="H100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>8249751</v>
       </c>
       <c r="I100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>8275751</v>
       </c>
       <c r="J100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>7847134</v>
       </c>
       <c r="K100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>7208409</v>
       </c>
       <c r="L100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>6542493</v>
       </c>
       <c r="M100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>5772034</v>
       </c>
       <c r="N100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>5108414</v>
       </c>
       <c r="O100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>4511682</v>
       </c>
       <c r="P100" s="278">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v>3942836</v>
       </c>
       <c r="Q100" s="278" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -14817,47 +14824,47 @@
       <c r="E107" s="243"/>
       <c r="F107" s="25"/>
       <c r="G107" s="91">
-        <f t="shared" ref="G107:Q107" si="17">IF(G$4="","",G101/G$4)</f>
+        <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
         <v>6.6962248566053942E-2</v>
       </c>
       <c r="H107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>5.246327190453378E-2</v>
       </c>
       <c r="I107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>4.989072704047566E-2</v>
       </c>
       <c r="J107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>2.7200831696654295E-2</v>
       </c>
       <c r="K107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>2.9843538065570184E-2</v>
       </c>
       <c r="L107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="O107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="P107" s="91">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="Q107" s="91" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -14874,47 +14881,47 @@
       <c r="E108" s="243"/>
       <c r="F108" s="25"/>
       <c r="G108" s="91">
-        <f t="shared" ref="G108:Q108" si="18">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>0.26858979419336082</v>
       </c>
       <c r="H108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0.21269095584561662</v>
       </c>
       <c r="I108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0.25072779567015685</v>
       </c>
       <c r="J108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0.21594833368302657</v>
       </c>
       <c r="K108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0.25418736859569985</v>
       </c>
       <c r="L108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P108" s="91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q108" s="91" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -15017,11 +15024,11 @@
       <c r="E113" s="242"/>
       <c r="G113" s="258">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.1328428033755111</v>
+        <v>1.1216280762509929</v>
       </c>
       <c r="H113" s="258">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.0562397345221735</v>
+        <v>1.0512340592849492</v>
       </c>
       <c r="I113" s="258">
         <f>IF(I$4="","",Data!E$22/I19)</f>
@@ -15125,51 +15132,51 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.4189705857001696</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="E116" s="242"/>
       <c r="G116" s="22">
-        <f>IF(G4="","",G77)</f>
-        <v>0.51159046230921634</v>
+        <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
+        <v>0.51460063887624929</v>
       </c>
       <c r="H116" s="22">
-        <f>IF(H4="","",H77)</f>
-        <v>0.64096286608709419</v>
+        <f t="shared" si="44"/>
+        <v>0.64285476560046906</v>
       </c>
       <c r="I116" s="22">
-        <f>IF(I4="","",I77)</f>
+        <f t="shared" si="44"/>
         <v>0.5400405042120513</v>
       </c>
       <c r="J116" s="22">
-        <f>IF(J4="","",J77)</f>
+        <f t="shared" si="44"/>
         <v>0.54517019168922476</v>
       </c>
       <c r="K116" s="22">
-        <f>IF(K4="","",K77)</f>
+        <f t="shared" si="44"/>
         <v>0.55575558100053002</v>
       </c>
       <c r="L116" s="22">
-        <f>IF(L4="","",L77)</f>
+        <f t="shared" si="44"/>
         <v>0.53879282860344957</v>
       </c>
       <c r="M116" s="22">
-        <f>IF(M4="","",M77)</f>
+        <f t="shared" si="44"/>
         <v>0.52903441472440782</v>
       </c>
       <c r="N116" s="22">
-        <f>IF(N4="","",N77)</f>
+        <f t="shared" si="44"/>
         <v>0.42375819789765556</v>
       </c>
       <c r="O116" s="22">
-        <f>IF(O4="","",O77)</f>
+        <f t="shared" si="44"/>
         <v>0.39300125034019506</v>
       </c>
       <c r="P116" s="22">
-        <f>IF(P4="","",P77)</f>
+        <f t="shared" si="44"/>
         <v>0.35779540777645402</v>
       </c>
       <c r="Q116" s="22" t="str">
-        <f>IF(Q4="","",Q77)</f>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -15183,47 +15190,47 @@
       </c>
       <c r="E117" s="242"/>
       <c r="G117" s="40">
-        <f>IF(G4="","",G4/G100)</f>
+        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",G4/G100)</f>
         <v>0.28701352904468036</v>
       </c>
       <c r="H117" s="40">
-        <f>IF(H4="","",H4/H100)</f>
+        <f t="shared" si="45"/>
         <v>0.31855858437424356</v>
       </c>
       <c r="I117" s="40">
-        <f>IF(I4="","",I4/I100)</f>
+        <f t="shared" si="45"/>
         <v>0.26240833007179648</v>
       </c>
       <c r="J117" s="40">
-        <f>IF(J4="","",J4/J100)</f>
+        <f t="shared" si="45"/>
         <v>0.29639458176705025</v>
       </c>
       <c r="K117" s="40">
-        <f>IF(K4="","",K4/K100)</f>
+        <f t="shared" si="45"/>
         <v>0.26254572957777506</v>
       </c>
       <c r="L117" s="40">
-        <f>IF(L4="","",L4/L100)</f>
+        <f t="shared" si="45"/>
         <v>0.28285456323759156</v>
       </c>
       <c r="M117" s="40">
-        <f>IF(M4="","",M4/M100)</f>
+        <f t="shared" si="45"/>
         <v>0.2860861526456705</v>
       </c>
       <c r="N117" s="40">
-        <f>IF(N4="","",N4/N100)</f>
+        <f t="shared" si="45"/>
         <v>0.28917155109198278</v>
       </c>
       <c r="O117" s="40">
-        <f>IF(O4="","",O4/O100)</f>
+        <f t="shared" si="45"/>
         <v>0.28097170855570053</v>
       </c>
       <c r="P117" s="40">
-        <f>IF(P4="","",P4/P100)</f>
+        <f t="shared" si="45"/>
         <v>0.28100585466907574</v>
       </c>
       <c r="Q117" s="40" t="str">
-        <f>IF(Q4="","",Q4/Q100)</f>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -15239,47 +15246,47 @@
       <c r="E118" s="246"/>
       <c r="F118" s="11"/>
       <c r="G118" s="15">
-        <f t="shared" ref="G118:Q118" si="19">IF(G$4="","",G100/G104)</f>
+        <f t="shared" ref="G118:Q118" si="46">IF(G$4="","",G100/G104)</f>
         <v>1.4876341835211095</v>
       </c>
       <c r="H118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.340152941245272</v>
       </c>
       <c r="I118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.2588868586268289</v>
       </c>
       <c r="J118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.2834689018849186</v>
       </c>
       <c r="K118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.270804362236263</v>
       </c>
       <c r="L118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.2723421973105857</v>
       </c>
       <c r="M118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.258836612388563</v>
       </c>
       <c r="N118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.2610618475033715</v>
       </c>
       <c r="O118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.2516790104824409</v>
       </c>
       <c r="P118" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v>1.3016784195652749</v>
       </c>
       <c r="Q118" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -15290,53 +15297,53 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.12522184312454268</v>
+        <v>0.12416948697308672</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="245"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
-        <f>IF(G$4="","",G11/G104)</f>
-        <v>0.21843436133977279</v>
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
+        <v>0.21971961985098865</v>
       </c>
       <c r="H119" s="99">
-        <f>IF(H$4="","",H11/H104)</f>
-        <v>0.27363808735396766</v>
+        <f t="shared" si="47"/>
+        <v>0.27444577184194152</v>
       </c>
       <c r="I119" s="99">
-        <f>IF(I$4="","",I11/I104)</f>
+        <f t="shared" si="47"/>
         <v>0.17839827535221295</v>
       </c>
       <c r="J119" s="99">
-        <f>IF(J$4="","",J11/J104)</f>
+        <f t="shared" si="47"/>
         <v>0.20738995263987398</v>
       </c>
       <c r="K119" s="99">
-        <f>IF(K$4="","",K11/K104)</f>
+        <f t="shared" si="47"/>
         <v>0.18542465869344466</v>
       </c>
       <c r="L119" s="99">
-        <f>IF(L$4="","",L11/L104)</f>
+        <f t="shared" si="47"/>
         <v>0.19390496386097003</v>
       </c>
       <c r="M119" s="99">
-        <f>IF(M$4="","",M11/M104)</f>
+        <f t="shared" si="47"/>
         <v>0.19052419156972641</v>
       </c>
       <c r="N119" s="99">
-        <f>IF(N$4="","",N11/N104)</f>
+        <f t="shared" si="47"/>
         <v>0.15452902490642165</v>
       </c>
       <c r="O119" s="99">
-        <f>IF(O$4="","",O11/O104)</f>
+        <f t="shared" si="47"/>
         <v>0.13821319105208374</v>
       </c>
       <c r="P119" s="99">
-        <f>IF(P$4="","",P11/P104)</f>
+        <f t="shared" si="47"/>
         <v>0.13087413834086048</v>
       </c>
       <c r="Q119" s="99" t="str">
-        <f>IF(Q$4="","",Q11/Q104)</f>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -15411,53 +15418,53 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16487832026730623</v>
+        <v>0.16307394337009629</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
-        <f>IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.29386908450509636</v>
+        <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.29680736829349108</v>
       </c>
       <c r="H123" s="160">
-        <f>IF(H$4="","",H14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.49060170491364385</v>
+        <f t="shared" si="48"/>
+        <v>0.49293780959360128</v>
       </c>
       <c r="I123" s="160">
-        <f>IF(I$4="","",I14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.34729679444034101</v>
       </c>
       <c r="J123" s="160">
-        <f>IF(J$4="","",J14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.38000999612295283</v>
       </c>
       <c r="K123" s="160">
-        <f>IF(K$4="","",K14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.32502847488751863</v>
       </c>
       <c r="L123" s="160">
-        <f>IF(L$4="","",L14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.29553237207772143</v>
       </c>
       <c r="M123" s="160">
-        <f>IF(M$4="","",M14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.27589195291859731</v>
       </c>
       <c r="N123" s="160">
-        <f>IF(N$4="","",N14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.16846424935786589</v>
       </c>
       <c r="O123" s="160">
-        <f>IF(O$4="","",O14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.13163041716341178</v>
       </c>
       <c r="P123" s="160">
-        <f>IF(P$4="","",P14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v>0.10396064169677659</v>
       </c>
       <c r="Q123" s="160" t="str">
-        <f>IF(Q$4="","",Q14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -15468,53 +15475,53 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7852042199054821E-2</v>
+        <v>5.7218927498279393E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
-        <f t="shared" ref="G124" si="20">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1031119594754724</v>
+        <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
+        <v>0.10414293624333019</v>
       </c>
       <c r="H124" s="74">
-        <f t="shared" ref="H124" si="21">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.1721409490925066</v>
+        <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
+        <v>0.17296063494512326</v>
       </c>
       <c r="I124" s="74">
-        <f t="shared" ref="I124" si="22">IF(I$4="","",I123/Market_Price)</f>
+        <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
         <v>0.12185852436503193</v>
       </c>
       <c r="J124" s="74">
-        <f t="shared" ref="J124" si="23">IF(J$4="","",J123/Market_Price)</f>
+        <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
         <v>0.13333684074489571</v>
       </c>
       <c r="K124" s="74">
-        <f t="shared" ref="K124" si="24">IF(K$4="","",K123/Market_Price)</f>
+        <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
         <v>0.11404507890790126</v>
       </c>
       <c r="L124" s="74">
-        <f t="shared" ref="L124" si="25">IF(L$4="","",L123/Market_Price)</f>
+        <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
         <v>0.10369556915007769</v>
       </c>
       <c r="M124" s="74">
-        <f t="shared" ref="M124" si="26">IF(M$4="","",M123/Market_Price)</f>
+        <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
         <v>9.6804194006525374E-2</v>
       </c>
       <c r="N124" s="74">
-        <f t="shared" ref="N124" si="27">IF(N$4="","",N123/Market_Price)</f>
+        <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
         <v>5.911026293258452E-2</v>
       </c>
       <c r="O124" s="74">
-        <f t="shared" ref="O124" si="28">IF(O$4="","",O123/Market_Price)</f>
+        <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
         <v>4.6186111285407644E-2</v>
       </c>
       <c r="P124" s="74">
-        <f t="shared" ref="P124" si="29">IF(P$4="","",P123/Market_Price)</f>
+        <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
         <v>3.6477418139219855E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
-        <f t="shared" ref="Q124" si="30">IF(Q$4="","",Q123/Market_Price)</f>
+        <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -16252,7 +16259,7 @@
     <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G23:Q25 G4:Q11 G13:Q16">
+  <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -16316,7 +16323,7 @@
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16376,7 +16383,7 @@
       </c>
       <c r="C6" s="291">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>4678840.1745434245</v>
+        <v>4627636.4074077774</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16398,7 +16405,7 @@
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
-        <v>-2129.4182160879991</v>
+        <v>-7249.7949296527995</v>
       </c>
       <c r="J6" s="313"/>
       <c r="N6" s="136"/>
@@ -16439,7 +16446,7 @@
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
-        <v>6239586.0961522246</v>
+        <v>6188382.3290165775</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16462,7 +16469,7 @@
       </c>
       <c r="I8" s="321">
         <f>Normalized_FCF!C10</f>
-        <v>668.5817839120009</v>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="J8" s="321"/>
       <c r="N8" s="312"/>
@@ -16482,7 +16489,7 @@
         <v>CNY/HKD</v>
       </c>
       <c r="F9" s="331"/>
-      <c r="H9" s="473" t="str">
+      <c r="H9" s="316" t="str">
         <f>Normalized_FCF!B79</f>
         <v>NCI’s Share of Profits</v>
       </c>
@@ -16500,7 +16507,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6801148.8448059252</v>
+        <v>6745336.7386280699</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16522,7 +16529,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16645,7 +16652,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.6242418979097106</v>
+        <v>3.6001835392802444</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16720,7 +16727,7 @@
       </c>
       <c r="G21" s="285">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>620663.51378336665</v>
+        <v>615543.1370698018</v>
       </c>
       <c r="H21" s="307">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16728,11 +16735,11 @@
       </c>
       <c r="I21" s="285">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>357474.28742410452</v>
+        <v>353634.00488893088</v>
       </c>
       <c r="J21" s="307">
         <f>I21/C4-1</f>
-        <v>1.869772304981665E-2</v>
+        <v>1.8904609194863919E-2</v>
       </c>
       <c r="K21" s="120">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16740,7 +16747,7 @@
       </c>
       <c r="L21" s="285">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>332534.22085963213</v>
+        <v>328961.86501295894</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.15">
@@ -16769,7 +16776,7 @@
       </c>
       <c r="G22" s="285">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>632255.56617903092</v>
+        <v>627135.18946546607</v>
       </c>
       <c r="H22" s="307">
         <f t="shared" si="2"/>
@@ -16777,11 +16784,11 @@
       </c>
       <c r="I22" s="285">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>364157.6868361847</v>
+        <v>360317.40430101112</v>
       </c>
       <c r="J22" s="307">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.8696168220208476E-2</v>
+        <v>1.8899198944907436E-2</v>
       </c>
       <c r="K22" s="120">
         <f t="shared" si="3"/>
@@ -16789,7 +16796,7 @@
       </c>
       <c r="L22" s="285">
         <f t="shared" si="4"/>
-        <v>315117.52241097653</v>
+        <v>311794.40069314104</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.15">
@@ -16818,7 +16825,7 @@
       </c>
       <c r="G23" s="285">
         <f t="shared" si="8"/>
-        <v>644063.38158650743</v>
+        <v>638943.00487294258</v>
       </c>
       <c r="H23" s="307">
         <f t="shared" si="2"/>
@@ -16826,11 +16833,11 @@
       </c>
       <c r="I23" s="285">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>370965.48444256862</v>
+        <v>367125.20190739498</v>
       </c>
       <c r="J23" s="307">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.8694642053365129E-2</v>
+        <v>1.8893890567374783E-2</v>
       </c>
       <c r="K23" s="120">
         <f t="shared" si="3"/>
@@ -16838,7 +16845,7 @@
       </c>
       <c r="L23" s="285">
         <f t="shared" si="4"/>
-        <v>298612.5876252958</v>
+        <v>295521.31160870468</v>
       </c>
       <c r="N23" s="283"/>
       <c r="O23" s="283"/>
@@ -16875,7 +16882,7 @@
       </c>
       <c r="G24" s="285">
         <f t="shared" si="8"/>
-        <v>656090.97600535222</v>
+        <v>650970.59929178737</v>
       </c>
       <c r="H24" s="307">
         <f t="shared" si="2"/>
@@ -16883,11 +16890,11 @@
       </c>
       <c r="I24" s="285">
         <f t="shared" si="9"/>
-        <v>377899.99566835572</v>
+        <v>374059.71313318203</v>
       </c>
       <c r="J24" s="307">
         <f t="shared" si="10"/>
-        <v>1.8693144016369123E-2</v>
+        <v>1.888868208926775E-2</v>
       </c>
       <c r="K24" s="120">
         <f t="shared" si="3"/>
@@ -16895,7 +16902,7 @@
       </c>
       <c r="L24" s="285">
         <f t="shared" si="4"/>
-        <v>282971.71695895452</v>
+        <v>280096.11136212555</v>
       </c>
       <c r="N24" s="283"/>
       <c r="O24" s="283"/>
@@ -16932,7 +16939,7 @@
       </c>
       <c r="G25" s="285">
         <f t="shared" si="8"/>
-        <v>668342.44018496876</v>
+        <v>663222.0634714039</v>
       </c>
       <c r="H25" s="307">
         <f t="shared" si="2"/>
@@ -16940,11 +16947,11 @@
       </c>
       <c r="I25" s="285">
         <f t="shared" si="9"/>
-        <v>384963.57903568045</v>
+        <v>381123.29650050681</v>
       </c>
       <c r="J25" s="307">
         <f t="shared" si="10"/>
-        <v>1.8691673586373136E-2</v>
+        <v>1.8883571577807956E-2</v>
       </c>
       <c r="K25" s="120">
         <f t="shared" si="3"/>
@@ -16952,7 +16959,7 @@
       </c>
       <c r="L25" s="285">
         <f t="shared" si="4"/>
-        <v>268149.70411769941</v>
+        <v>265474.72216716083</v>
       </c>
       <c r="N25" s="283"/>
       <c r="O25" s="283"/>
@@ -18270,7 +18277,7 @@
       </c>
       <c r="G51" s="285">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>668342.44018496876</v>
+        <v>663222.0634714039</v>
       </c>
       <c r="H51" s="307">
         <f>F18</f>
@@ -18278,11 +18285,11 @@
       </c>
       <c r="I51" s="285">
         <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
-        <v>6683424.401849688</v>
+        <v>6632220.634714039</v>
       </c>
       <c r="J51" s="424">
         <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>0.30208897006401592</v>
+        <v>0.3051328852653632</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18290,7 +18297,7 @@
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>4655396.9607678121</v>
+        <v>4619730.5347606307</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.15">
@@ -18303,7 +18310,7 @@
       <c r="K52" s="463"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>6152782.712740371</v>
+        <v>6101578.945604722</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.15">
@@ -18327,7 +18334,7 @@
     <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>6152782.712740371</v>
+        <v>6101578.945604722</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18362,19 +18369,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>3560752.6739114448</v>
+        <v>3509548.9067757959</v>
       </c>
       <c r="C56" s="119">
-        <v>5922264.5840855371</v>
+        <v>5871060.8169498891</v>
       </c>
       <c r="D56" s="119">
-        <v>6190598.5136441011</v>
+        <v>6139394.746508453</v>
       </c>
       <c r="E56" s="119">
-        <v>6469057.316569577</v>
+        <v>6417853.549433928</v>
       </c>
       <c r="F56" s="119">
-        <v>8023647.834886956</v>
+        <v>7972444.0677513061</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18388,19 +18395,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>2519280.4937807024</v>
+        <v>2468076.7266450538</v>
       </c>
       <c r="C57" s="119">
-        <v>5797393.264842676</v>
+        <v>5746189.4977070298</v>
       </c>
       <c r="D57" s="119">
-        <v>6265785.9077589866</v>
+        <v>6214582.1406233367</v>
       </c>
       <c r="E57" s="119">
-        <v>6772859.4885812942</v>
+        <v>6721655.7214456452</v>
       </c>
       <c r="F57" s="119">
-        <v>9999785.1733602174</v>
+        <v>9948581.4062245712</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18414,19 +18421,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>2090911.6269470521</v>
+        <v>2039707.8598114038</v>
       </c>
       <c r="C58" s="285">
-        <v>5705976.2053685235</v>
+        <v>5654772.4382328764</v>
       </c>
       <c r="D58" s="119">
-        <v>6323609.3005885473</v>
+        <v>6272405.5334528992</v>
       </c>
       <c r="E58" s="119">
-        <v>7018180.4605820049</v>
+        <v>6966976.6934463568</v>
       </c>
       <c r="F58" s="119">
-        <v>12022308.691164127</v>
+        <v>11971104.924028479</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18449,19 +18456,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>1914718.8398777812</v>
+        <v>1863515.0727421327</v>
       </c>
       <c r="C59" s="285">
-        <v>5639050.6790461261</v>
+        <v>5587846.911910478</v>
       </c>
       <c r="D59" s="119">
-        <v>6368078.7864336483</v>
+        <v>6316875.0192980003</v>
       </c>
       <c r="E59" s="119">
-        <v>7216277.7253410388</v>
+        <v>7165073.9582053907</v>
       </c>
       <c r="F59" s="119">
-        <v>14092307.218306091</v>
+        <v>14041103.451170441</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18484,19 +18491,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>1842248.8248538072</v>
+        <v>1791045.0577181585</v>
       </c>
       <c r="C60" s="285">
-        <v>5590055.1622433076</v>
+        <v>5538851.3951076595</v>
       </c>
       <c r="D60" s="119">
-        <v>6402278.3564442908</v>
+        <v>6351074.5893086437</v>
       </c>
       <c r="E60" s="119">
-        <v>7376241.7348791063</v>
+        <v>7325037.9677434601</v>
       </c>
       <c r="F60" s="119">
-        <v>16210895.143069753</v>
+        <v>16159691.375934105</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18519,19 +18526,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>1812441.117257297</v>
+        <v>1761237.3501216481</v>
       </c>
       <c r="C61" s="285">
-        <v>5554186.0283165742</v>
+        <v>5502982.2611809243</v>
       </c>
       <c r="D61" s="119">
-        <v>6428579.7756463708</v>
+        <v>6377376.0085107237</v>
       </c>
       <c r="E61" s="119">
-        <v>7505413.0506901648</v>
+        <v>7454209.2835545167</v>
       </c>
       <c r="F61" s="119">
-        <v>18379213.01194841</v>
+        <v>18328009.244812761</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18628,23 +18635,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18660,23 +18667,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.4063629850693284</v>
+        <v>2.3823046264398617</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.5159317457468959</v>
+        <v>3.4918733871174301</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.6420098503650884</v>
+        <v>3.6179514917356226</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.7728451798549165</v>
+        <v>3.7487868212254503</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>4.5032776910520962</v>
+        <v>4.4792193324226286</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18692,23 +18699,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>1.9170218171466811</v>
+        <v>1.892963458517215</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.4572603012627305</v>
+        <v>3.4332019426332656</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>3.6773370419609503</v>
+        <v>3.6532786833314832</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>3.9155882242740079</v>
+        <v>3.8915298656445416</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>5.4317761873467001</v>
+        <v>5.4077178287172352</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18724,23 +18731,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.7157504576258105</v>
+        <v>1.6916920989963447</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.414307516248809</v>
+        <v>3.3902491576193436</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>3.7045056664525955</v>
+        <v>3.6804473078231297</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>4.0308535700460641</v>
+        <v>4.0067952114165974</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>6.3820694733650969</v>
+        <v>6.3580111147356311</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18756,23 +18763,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.6329653522251077</v>
+        <v>1.6089069935956413</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.3828622065811724</v>
+        <v>3.3588038479517066</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>3.7253998876862631</v>
+        <v>3.7013415290567968</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>4.1239306092112376</v>
+        <v>4.0998722505817708</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>7.3546691415988166</v>
+        <v>7.3306107829693499</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18788,23 +18795,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.5989149354518519</v>
+        <v>1.5748565768223854</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.3598414059561814</v>
+        <v>3.3357830473267152</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>3.7414687350839526</v>
+        <v>3.7174103764544868</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.1990905383445538</v>
+        <v>4.1750321797150889</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>8.3500987932295718</v>
+        <v>8.326040434600106</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18820,23 +18827,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.584909627651367</v>
+        <v>1.5608512690219007</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3429881051931418</v>
+        <v>3.3189297465636751</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>3.7538265948865575</v>
+        <v>3.7297682362570916</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>4.2597823587762367</v>
+        <v>4.2357240001467709</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>9.3688943200111225</v>
+        <v>9.3448359613816532</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18883,7 +18890,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>4.5032776910520962</v>
+        <v>4.4792193324226286</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -18911,7 +18918,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.7728451798549165</v>
+        <v>3.7487868212254503</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -18939,7 +18946,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.6420098503650884</v>
+        <v>3.6179514917356226</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -18967,7 +18974,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.5159317457468959</v>
+        <v>3.4918733871174301</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -18995,7 +19002,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.4063629850693284</v>
+        <v>2.3823046264398617</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19197,7 +19204,7 @@
       </c>
       <c r="C8" s="283">
         <f>Normalized_FCF!G19</f>
-        <v>625446</v>
+        <v>631699.59365518577</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -19213,7 +19220,7 @@
       </c>
       <c r="C9" s="283">
         <f>Normalized_FCF!C19</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -19267,7 +19274,7 @@
       </c>
       <c r="C14" s="145">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-8.0129772724134352E-2</v>
+        <v>-7.5542496754235966E-2</v>
       </c>
       <c r="E14" s="464"/>
       <c r="F14" s="464"/>
@@ -19344,7 +19351,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.7728451798549165</v>
+        <v>3.7487868212254503</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19368,7 +19375,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.6420098503650884</v>
+        <v>3.6179514917356226</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19391,7 +19398,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.5159317457468959</v>
+        <v>3.4918733871174301</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19407,7 +19414,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.6429612953394157</v>
+        <v>3.6189029367099499</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19454,7 +19461,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>4.5032776910520962</v>
+        <v>4.4792193324226286</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19477,7 +19484,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.4063629850693284</v>
+        <v>2.3823046264398617</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19533,7 +19540,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18043592891736998</v>
+        <v>0.17676784240120927</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.15">
@@ -19542,7 +19549,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19553,7 +19560,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.16347546052465062</v>
+        <v>0.16476263394177712</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.15">
@@ -19562,7 +19569,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.6241471996115449</v>
+        <v>3.600088840982079</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19665,7 +19672,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.6242418979097106</v>
+        <v>3.6001835392802444</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19728,7 +19735,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.23729758910446588</v>
+        <v>0.23888338066482792</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
@@ -19806,11 +19813,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>1.9885581342175827</v>
+        <v>1.9753573887418812</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>2.1938365978664169</v>
+        <v>2.1806358523907154</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19818,7 +19825,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.39466128801237321</v>
+        <v>0.39428276670087581</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.15">
@@ -19831,11 +19838,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.3194542077513889</v>
+        <v>2.3040568582285306</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.548702207751389</v>
+        <v>2.5333048582285307</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19843,7 +19850,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.29674429117432854</v>
+        <v>0.29632157145948024</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
@@ -19877,11 +19884,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>2.9026087142285588</v>
+        <v>2.8833401808159511</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>3.1725868773100352</v>
+        <v>3.1533183438974275</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19889,7 +19896,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.12462055053780174</v>
+        <v>0.12412289276567134</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.15">
@@ -19902,11 +19909,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>3.1360927633198878</v>
+        <v>3.1152742810012586</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.4219467384415752</v>
+        <v>3.4011282561229459</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -19914,7 +19921,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>5.5792563059150146E-2</v>
+        <v>5.5265465283589554E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20055,7 +20062,7 @@
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.18043592891736998</v>
+        <v>0.17676784240120927</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -20082,13 +20089,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="466" t="s">
         <v>507</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="466"/>
+      <c r="D12" s="466"/>
+      <c r="E12" s="466"/>
+      <c r="F12" s="466"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="356" t="s">
@@ -20152,7 +20159,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.6241471996115449</v>
+        <v>3.600088840982079</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>367</v>
@@ -20204,7 +20211,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>2.1938365978664169</v>
+        <v>2.1806358523907154</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>449</v>
@@ -20220,7 +20227,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.548702207751389</v>
+        <v>2.5333048582285307</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>450</v>
@@ -20236,7 +20243,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>3.1725868773100352</v>
+        <v>3.1533183438974275</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>452</v>
@@ -20252,7 +20259,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.4219467384415752</v>
+        <v>3.4011282561229459</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>451</v>
@@ -20273,22 +20280,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="466" t="s">
         <v>508</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="466"/>
+      <c r="D29" s="466"/>
+      <c r="E29" s="466"/>
+      <c r="F29" s="466"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="467" t="s">
         <v>509</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="378" t="s">
@@ -20340,7 +20347,7 @@
       </c>
       <c r="C37" s="382">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>173178.99999999997</v>
       </c>
       <c r="D37" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20353,7 +20360,7 @@
       </c>
       <c r="C38" s="382">
         <f>Normalized_FCF!C16</f>
-        <v>0</v>
+        <v>-173178.99999999997</v>
       </c>
       <c r="D38" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20397,7 +20404,7 @@
       </c>
       <c r="C44" s="385">
         <f>Normalized_FCF!C46</f>
-        <v>6060.7417839120008</v>
+        <v>3636.4450703472003</v>
       </c>
       <c r="D44" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20412,7 +20419,7 @@
       </c>
       <c r="C45" s="385">
         <f>Normalized_FCF!C45</f>
-        <v>-5392.16</v>
+        <v>-8088.24</v>
       </c>
       <c r="D45" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20427,7 +20434,7 @@
       </c>
       <c r="C46" s="382">
         <f>Normalized_FCF!C10</f>
-        <v>668.5817839120009</v>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="D46" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20467,7 +20474,7 @@
       </c>
       <c r="C52" s="382">
         <f>Normalized_FCF!C12</f>
-        <v>-152320.82044597794</v>
+        <v>-151040.72626758672</v>
       </c>
       <c r="D52" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20478,10 +20485,10 @@
       <c r="B54" s="465" t="s">
         <v>516</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="468"/>
+      <c r="D54" s="468"/>
+      <c r="E54" s="468"/>
+      <c r="F54" s="468"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="381" t="s">
@@ -20497,22 +20504,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="466" t="s">
         <v>517</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="466"/>
+      <c r="D57" s="466"/>
+      <c r="E57" s="466"/>
+      <c r="F57" s="466"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="466" t="s">
         <v>518</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="466"/>
+      <c r="D58" s="466"/>
+      <c r="E58" s="466"/>
+      <c r="F58" s="466"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="381" t="s">
@@ -20520,7 +20527,7 @@
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
-        <v>625446</v>
+        <v>631699.59365518577</v>
       </c>
       <c r="D60" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20533,7 +20540,7 @@
       </c>
       <c r="C61" s="382">
         <f>Normalized_FCF!C19</f>
-        <v>350913.01309075684</v>
+        <v>347072.73055558326</v>
       </c>
       <c r="D61" s="352" t="str">
         <f>Reporting_currency</f>
@@ -20546,7 +20553,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.7852042199054821E-2</v>
+        <v>5.7218927498279393E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20563,7 +20570,7 @@
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
-        <v>1.0524609889200147</v>
+        <v>1.0641062355754669</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -20583,11 +20590,11 @@
       </c>
       <c r="C66" s="387">
         <f>Normalized_FCF!C119</f>
-        <v>0.12522184312454268</v>
+        <v>0.12416948697308672</v>
       </c>
       <c r="D66" s="387">
         <f>Normalized_FCF!G119</f>
-        <v>0.21843436133977279</v>
+        <v>0.21971961985098865</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -20597,11 +20604,11 @@
       </c>
       <c r="C67" s="392">
         <f>Normalized_FCF!C116</f>
-        <v>0.4189705857001696</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D67" s="392">
         <f>Normalized_FCF!G116</f>
-        <v>0.51159046230921634</v>
+        <v>0.51460063887624929</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -20647,22 +20654,22 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="466" t="s">
         <v>519</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="466"/>
+      <c r="D73" s="466"/>
+      <c r="E73" s="466"/>
+      <c r="F73" s="466"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="467" t="s">
         <v>488</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="467"/>
+      <c r="D74" s="467"/>
+      <c r="E74" s="467"/>
+      <c r="F74" s="467"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="378" t="s">
@@ -20670,13 +20677,13 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="466" t="s">
         <v>520</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="466"/>
+      <c r="D77" s="466"/>
+      <c r="E77" s="466"/>
+      <c r="F77" s="466"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="352" t="s">
@@ -20825,33 +20832,33 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="466" t="s">
         <v>523</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="466"/>
+      <c r="D96" s="466"/>
+      <c r="E96" s="466"/>
+      <c r="F96" s="466"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="394"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="394"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="394"/>
@@ -20914,23 +20921,23 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="466" t="s">
         <v>526</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="466"/>
+      <c r="D107" s="466"/>
+      <c r="E107" s="466"/>
+      <c r="F107" s="466"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="466" t="s">
         <v>545</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="466"/>
+      <c r="D108" s="466"/>
+      <c r="E108" s="466"/>
+      <c r="F108" s="466"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="394"/>
@@ -20962,7 +20969,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.9317022632920868</v>
+        <v>2.907643904662621</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -20974,13 +20981,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="466" t="s">
         <v>527</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="466"/>
+      <c r="D114" s="466"/>
+      <c r="E114" s="466"/>
+      <c r="F114" s="466"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="394"/>
@@ -21025,7 +21032,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.5 HKD</v>
+        <v>4.48 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21048,7 +21055,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.77 HKD</v>
+        <v>3.75 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21070,7 +21077,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.64 HKD</v>
+        <v>3.62 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21092,7 +21099,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.52 HKD</v>
+        <v>3.49 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21114,7 +21121,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.41 HKD</v>
+        <v>2.38 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21136,7 +21143,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.6241471996115449</v>
+        <v>3.600088840982079</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21144,13 +21151,13 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="467" t="s">
+      <c r="B127" s="470" t="s">
         <v>529</v>
       </c>
-      <c r="C127" s="467"/>
-      <c r="D127" s="467"/>
-      <c r="E127" s="467"/>
-      <c r="F127" s="467"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="354" t="s">
@@ -21163,22 +21170,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="471" t="s">
         <v>530</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="466" t="s">
         <v>531</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="466"/>
+      <c r="D132" s="466"/>
+      <c r="E132" s="466"/>
+      <c r="F132" s="466"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="378" t="s">
@@ -21243,11 +21250,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>1.9885581342175827</v>
+        <v>1.9753573887418812</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>2.1938365978664169</v>
+        <v>2.1806358523907154</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21264,11 +21271,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.3194542077513889</v>
+        <v>2.3040568582285306</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.548702207751389</v>
+        <v>2.5333048582285307</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21304,11 +21311,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>2.9026087142285588</v>
+        <v>2.8833401808159511</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>3.1725868773100352</v>
+        <v>3.1533183438974275</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21325,11 +21332,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>3.1360927633198878</v>
+        <v>3.1152742810012586</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.4219467384415752</v>
+        <v>3.4011282561229459</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21347,13 +21354,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="470" t="s">
+      <c r="B149" s="472" t="s">
         <v>532</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="466"/>
+      <c r="D149" s="466"/>
+      <c r="E149" s="466"/>
+      <c r="F149" s="466"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="378" t="s">
@@ -21361,13 +21368,13 @@
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="468" t="s">
         <v>533</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="468"/>
+      <c r="D152" s="468"/>
+      <c r="E152" s="468"/>
+      <c r="F152" s="468"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="421" t="s">
@@ -21404,22 +21411,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="469" t="s">
         <v>393</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="469" t="s">
         <v>394</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="352" t="s">
@@ -21443,12 +21450,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21463,15 +21473,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF390F96-64AC-4ADB-8C95-DD0C33D85047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3213AE-84E2-4C66-A74A-64B020FB4FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="557">
   <si>
     <t>Sales</t>
   </si>
@@ -2126,9 +2126,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Note on g=0: It's to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-  </si>
-  <si>
     <t>@Target return</t>
   </si>
   <si>
@@ -2163,9 +2160,6 @@
   </si>
   <si>
     <t>Non-op EBIT</t>
-  </si>
-  <si>
-    <t>EBITDA</t>
   </si>
   <si>
     <t>T</t>
@@ -3265,16 +3259,19 @@
     <t>更新日期:</t>
   </si>
   <si>
+    <t>1448.HK</t>
+  </si>
+  <si>
     <t>福寿园</t>
   </si>
   <si>
-    <t>1448.HK</t>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>EBIT</t>
   </si>
   <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>CNY</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -4996,30 +4993,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5029,31 +5026,31 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{15EB927F-F885-4F39-B6B5-46C82A39870C}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{07C6F35C-38E6-4C10-90D6-CF6B1E223929}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5146,8 +5143,8 @@
       <sheetName val="Normalized_FCF"/>
       <sheetName val="DCF"/>
       <sheetName val="Scenarios"/>
+      <sheetName val="投资主题"/>
       <sheetName val="Breakdown"/>
-      <sheetName val="投资主题"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5424,10 +5421,10 @@
   <dimension ref="A2:I167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5446,7 +5443,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5454,13 +5451,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>325</v>
@@ -5471,13 +5468,13 @@
         <v>352</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5505,7 +5502,7 @@
         <v>353</v>
       </c>
       <c r="C8" s="47">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5517,11 +5514,11 @@
         <v>2319863422</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.20873884600524042</v>
+        <v>0.19236735001465252</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5530,21 +5527,21 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6611.6107526999995</v>
+        <v>6634.8093869200002</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.6" customHeight="1">
-      <c r="B12" s="458" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5579,12 +5576,12 @@
         <v>357</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0900000000000001</v>
+        <v>1.0932867000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5593,7 +5590,7 @@
         <v>275</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5603,7 +5600,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.8123601295658958</v>
+        <v>3.7171512243872273</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>350</v>
@@ -5653,10 +5650,10 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>2.2971084387192842</v>
+        <v>2.2448676128324978</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5668,10 +5665,10 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.6691584829221733</v>
+        <v>2.6082247836078256</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E23" s="453">
         <v>0.25</v>
@@ -5683,10 +5680,10 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>3.3233281305004532</v>
+        <v>3.2470745506587226</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E24" s="453">
         <v>0.1174</v>
@@ -5698,13 +5695,13 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.5848135247730846</v>
+        <v>3.5184275020346356</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E25" s="454">
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5722,22 +5719,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5748,14 +5745,14 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B33" s="459" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5774,21 +5771,21 @@
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B36" s="459" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
       <c r="C37" s="293">
-        <f>Normalized_FCF!C9</f>
+        <f>Normalized_FCF!C15</f>
         <v>173178.99999999997</v>
       </c>
       <c r="D37" s="1" t="str">
@@ -5801,7 +5798,7 @@
         <v>200</v>
       </c>
       <c r="C38" s="293">
-        <f>Normalized_FCF!C10</f>
+        <f>Normalized_FCF!C16</f>
         <v>-173178.99999999997</v>
       </c>
       <c r="D38" s="1" t="str">
@@ -5810,20 +5807,20 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
       <c r="C41" s="293">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>-2798</v>
       </c>
       <c r="D41" s="1" t="str">
@@ -5832,13 +5829,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5875,7 +5872,7 @@
         <v>203</v>
       </c>
       <c r="C46" s="293">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-4451.7949296527995</v>
       </c>
       <c r="D46" s="1" t="str">
@@ -5893,7 +5890,7 @@
         <v>223</v>
       </c>
       <c r="C49" s="293">
-        <f>Normalized_FCF!C15</f>
+        <f>Normalized_FCF!C13</f>
         <v>-106049.44824717694</v>
       </c>
       <c r="D49" s="1" t="str">
@@ -5902,20 +5899,20 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
       <c r="C52" s="293">
-        <f>Normalized_FCF!C14</f>
+        <f>Normalized_FCF!C12</f>
         <v>-151040.72626758672</v>
       </c>
       <c r="D52" s="1" t="str">
@@ -5924,7 +5921,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5945,23 +5942,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B57" s="458" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5995,7 +5992,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.7218927498279393E-2</v>
+        <v>5.7190791493898586E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6005,7 +6002,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.5859649122807019E-2</v>
+        <v>5.5664335664335672E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6046,7 +6043,7 @@
       </c>
       <c r="C67" s="270">
         <f>Normalized_FCF!C116</f>
-        <v>0.1338533079637913</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D67" s="270">
         <f>Normalized_FCF!G116</f>
@@ -6083,7 +6080,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6096,18 +6093,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
-        <v>487</v>
-      </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="B73" s="460" t="s">
+        <v>485</v>
+      </c>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6121,13 +6118,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6150,7 +6147,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.333836664975874E-2</v>
+        <v>-6.3529352163215411E-2</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6180,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6221,7 +6218,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.70843074207219081</v>
+        <v>0.71056688823729974</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6258,7 +6255,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8232284305571493E-2</v>
+        <v>8.8498332974220231E-2</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6271,11 +6268,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>0.73332465972800365</v>
+        <v>0.7355358690483047</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6284,7 +6281,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6295,32 +6292,32 @@
     <row r="95" spans="1:6">
       <c r="A95" s="192"/>
     </row>
-    <row r="96" spans="1:6" ht="11.65" customHeight="1">
-      <c r="B96" s="458" t="s">
-        <v>494</v>
-      </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
+        <v>492</v>
+      </c>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
-        <v>493</v>
-      </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="B97" s="464" t="s">
+        <v>491</v>
+      </c>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
-        <v>492</v>
-      </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="B98" s="464" t="s">
+        <v>490</v>
+      </c>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6329,11 +6326,11 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="102" spans="2:6">
@@ -6342,7 +6339,7 @@
       </c>
       <c r="C102" s="270">
         <f>E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="103" spans="2:6">
@@ -6370,35 +6367,35 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>0.40638898525639144</v>
+        <v>0.40761437853881549</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6411,25 +6408,25 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B114" s="458" t="s">
-        <v>500</v>
-      </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
+        <v>498</v>
+      </c>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6464,7 +6461,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.73 HKD</v>
+        <v>4.63 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6486,7 +6483,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.97 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6508,7 +6505,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.83 HKD</v>
+        <v>3.74 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6530,7 +6527,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.7 HKD</v>
+        <v>3.6 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6552,7 +6549,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.53 HKD</v>
+        <v>2.45 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6560,13 +6557,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6574,14 +6571,14 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.8123601295658958</v>
+        <v>3.7171512243872273</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.6" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="463" t="s">
         <v>361</v>
       </c>
@@ -6592,7 +6589,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6601,22 +6598,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>362</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6647,28 +6644,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6681,11 +6678,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>2.0918299750704499</v>
+        <v>2.0395891491836635</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>2.2971084387192842</v>
+        <v>2.2448676128324978</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6702,11 +6699,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.4399104829221732</v>
+        <v>2.3789767836078255</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.6691584829221733</v>
+        <v>2.6082247836078256</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6722,21 +6719,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6749,11 +6746,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>3.0533499674189768</v>
+        <v>2.9770963875772463</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>3.3233281305004532</v>
+        <v>3.2470745506587226</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6766,24 +6763,24 @@
       </c>
       <c r="C145" s="342">
         <f>Scenarios!C67</f>
-        <v>0.28585397512168731</v>
+        <v>0.28684217103797521</v>
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>3.2989595496513973</v>
+        <v>3.2315853309966602</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.5848135247730846</v>
+        <v>3.5184275020346356</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6792,13 +6789,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>363</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6834,37 +6831,37 @@
         <v>297</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B158" s="459" t="s">
-        <v>447</v>
-      </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
+        <v>445</v>
+      </c>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B161" s="464" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6888,18 +6885,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6916,6 +6901,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6943,12 +6940,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -7610,7 +7607,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8318,11 +8315,11 @@
         <v>47</v>
       </c>
       <c r="C46" s="278">
-        <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
+        <f>IF(C$4="","",-C14)</f>
         <v>-313181</v>
       </c>
       <c r="D46" s="278">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D46:M46" si="20">IF(D$4="","",-D14)</f>
         <v>-455638</v>
       </c>
       <c r="E46" s="278">
@@ -8519,11 +8516,11 @@
         <v>64</v>
       </c>
       <c r="C52" s="278">
-        <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
+        <f>IF(C$4="","",C13)</f>
         <v>21811</v>
       </c>
       <c r="D52" s="278">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="D52:M52" si="24">IF(D$4="","",D13)</f>
         <v>17341</v>
       </c>
       <c r="E52" s="278">
@@ -9537,15 +9534,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -10335,11 +10332,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0162592787326599</v>
+        <v>2.0223389478807432</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.40638898525639144</v>
+        <v>0.40761437853881549</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10418,11 +10415,11 @@
         <v>118</v>
       </c>
       <c r="C55" s="89">
-        <f>Normalized_FCF!C11/G40</f>
+        <f>Normalized_FCF!C9/G40</f>
         <v>-1.1084375151033524E-3</v>
       </c>
       <c r="D55" s="89">
-        <f>Normalized_FCF!G11/G40</f>
+        <f>Normalized_FCF!G9/G40</f>
         <v>-1.1084375151033524E-3</v>
       </c>
       <c r="F55" s="227"/>
@@ -10448,7 +10445,7 @@
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
-        <f>Normalized_FCF!G9/BS!$G$39</f>
+        <f>Normalized_FCF!G15/BS!$G$39</f>
         <v>6.4713105320271552E-2</v>
       </c>
       <c r="F58" s="5"/>
@@ -10745,11 +10742,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>146936.36000000002</v>
+        <v>147379.42030680002</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.3338366649758754E-2</v>
+        <v>6.3529352163215411E-2</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10762,11 +10759,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1643462.5655535921</v>
+        <v>1648418.1329060739</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.70843074207219081</v>
+        <v>0.71056688823729985</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10779,11 +10776,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>204686.84899999999</v>
+        <v>205304.04557487002</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>8.8232284305571507E-2</v>
+        <v>8.8498332974220245E-2</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10796,11 +10793,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>1995085.7745535921</v>
+        <v>2001101.5987877438</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>0.8600013930275211</v>
+        <v>0.86259457337473555</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -10826,16 +10823,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10931,7 +10928,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11219,447 +11216,447 @@
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="274">
-        <f>BS!$G$39*BS!D58</f>
-        <v>173178.99999999997</v>
-      </c>
-      <c r="E9" s="242"/>
-      <c r="G9" s="274">
-        <f>IF(Data!C61="","",-Data!C61)</f>
-        <v>173179</v>
-      </c>
-      <c r="H9" s="274">
-        <f>IF(Data!D61="","",-Data!D61)</f>
-        <v>166609</v>
-      </c>
-      <c r="I9" s="274">
-        <f>IF(Data!E61="","",-Data!E61)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="274">
-        <f>IF(Data!F61="","",-Data!F61)</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="274">
-        <f>IF(Data!G61="","",-Data!G61)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="274">
-        <f>IF(Data!H61="","",-Data!H61)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="274">
-        <f>IF(Data!I61="","",-Data!I61)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="274">
-        <f>IF(Data!J61="","",-Data!J61)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="274">
-        <f>IF(Data!K61="","",-Data!K61)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="274">
-        <f>IF(Data!L61="","",-Data!L61)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="274" t="str">
-        <f>IF(Data!M61="","",-Data!M61)</f>
+      <c r="B9" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="C9" s="308">
+        <f>C61</f>
+        <v>-2798</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="278">
+        <f>G59</f>
+        <v>-2798</v>
+      </c>
+      <c r="H9" s="278">
+        <f t="shared" ref="H9:Q9" si="5">H59</f>
+        <v>-18436</v>
+      </c>
+      <c r="I9" s="278">
+        <f t="shared" si="5"/>
+        <v>-7407</v>
+      </c>
+      <c r="J9" s="278">
+        <f t="shared" si="5"/>
+        <v>-11577</v>
+      </c>
+      <c r="K9" s="278">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="L9" s="278">
+        <f t="shared" si="5"/>
+        <v>-176</v>
+      </c>
+      <c r="M9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="278">
+        <f t="shared" si="5"/>
+        <v>398</v>
+      </c>
+      <c r="O9" s="278">
+        <f t="shared" si="5"/>
+        <v>485</v>
+      </c>
+      <c r="P9" s="278">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="278" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>402</v>
+        <v>65</v>
       </c>
       <c r="C10" s="274">
-        <f>-C4*C76</f>
-        <v>-173178.99999999997</v>
+        <f>C48</f>
+        <v>-4451.7949296527995</v>
       </c>
       <c r="E10" s="242"/>
       <c r="G10" s="274">
-        <f>Data!C62</f>
-        <v>-173179</v>
+        <f>G48</f>
+        <v>-10168.406344814284</v>
       </c>
       <c r="H10" s="274">
-        <f>Data!D62</f>
-        <v>-166609</v>
+        <f t="shared" ref="H10:Q10" si="6">H48</f>
+        <v>-2420.0332137648202</v>
       </c>
       <c r="I10" s="274">
-        <f>Data!E62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-5008</v>
       </c>
       <c r="J10" s="274">
-        <f>Data!F62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-7246</v>
       </c>
       <c r="K10" s="274">
-        <f>Data!G62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-9525</v>
       </c>
       <c r="L10" s="274">
-        <f>Data!H62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-11128</v>
       </c>
       <c r="M10" s="274">
-        <f>Data!I62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-8293</v>
       </c>
       <c r="N10" s="274">
-        <f>Data!J62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-15585</v>
       </c>
       <c r="O10" s="274">
-        <f>Data!K62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-8256</v>
       </c>
       <c r="P10" s="274">
-        <f>Data!L62</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>-7799</v>
       </c>
       <c r="Q10" s="274" t="str">
-        <f>Data!M62</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
-      <c r="B11" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="C11" s="308">
-        <f>C61</f>
-        <v>-2798</v>
-      </c>
-      <c r="D11" s="55"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="278">
-        <f>G59</f>
-        <v>-2798</v>
-      </c>
-      <c r="H11" s="278">
-        <f t="shared" ref="H11:Q11" si="5">H59</f>
-        <v>-18436</v>
-      </c>
-      <c r="I11" s="278">
-        <f t="shared" si="5"/>
-        <v>-7407</v>
-      </c>
-      <c r="J11" s="278">
-        <f t="shared" si="5"/>
-        <v>-11577</v>
-      </c>
-      <c r="K11" s="278">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="L11" s="278">
-        <f t="shared" si="5"/>
-        <v>-176</v>
-      </c>
-      <c r="M11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="278">
-        <f t="shared" si="5"/>
-        <v>398</v>
-      </c>
-      <c r="O11" s="278">
-        <f t="shared" si="5"/>
-        <v>485</v>
-      </c>
-      <c r="P11" s="278">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="278" t="str">
-        <f t="shared" si="5"/>
+      <c r="B11" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="275">
+        <f>SUM(C8:C10)</f>
+        <v>604162.9050703469</v>
+      </c>
+      <c r="E11" s="242"/>
+      <c r="G11" s="275">
+        <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
+        <v>1069074.5936551858</v>
+      </c>
+      <c r="H11" s="275">
+        <f t="shared" si="7"/>
+        <v>1689440.9667862351</v>
+      </c>
+      <c r="I11" s="275">
+        <f t="shared" si="7"/>
+        <v>1172766</v>
+      </c>
+      <c r="J11" s="275">
+        <f t="shared" si="7"/>
+        <v>1267983</v>
+      </c>
+      <c r="K11" s="275">
+        <f t="shared" si="7"/>
+        <v>1051788</v>
+      </c>
+      <c r="L11" s="275">
+        <f t="shared" si="7"/>
+        <v>997076</v>
+      </c>
+      <c r="M11" s="275">
+        <f t="shared" si="7"/>
+        <v>873594</v>
+      </c>
+      <c r="N11" s="275">
+        <f t="shared" si="7"/>
+        <v>625979</v>
+      </c>
+      <c r="O11" s="275">
+        <f t="shared" si="7"/>
+        <v>498190</v>
+      </c>
+      <c r="P11" s="275">
+        <f t="shared" si="7"/>
+        <v>396423</v>
+      </c>
+      <c r="Q11" s="275" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C12" s="274">
-        <f>C48</f>
-        <v>-4451.7949296527995</v>
+        <f>-C11*C41</f>
+        <v>-151040.72626758672</v>
       </c>
       <c r="E12" s="242"/>
       <c r="G12" s="274">
-        <f>G48</f>
-        <v>-10168.406344814284</v>
+        <f>Data!C46</f>
+        <v>-313181</v>
       </c>
       <c r="H12" s="274">
-        <f t="shared" ref="H12:Q12" si="6">H48</f>
-        <v>-2420.0332137648202</v>
+        <f>Data!D46</f>
+        <v>-455638</v>
       </c>
       <c r="I12" s="274">
-        <f t="shared" si="6"/>
-        <v>-5008</v>
+        <f>Data!E46</f>
+        <v>-281476</v>
       </c>
       <c r="J12" s="274">
-        <f t="shared" si="6"/>
-        <v>-7246</v>
+        <f>Data!F46</f>
+        <v>-289591</v>
       </c>
       <c r="K12" s="274">
-        <f t="shared" si="6"/>
-        <v>-9525</v>
+        <f>Data!G46</f>
+        <v>-222784</v>
       </c>
       <c r="L12" s="274">
-        <f t="shared" si="6"/>
-        <v>-11128</v>
+        <f>Data!H46</f>
+        <v>-211350</v>
       </c>
       <c r="M12" s="274">
-        <f t="shared" si="6"/>
-        <v>-8293</v>
+        <f>Data!I46</f>
+        <v>-159140</v>
       </c>
       <c r="N12" s="274">
-        <f t="shared" si="6"/>
-        <v>-15585</v>
+        <f>Data!J46</f>
+        <v>-134611</v>
       </c>
       <c r="O12" s="274">
-        <f t="shared" si="6"/>
-        <v>-8256</v>
+        <f>Data!K46</f>
+        <v>-108508</v>
       </c>
       <c r="P12" s="274">
-        <f t="shared" si="6"/>
-        <v>-7799</v>
+        <f>Data!L46</f>
+        <v>-94437</v>
       </c>
       <c r="Q12" s="274" t="str">
-        <f t="shared" si="6"/>
+        <f>Data!M46</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
-      <c r="B13" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="275">
-        <f>SUM(C8:C12)</f>
-        <v>604162.9050703469</v>
-      </c>
-      <c r="E13" s="242"/>
-      <c r="G13" s="275">
-        <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1069074.5936551858</v>
-      </c>
-      <c r="H13" s="275">
-        <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1689440.9667862351</v>
-      </c>
-      <c r="I13" s="275">
-        <f t="shared" si="7"/>
-        <v>1172766</v>
-      </c>
-      <c r="J13" s="275">
-        <f t="shared" si="7"/>
-        <v>1267983</v>
-      </c>
-      <c r="K13" s="275">
-        <f t="shared" si="7"/>
-        <v>1051788</v>
-      </c>
-      <c r="L13" s="275">
-        <f t="shared" si="7"/>
-        <v>997076</v>
-      </c>
-      <c r="M13" s="275">
-        <f t="shared" si="7"/>
-        <v>873594</v>
-      </c>
-      <c r="N13" s="275">
-        <f t="shared" si="7"/>
-        <v>625979</v>
-      </c>
-      <c r="O13" s="275">
-        <f t="shared" si="7"/>
-        <v>498190</v>
-      </c>
-      <c r="P13" s="275">
-        <f t="shared" si="7"/>
-        <v>396423</v>
-      </c>
-      <c r="Q13" s="275" t="str">
-        <f t="shared" si="7"/>
+      <c r="B13" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="274">
+        <f>-C4*C79</f>
+        <v>-106049.44824717694</v>
+      </c>
+      <c r="D13" s="57"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="278">
+        <f>Data!C48</f>
+        <v>-124194</v>
+      </c>
+      <c r="H13" s="278">
+        <f>Data!D48</f>
+        <v>-184676</v>
+      </c>
+      <c r="I13" s="278">
+        <f>Data!E48</f>
+        <v>-152133</v>
+      </c>
+      <c r="J13" s="278">
+        <f>Data!F48</f>
+        <v>-169611</v>
+      </c>
+      <c r="K13" s="278">
+        <f>Data!G48</f>
+        <v>-137241</v>
+      </c>
+      <c r="L13" s="278">
+        <f>Data!H48</f>
+        <v>-156740</v>
+      </c>
+      <c r="M13" s="278">
+        <f>Data!I48</f>
+        <v>-127269</v>
+      </c>
+      <c r="N13" s="278">
+        <f>Data!J48</f>
+        <v>-132823</v>
+      </c>
+      <c r="O13" s="278">
+        <f>Data!K48</f>
+        <v>-109531</v>
+      </c>
+      <c r="P13" s="278">
+        <f>Data!L48</f>
+        <v>-80725</v>
+      </c>
+      <c r="Q13" s="278" t="str">
+        <f>Data!M48</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
-      <c r="B14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="274">
-        <f>-SUM(C8+C11,C12)*C41</f>
-        <v>-151040.72626758672</v>
-      </c>
-      <c r="E14" s="242"/>
-      <c r="G14" s="274">
-        <f>Data!C46</f>
-        <v>-313181</v>
-      </c>
-      <c r="H14" s="274">
-        <f>Data!D46</f>
-        <v>-455638</v>
-      </c>
-      <c r="I14" s="274">
-        <f>Data!E46</f>
-        <v>-281476</v>
-      </c>
-      <c r="J14" s="274">
-        <f>Data!F46</f>
-        <v>-289591</v>
-      </c>
-      <c r="K14" s="274">
-        <f>Data!G46</f>
-        <v>-222784</v>
-      </c>
-      <c r="L14" s="274">
-        <f>Data!H46</f>
-        <v>-211350</v>
-      </c>
-      <c r="M14" s="274">
-        <f>Data!I46</f>
-        <v>-159140</v>
-      </c>
-      <c r="N14" s="274">
-        <f>Data!J46</f>
-        <v>-134611</v>
-      </c>
-      <c r="O14" s="274">
-        <f>Data!K46</f>
-        <v>-108508</v>
-      </c>
-      <c r="P14" s="274">
-        <f>Data!L46</f>
-        <v>-94437</v>
-      </c>
-      <c r="Q14" s="274" t="str">
-        <f>Data!M46</f>
+      <c r="B14" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="277">
+        <f>SUM(C11:C13)</f>
+        <v>347072.73055558326</v>
+      </c>
+      <c r="D14" s="58"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="275">
+        <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
+        <v>631699.59365518577</v>
+      </c>
+      <c r="H14" s="275">
+        <f t="shared" si="8"/>
+        <v>1049126.9667862351</v>
+      </c>
+      <c r="I14" s="275">
+        <f t="shared" si="8"/>
+        <v>739157</v>
+      </c>
+      <c r="J14" s="275">
+        <f t="shared" si="8"/>
+        <v>808781</v>
+      </c>
+      <c r="K14" s="275">
+        <f t="shared" si="8"/>
+        <v>691763</v>
+      </c>
+      <c r="L14" s="275">
+        <f t="shared" si="8"/>
+        <v>628986</v>
+      </c>
+      <c r="M14" s="275">
+        <f t="shared" si="8"/>
+        <v>587185</v>
+      </c>
+      <c r="N14" s="275">
+        <f t="shared" si="8"/>
+        <v>358545</v>
+      </c>
+      <c r="O14" s="275">
+        <f t="shared" si="8"/>
+        <v>280151</v>
+      </c>
+      <c r="P14" s="275">
+        <f t="shared" si="8"/>
+        <v>221261</v>
+      </c>
+      <c r="Q14" s="275" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
-      <c r="B15" s="38" t="s">
-        <v>208</v>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C15" s="274">
-        <f>-C4*C81</f>
-        <v>-106049.44824717694</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="278">
-        <f>Data!C48</f>
-        <v>-124194</v>
-      </c>
-      <c r="H15" s="278">
-        <f>Data!D48</f>
-        <v>-184676</v>
-      </c>
-      <c r="I15" s="278">
-        <f>Data!E48</f>
-        <v>-152133</v>
-      </c>
-      <c r="J15" s="278">
-        <f>Data!F48</f>
-        <v>-169611</v>
-      </c>
-      <c r="K15" s="278">
-        <f>Data!G48</f>
-        <v>-137241</v>
-      </c>
-      <c r="L15" s="278">
-        <f>Data!H48</f>
-        <v>-156740</v>
-      </c>
-      <c r="M15" s="278">
-        <f>Data!I48</f>
-        <v>-127269</v>
-      </c>
-      <c r="N15" s="278">
-        <f>Data!J48</f>
-        <v>-132823</v>
-      </c>
-      <c r="O15" s="278">
-        <f>Data!K48</f>
-        <v>-109531</v>
-      </c>
-      <c r="P15" s="278">
-        <f>Data!L48</f>
-        <v>-80725</v>
-      </c>
-      <c r="Q15" s="278" t="str">
-        <f>Data!M48</f>
+        <f>BS!$G$39*BS!D58</f>
+        <v>173178.99999999997</v>
+      </c>
+      <c r="E15" s="242"/>
+      <c r="G15" s="274">
+        <f>IF(Data!C61="","",-Data!C61)</f>
+        <v>173179</v>
+      </c>
+      <c r="H15" s="274">
+        <f>IF(Data!D61="","",-Data!D61)</f>
+        <v>166609</v>
+      </c>
+      <c r="I15" s="274">
+        <f>IF(Data!E61="","",-Data!E61)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="274">
+        <f>IF(Data!F61="","",-Data!F61)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="274">
+        <f>IF(Data!G61="","",-Data!G61)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="274">
+        <f>IF(Data!H61="","",-Data!H61)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="274">
+        <f>IF(Data!I61="","",-Data!I61)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="274">
+        <f>IF(Data!J61="","",-Data!J61)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="274">
+        <f>IF(Data!K61="","",-Data!K61)</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="274">
+        <f>IF(Data!L61="","",-Data!L61)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="274" t="str">
+        <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
-      <c r="B16" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="277">
-        <f>SUM(C13:C15)</f>
-        <v>347072.73055558326</v>
-      </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="250"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="275">
-        <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>631699.59365518577</v>
-      </c>
-      <c r="H16" s="275">
-        <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1049126.9667862351</v>
-      </c>
-      <c r="I16" s="275">
-        <f t="shared" si="8"/>
-        <v>739157</v>
-      </c>
-      <c r="J16" s="275">
-        <f t="shared" si="8"/>
-        <v>808781</v>
-      </c>
-      <c r="K16" s="275">
-        <f t="shared" si="8"/>
-        <v>691763</v>
-      </c>
-      <c r="L16" s="275">
-        <f t="shared" si="8"/>
-        <v>628986</v>
-      </c>
-      <c r="M16" s="275">
-        <f t="shared" si="8"/>
-        <v>587185</v>
-      </c>
-      <c r="N16" s="275">
-        <f t="shared" si="8"/>
-        <v>358545</v>
-      </c>
-      <c r="O16" s="275">
-        <f t="shared" si="8"/>
-        <v>280151</v>
-      </c>
-      <c r="P16" s="275">
-        <f t="shared" si="8"/>
-        <v>221261</v>
-      </c>
-      <c r="Q16" s="275" t="str">
-        <f t="shared" si="8"/>
+      <c r="B16" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="274">
+        <f>-C4*C82</f>
+        <v>-173178.99999999997</v>
+      </c>
+      <c r="E16" s="242"/>
+      <c r="G16" s="274">
+        <f>Data!C62</f>
+        <v>-173179</v>
+      </c>
+      <c r="H16" s="274">
+        <f>Data!D62</f>
+        <v>-166609</v>
+      </c>
+      <c r="I16" s="274">
+        <f>Data!E62</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="274">
+        <f>Data!F62</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="274">
+        <f>Data!G62</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="274">
+        <f>Data!H62</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="274">
+        <f>Data!I62</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="274">
+        <f>Data!J62</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="274">
+        <f>Data!K62</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="274">
+        <f>Data!L62</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="274" t="str">
+        <f>Data!M62</f>
         <v/>
       </c>
     </row>
@@ -11720,18 +11717,18 @@
         <v>63</v>
       </c>
       <c r="C19" s="275">
-        <f>C16+C17</f>
+        <f>C14+C17</f>
         <v>347072.73055558326</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="239"/>
       <c r="F19" s="26"/>
       <c r="G19" s="279">
-        <f>IF(G$4="","",G16+G17)</f>
+        <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
         <v>631699.59365518577</v>
       </c>
       <c r="H19" s="279">
-        <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
+        <f t="shared" si="9"/>
         <v>1049126.9667862351</v>
       </c>
       <c r="I19" s="279">
@@ -12459,7 +12456,7 @@
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
-        <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
+        <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
         <v>0.29294588222251955</v>
       </c>
       <c r="H41" s="6">
@@ -13389,54 +13386,54 @@
         <v>43</v>
       </c>
       <c r="C71" s="74">
-        <f>ABS(C5/C$4)</f>
+        <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
         <v>0.24487456943110034</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="239"/>
       <c r="F71" s="26"/>
       <c r="G71" s="6">
-        <f t="shared" ref="G71:Q71" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G71:Q71" si="23">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.24487456943110031</v>
       </c>
       <c r="H71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.1565325192378014</v>
       </c>
       <c r="I71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.24075093961851626</v>
       </c>
       <c r="J71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.24482511324901712</v>
       </c>
       <c r="K71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.23535761784313861</v>
       </c>
       <c r="L71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2302361321406223</v>
       </c>
       <c r="M71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.22298808392665412</v>
       </c>
       <c r="N71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.3676841717618643</v>
       </c>
       <c r="O71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.38087650030962683</v>
       </c>
       <c r="P71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.40940376908913678</v>
       </c>
       <c r="Q71" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -13446,54 +13443,54 @@
         <v>45</v>
       </c>
       <c r="C72" s="75">
-        <f>ABS(C6/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.75512543056889958</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="239"/>
       <c r="F72" s="26"/>
       <c r="G72" s="62">
-        <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G72:Q72" si="24">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.75512543056889969</v>
       </c>
       <c r="H72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.84346748076219857</v>
       </c>
       <c r="I72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.75924906038148376</v>
       </c>
       <c r="J72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.75517488675098288</v>
       </c>
       <c r="K72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.76464238215686142</v>
       </c>
       <c r="L72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.76976386785937767</v>
       </c>
       <c r="M72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.77701191607334585</v>
       </c>
       <c r="N72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.6323158282381357</v>
       </c>
       <c r="O72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.61912349969037317</v>
       </c>
       <c r="P72" s="62">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.59059623091086322</v>
       </c>
       <c r="Q72" s="62" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -13503,54 +13500,54 @@
         <v>42</v>
       </c>
       <c r="C73" s="74">
-        <f>ABS(C7/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.33469056113755186</v>
       </c>
       <c r="D73" s="26"/>
       <c r="E73" s="239"/>
       <c r="F73" s="26"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="25">IF(G$4="","",ABS(G7/G$4))</f>
         <v>0.23428339279628627</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.19267671703774958</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.21349164174678328</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.20191173283894734</v>
       </c>
       <c r="K73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.20385598802031346</v>
       </c>
       <c r="L73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.22486266423282722</v>
       </c>
       <c r="M73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.24295539451062467</v>
       </c>
       <c r="N73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.1982767491104841</v>
       </c>
       <c r="O73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.21999203253251082</v>
       </c>
       <c r="P73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.22576176035235929</v>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -13560,513 +13557,513 @@
         <v>127</v>
       </c>
       <c r="C74" s="75">
-        <f>ABS(C8/C$4)</f>
+        <f t="shared" si="22"/>
         <v>0.42043486943134772</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="239"/>
       <c r="F74" s="26"/>
       <c r="G74" s="62">
-        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="26">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.5208420377726134</v>
       </c>
       <c r="H74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.650790763724449</v>
       </c>
       <c r="I74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.5457574186347004</v>
       </c>
       <c r="J74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.55326315391203551</v>
       </c>
       <c r="K74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.56078639413654796</v>
       </c>
       <c r="L74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.54490120362655048</v>
       </c>
       <c r="M74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.53405652156272121</v>
       </c>
       <c r="N74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.43403907912765161</v>
       </c>
       <c r="O74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.39913146715786235</v>
       </c>
       <c r="P74" s="62">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.36483447055850393</v>
       </c>
       <c r="Q74" s="62" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
-      <c r="B75" s="2" t="s">
-        <v>62</v>
+      <c r="B75" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="C75" s="74">
-        <f>ABS(C9/C$4)</f>
-        <v>0.11908566873611129</v>
+        <f t="shared" si="22"/>
+        <v>1.9240306337583624E-3</v>
       </c>
       <c r="D75" s="26"/>
       <c r="E75" s="239"/>
       <c r="F75" s="26"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",G9/G$4)</f>
-        <v>8.3359968115277905E-2</v>
+        <f t="shared" ref="G75:Q75" si="27">IF(G$4="","",G9/G$4)</f>
+        <v>-1.3468214436308534E-3</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="26"/>
-        <v>6.3396941205747723E-2</v>
+        <f t="shared" si="27"/>
+        <v>-7.0151432879926364E-3</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>-3.4108083067710556E-3</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>-4.9775393748860627E-3</v>
       </c>
       <c r="K75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>2.1135650188080867E-6</v>
       </c>
       <c r="L75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>-9.5105626686638853E-5</v>
       </c>
       <c r="M75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>2.6942718967132588E-4</v>
       </c>
       <c r="O75" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>3.825962111142227E-4</v>
       </c>
       <c r="P75" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="85">
-        <f>MAX(AVERAGE(G76:J76),C75)</f>
-        <v>0.11908566873611129</v>
+        <v>65</v>
+      </c>
+      <c r="C76" s="74">
+        <f t="shared" si="22"/>
+        <v>3.0612544030958326E-3</v>
       </c>
       <c r="D76" s="26"/>
-      <c r="E76" s="240"/>
+      <c r="E76" s="239"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
-        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",-G10/G$4)</f>
-        <v>8.3359968115277905E-2</v>
+        <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
+        <v>4.8945774527333471E-3</v>
       </c>
       <c r="H76" s="6">
-        <f t="shared" si="27"/>
-        <v>6.3396941205747723E-2</v>
+        <f t="shared" si="28"/>
+        <v>9.2085483598728182E-4</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>2.3061061158781483E-3</v>
       </c>
       <c r="J76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>3.115422847924714E-3</v>
       </c>
       <c r="K76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>5.0329267010367565E-3</v>
       </c>
       <c r="L76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>6.0132693964143015E-3</v>
       </c>
       <c r="M76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>5.022106838313352E-3</v>
       </c>
       <c r="N76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>1.0550308419667373E-2</v>
       </c>
       <c r="O76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>6.5128130287814903E-3</v>
       </c>
       <c r="P76" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>7.0390627820498932E-3</v>
       </c>
       <c r="Q76" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
-      <c r="B77" s="30" t="s">
-        <v>128</v>
+      <c r="B77" s="67" t="s">
+        <v>137</v>
       </c>
       <c r="C77" s="75">
-        <f>ABS(C11/C$4)</f>
-        <v>1.9240306337583624E-3</v>
+        <f>C11/C4</f>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="239"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
-        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G11/G$4)</f>
-        <v>-1.3468214436308534E-3</v>
+        <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
+        <v>0.51460063887624918</v>
       </c>
       <c r="H77" s="62">
-        <f t="shared" si="28"/>
-        <v>-7.0151432879926364E-3</v>
+        <f t="shared" si="29"/>
+        <v>0.64285476560046906</v>
       </c>
       <c r="I77" s="62">
-        <f t="shared" si="28"/>
-        <v>-3.4108083067710556E-3</v>
+        <f t="shared" si="29"/>
+        <v>0.5400405042120513</v>
       </c>
       <c r="J77" s="62">
-        <f t="shared" si="28"/>
-        <v>-4.9775393748860627E-3</v>
+        <f t="shared" si="29"/>
+        <v>0.54517019168922476</v>
       </c>
       <c r="K77" s="62">
-        <f t="shared" si="28"/>
-        <v>2.1135650188080867E-6</v>
+        <f t="shared" si="29"/>
+        <v>0.55575558100053002</v>
       </c>
       <c r="L77" s="62">
-        <f t="shared" si="28"/>
-        <v>-9.5105626686638853E-5</v>
+        <f t="shared" si="29"/>
+        <v>0.53879282860344957</v>
       </c>
       <c r="M77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.52903441472440782</v>
       </c>
       <c r="N77" s="62">
-        <f t="shared" si="28"/>
-        <v>2.6942718967132588E-4</v>
+        <f t="shared" si="29"/>
+        <v>0.42375819789765556</v>
       </c>
       <c r="O77" s="62">
-        <f t="shared" si="28"/>
-        <v>3.825962111142227E-4</v>
+        <f t="shared" si="29"/>
+        <v>0.39300125034019506</v>
       </c>
       <c r="P77" s="62">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.35779540777645402</v>
       </c>
       <c r="Q77" s="62" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>3.0612544030958326E-3</v>
+        <v>0.10386239609862338</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="239"/>
       <c r="F78" s="26"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>4.8945774527333471E-3</v>
+        <f t="shared" ref="G78:Q78" si="30">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>0.15075013814787502</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="29"/>
-        <v>9.2085483598728182E-4</v>
+        <f t="shared" si="30"/>
+        <v>0.17337632118975857</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="29"/>
-        <v>2.3061061158781483E-3</v>
+        <f t="shared" si="30"/>
+        <v>0.12961532050178071</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="29"/>
-        <v>3.115422847924714E-3</v>
+        <f t="shared" si="30"/>
+        <v>0.12450985619008637</v>
       </c>
       <c r="K78" s="6">
-        <f t="shared" si="29"/>
-        <v>5.0329267010367565E-3</v>
+        <f t="shared" si="30"/>
+        <v>0.1177171172875352</v>
       </c>
       <c r="L78" s="6">
-        <f t="shared" si="29"/>
-        <v>6.0132693964143015E-3</v>
+        <f t="shared" si="30"/>
+        <v>0.11420780795580182</v>
       </c>
       <c r="M78" s="6">
-        <f t="shared" si="29"/>
-        <v>5.022106838313352E-3</v>
+        <f t="shared" si="30"/>
+        <v>9.6372613318363304E-2</v>
       </c>
       <c r="N78" s="6">
-        <f t="shared" si="29"/>
-        <v>1.0550308419667373E-2</v>
+        <f t="shared" si="30"/>
+        <v>9.1125284997102637E-2</v>
       </c>
       <c r="O78" s="6">
-        <f t="shared" si="29"/>
-        <v>6.5128130287814903E-3</v>
+        <f t="shared" si="30"/>
+        <v>8.5597422011509439E-2</v>
       </c>
       <c r="P78" s="6">
-        <f t="shared" si="29"/>
-        <v>7.0390627820498932E-3</v>
+        <f t="shared" si="30"/>
+        <v>8.5235026535253985E-2</v>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
-      <c r="B79" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C79" s="75">
+      <c r="B79" s="38" t="str">
+        <f>B13</f>
+        <v>NCI’s Share of Profits</v>
+      </c>
+      <c r="C79" s="238">
         <f>MIN(BS!C62,MAX(G79:K79))</f>
-        <v>0.1338533079637913</v>
+        <v>7.2924369950228912E-2</v>
       </c>
       <c r="D79" s="26"/>
       <c r="E79" s="239"/>
       <c r="F79" s="26"/>
-      <c r="G79" s="62">
-        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>0.51460063887624918</v>
-      </c>
-      <c r="H79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.64285476560046906</v>
-      </c>
-      <c r="I79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.5400405042120513</v>
-      </c>
-      <c r="J79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.54517019168922476</v>
-      </c>
-      <c r="K79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.55575558100053002</v>
-      </c>
-      <c r="L79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.53879282860344957</v>
-      </c>
-      <c r="M79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.52903441472440782</v>
-      </c>
-      <c r="N79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.42375819789765556</v>
-      </c>
-      <c r="O79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.39300125034019506</v>
-      </c>
-      <c r="P79" s="62">
-        <f t="shared" si="30"/>
-        <v>0.35779540777645402</v>
-      </c>
-      <c r="Q79" s="62" t="str">
-        <f t="shared" si="30"/>
+      <c r="G79" s="6">
+        <f t="shared" ref="G79:Q79" si="31">IF(G$4="","",-G13/G$4)</f>
+        <v>5.9780965822119447E-2</v>
+      </c>
+      <c r="H79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.0271675084255164E-2</v>
+      </c>
+      <c r="I79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.0054880536519634E-2</v>
+      </c>
+      <c r="J79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.2924369950228912E-2</v>
+      </c>
+      <c r="K79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.2516944186560156E-2</v>
+      </c>
+      <c r="L79" s="6">
+        <f t="shared" si="31"/>
+        <v>8.4698045038998707E-2</v>
+      </c>
+      <c r="M79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.7072050549294821E-2</v>
+      </c>
+      <c r="N79" s="6">
+        <f t="shared" si="31"/>
+        <v>8.9914893501795282E-2</v>
+      </c>
+      <c r="O79" s="6">
+        <f t="shared" si="31"/>
+        <v>8.6404423916601913E-2</v>
+      </c>
+      <c r="P79" s="6">
+        <f t="shared" si="31"/>
+        <v>7.2859128488393085E-2</v>
+      </c>
+      <c r="Q79" s="6" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
-      <c r="B80" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C80" s="74">
+      <c r="B80" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>0.10386239609862338</v>
+        <v>0.23866281834564124</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="239"/>
       <c r="F80" s="26"/>
-      <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>0.15075013814787502</v>
-      </c>
-      <c r="H80" s="6">
-        <f t="shared" si="31"/>
-        <v>0.17337632118975857</v>
-      </c>
-      <c r="I80" s="6">
-        <f t="shared" si="31"/>
-        <v>0.12961532050178071</v>
-      </c>
-      <c r="J80" s="6">
-        <f t="shared" si="31"/>
-        <v>0.12450985619008637</v>
-      </c>
-      <c r="K80" s="6">
-        <f t="shared" si="31"/>
-        <v>0.1177171172875352</v>
-      </c>
-      <c r="L80" s="6">
-        <f t="shared" si="31"/>
-        <v>0.11420780795580182</v>
-      </c>
-      <c r="M80" s="6">
-        <f t="shared" si="31"/>
-        <v>9.6372613318363304E-2</v>
-      </c>
-      <c r="N80" s="6">
-        <f t="shared" si="31"/>
-        <v>9.1125284997102637E-2</v>
-      </c>
-      <c r="O80" s="6">
-        <f t="shared" si="31"/>
-        <v>8.5597422011509439E-2</v>
-      </c>
-      <c r="P80" s="6">
-        <f t="shared" si="31"/>
-        <v>8.5235026535253985E-2</v>
-      </c>
-      <c r="Q80" s="6" t="str">
-        <f t="shared" si="31"/>
+      <c r="G80" s="62">
+        <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
+        <v>0.30406953490625477</v>
+      </c>
+      <c r="H80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.39920676932645532</v>
+      </c>
+      <c r="I80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.34037030317375089</v>
+      </c>
+      <c r="J80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.34773596554890945</v>
+      </c>
+      <c r="K80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.36552151952643464</v>
+      </c>
+      <c r="L80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.339886975608649</v>
+      </c>
+      <c r="M80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.35558975085674976</v>
+      </c>
+      <c r="N80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.24271801939875765</v>
+      </c>
+      <c r="O80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.22099940441208374</v>
+      </c>
+      <c r="P80" s="62">
+        <f t="shared" si="32"/>
+        <v>0.19970125275280695</v>
+      </c>
+      <c r="Q80" s="62" t="str">
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
-      <c r="B81" s="38" t="str">
-        <f>B15</f>
-        <v>NCI’s Share of Profits</v>
-      </c>
-      <c r="C81" s="238">
-        <f>MIN(BS!C62,MAX(G81:K81))</f>
-        <v>7.2924369950228912E-2</v>
+      <c r="B81" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="74">
+        <f>ABS(C15/C$4)</f>
+        <v>0.11908566873611129</v>
       </c>
       <c r="D81" s="26"/>
       <c r="E81" s="239"/>
       <c r="F81" s="26"/>
       <c r="G81" s="6">
-        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",-G15/G$4)</f>
-        <v>5.9780965822119447E-2</v>
+        <f t="shared" ref="G81:Q81" si="33">IF(G$4="","",G15/G$4)</f>
+        <v>8.3359968115277905E-2</v>
       </c>
       <c r="H81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.0271675084255164E-2</v>
+        <f t="shared" si="33"/>
+        <v>6.3396941205747723E-2</v>
       </c>
       <c r="I81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.0054880536519634E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.2924369950228912E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="K81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.2516944186560156E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="L81" s="6">
-        <f t="shared" si="32"/>
-        <v>8.4698045038998707E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="M81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.7072050549294821E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="N81" s="6">
-        <f t="shared" si="32"/>
-        <v>8.9914893501795282E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="O81" s="6">
-        <f t="shared" si="32"/>
-        <v>8.6404423916601913E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="P81" s="6">
-        <f t="shared" si="32"/>
-        <v>7.2859128488393085E-2</v>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="Q81" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
-      <c r="B82" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="C82" s="75">
+      <c r="B82" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
-        <v>0.34784564323884259</v>
+        <v>0.11908566873611129</v>
       </c>
       <c r="D82" s="26"/>
-      <c r="E82" s="239" t="s">
-        <v>557</v>
+      <c r="E82" s="240" t="s">
+        <v>556</v>
       </c>
       <c r="F82" s="26"/>
-      <c r="G82" s="62">
-        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.30406953490625477</v>
-      </c>
-      <c r="H82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.39920676932645532</v>
-      </c>
-      <c r="I82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.34037030317375089</v>
-      </c>
-      <c r="J82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.34773596554890945</v>
-      </c>
-      <c r="K82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.36552151952643464</v>
-      </c>
-      <c r="L82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.339886975608649</v>
-      </c>
-      <c r="M82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.35558975085674976</v>
-      </c>
-      <c r="N82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.24271801939875765</v>
-      </c>
-      <c r="O82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.22099940441208374</v>
-      </c>
-      <c r="P82" s="62">
-        <f t="shared" si="33"/>
-        <v>0.19970125275280695</v>
-      </c>
-      <c r="Q82" s="62" t="str">
-        <f t="shared" si="33"/>
+      <c r="G82" s="6">
+        <f t="shared" ref="G82:Q82" si="34">IF(G$4="","",-G16/G$4)</f>
+        <v>8.3359968115277905E-2</v>
+      </c>
+      <c r="H82" s="6">
+        <f t="shared" si="34"/>
+        <v>6.3396941205747723E-2</v>
+      </c>
+      <c r="I82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="J82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="L82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="N82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="P82" s="6">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="Q82" s="6" t="str">
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -14133,47 +14130,47 @@
       <c r="E85" s="239"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
-        <f t="shared" ref="G85:Q85" si="34">IF(G$4="","",ABS(G19/G$4))</f>
+        <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
         <v>0.30406953490625477</v>
       </c>
       <c r="H85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.39920676932645532</v>
       </c>
       <c r="I85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.34037030317375089</v>
       </c>
       <c r="J85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.34773596554890945</v>
       </c>
       <c r="K85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.36552151952643464</v>
       </c>
       <c r="L85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.339886975608649</v>
       </c>
       <c r="M85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.35558975085674976</v>
       </c>
       <c r="N85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.24271801939875765</v>
       </c>
       <c r="O85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.22099940441208374</v>
       </c>
       <c r="P85" s="62">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.19970125275280695</v>
       </c>
       <c r="Q85" s="62" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -14256,47 +14253,47 @@
       </c>
       <c r="E89" s="242"/>
       <c r="G89" s="71">
-        <f t="shared" ref="G89:Q89" si="35">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
+        <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
         <v>369322.25678240001</v>
       </c>
       <c r="H89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>369322.25678240001</v>
       </c>
       <c r="I89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="J89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="K89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="P89" s="71">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q89" s="71" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -14311,47 +14308,47 @@
       </c>
       <c r="E90" s="242"/>
       <c r="G90" s="153">
-        <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
+        <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
         <v>0.58464855841587759</v>
       </c>
       <c r="H90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.35202818007217546</v>
       </c>
       <c r="I90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="M90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="P90" s="153">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Q90" s="153" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -14383,51 +14380,51 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5859649122807019E-2</v>
+        <v>5.5664335664335672E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
-        <f t="shared" ref="G92:Q92" si="37">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.5859649122807019E-2</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>5.5664335664335672E-2</v>
       </c>
       <c r="H92" s="22">
-        <f t="shared" si="37"/>
-        <v>5.5859649122807019E-2</v>
+        <f t="shared" si="38"/>
+        <v>5.5664335664335672E-2</v>
       </c>
       <c r="I92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="J92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="K92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="N92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="O92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="P92" s="22">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="Q92" s="22" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -14469,47 +14466,47 @@
       <c r="E95" s="239"/>
       <c r="F95" s="26"/>
       <c r="G95" s="6">
-        <f t="shared" ref="G95:Q95" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
         <v>-0.20948969741201484</v>
       </c>
       <c r="H95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.21016648354735112</v>
       </c>
       <c r="I95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>-6.6307858467105296E-2</v>
       </c>
       <c r="J95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.22895774296618776</v>
       </c>
       <c r="K95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.2675667117337595E-2</v>
       </c>
       <c r="L95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.12067772099419916</v>
       </c>
       <c r="M95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.11785137908811749</v>
       </c>
       <c r="N95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.16530759552086338</v>
       </c>
       <c r="O95" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.14413426477490154</v>
       </c>
       <c r="P95" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q95" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -14519,54 +14516,54 @@
         <v>137</v>
       </c>
       <c r="C96" s="74">
-        <f>C13/G13-1</f>
+        <f>C11/G11-1</f>
         <v>-0.43487301199002137</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="239"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="39">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
         <v>-0.36720216055323363</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.44056100431478673</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-7.5093278064453539E-2</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.20554997775217054</v>
       </c>
       <c r="K96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.4872447035130723E-2</v>
       </c>
       <c r="L96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.14134941402985834</v>
       </c>
       <c r="M96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.39556438794272641</v>
       </c>
       <c r="N96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.25650655372448261</v>
       </c>
       <c r="O96" s="6">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.25671315741014022</v>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -14619,47 +14616,47 @@
       <c r="E100" s="243"/>
       <c r="F100" s="25"/>
       <c r="G100" s="278">
-        <f t="shared" ref="G100:Q100" si="40">IF(G$4="","",G104+G103)</f>
+        <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
         <v>7238279</v>
       </c>
       <c r="H100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8249751</v>
       </c>
       <c r="I100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8275751</v>
       </c>
       <c r="J100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7847134</v>
       </c>
       <c r="K100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>7208409</v>
       </c>
       <c r="L100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6542493</v>
       </c>
       <c r="M100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5772034</v>
       </c>
       <c r="N100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5108414</v>
       </c>
       <c r="O100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4511682</v>
       </c>
       <c r="P100" s="278">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3942836</v>
       </c>
       <c r="Q100" s="278" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -14931,47 +14928,47 @@
       <c r="E107" s="243"/>
       <c r="F107" s="25"/>
       <c r="G107" s="91">
-        <f t="shared" ref="G107:Q107" si="41">IF(G$4="","",G101/G$4)</f>
+        <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
         <v>6.6962248566053942E-2</v>
       </c>
       <c r="H107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>5.246327190453378E-2</v>
       </c>
       <c r="I107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4.989072704047566E-2</v>
       </c>
       <c r="J107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.7200831696654295E-2</v>
       </c>
       <c r="K107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.9843538065570184E-2</v>
       </c>
       <c r="L107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="N107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="O107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="P107" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="Q107" s="91" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -14988,47 +14985,47 @@
       <c r="E108" s="243"/>
       <c r="F108" s="25"/>
       <c r="G108" s="91">
-        <f t="shared" ref="G108:Q108" si="42">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>0.26858979419336082</v>
       </c>
       <c r="H108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.21269095584561662</v>
       </c>
       <c r="I108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.25072779567015685</v>
       </c>
       <c r="J108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.21594833368302657</v>
       </c>
       <c r="K108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.25418736859569985</v>
       </c>
       <c r="L108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P108" s="91">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q108" s="91" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -15238,52 +15235,52 @@
         <v>190</v>
       </c>
       <c r="C116" s="22">
-        <f>C79</f>
-        <v>0.1338533079637913</v>
+        <f>C77</f>
+        <v>0.41544958439449353</v>
       </c>
       <c r="E116" s="242"/>
       <c r="G116" s="22">
-        <f>IF(G4="","",G79)</f>
+        <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
         <v>0.51460063887624918</v>
       </c>
       <c r="H116" s="22">
-        <f t="shared" ref="H116:Q116" si="43">IF(H4="","",H79)</f>
+        <f t="shared" si="44"/>
         <v>0.64285476560046906</v>
       </c>
       <c r="I116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.5400405042120513</v>
       </c>
       <c r="J116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.54517019168922476</v>
       </c>
       <c r="K116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.55575558100053002</v>
       </c>
       <c r="L116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.53879282860344957</v>
       </c>
       <c r="M116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.52903441472440782</v>
       </c>
       <c r="N116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.42375819789765556</v>
       </c>
       <c r="O116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.39300125034019506</v>
       </c>
       <c r="P116" s="22">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.35779540777645402</v>
       </c>
       <c r="Q116" s="22" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -15297,47 +15294,47 @@
       </c>
       <c r="E117" s="242"/>
       <c r="G117" s="40">
-        <f>IF(G4="","",G4/G100)</f>
+        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",G4/G100)</f>
         <v>0.28701352904468036</v>
       </c>
       <c r="H117" s="40">
-        <f t="shared" ref="H117:Q117" si="44">IF(H4="","",H4/H100)</f>
+        <f t="shared" si="45"/>
         <v>0.31855858437424356</v>
       </c>
       <c r="I117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.26240833007179648</v>
       </c>
       <c r="J117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.29639458176705025</v>
       </c>
       <c r="K117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.26254572957777506</v>
       </c>
       <c r="L117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.28285456323759156</v>
       </c>
       <c r="M117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.2860861526456705</v>
       </c>
       <c r="N117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.28917155109198278</v>
       </c>
       <c r="O117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.28097170855570053</v>
       </c>
       <c r="P117" s="40">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.28100585466907574</v>
       </c>
       <c r="Q117" s="40" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -15353,47 +15350,47 @@
       <c r="E118" s="246"/>
       <c r="F118" s="11"/>
       <c r="G118" s="15">
-        <f t="shared" ref="G118:Q118" si="45">IF(G$4="","",G100/G104)</f>
+        <f t="shared" ref="G118:Q118" si="46">IF(G$4="","",G100/G104)</f>
         <v>1.4876341835211095</v>
       </c>
       <c r="H118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.340152941245272</v>
       </c>
       <c r="I118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2588868586268289</v>
       </c>
       <c r="J118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2834689018849186</v>
       </c>
       <c r="K118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.270804362236263</v>
       </c>
       <c r="L118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2723421973105857</v>
       </c>
       <c r="M118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.258836612388563</v>
       </c>
       <c r="N118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2610618475033715</v>
       </c>
       <c r="O118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.2516790104824409</v>
       </c>
       <c r="P118" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.3016784195652749</v>
       </c>
       <c r="Q118" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -15403,54 +15400,54 @@
         <v>191</v>
       </c>
       <c r="C119" s="99">
-        <f>C13/C104</f>
+        <f>C11/C104</f>
         <v>0.12416948697308672</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="245"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
-        <f t="shared" ref="G119:Q119" si="46">IF(G$4="","",G13/G104)</f>
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
         <v>0.21971961985098865</v>
       </c>
       <c r="H119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.27444577184194152</v>
       </c>
       <c r="I119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.17839827535221295</v>
       </c>
       <c r="J119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.20738995263987398</v>
       </c>
       <c r="K119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.18542465869344466</v>
       </c>
       <c r="L119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.19390496386097003</v>
       </c>
       <c r="M119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.19052419156972641</v>
       </c>
       <c r="N119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.15452902490642165</v>
       </c>
       <c r="O119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.13821319105208374</v>
       </c>
       <c r="P119" s="99">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.13087413834086048</v>
       </c>
       <c r="Q119" s="99" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -15524,54 +15521,54 @@
         <v>FCFE per share (HKD)</v>
       </c>
       <c r="C123" s="160">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16307394337009629</v>
+        <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.16356566367254996</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
-        <f t="shared" ref="G123:Q123" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.29680736829349108</v>
+        <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.29770233781401423</v>
       </c>
       <c r="H123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.49293780959360128</v>
+        <f t="shared" si="48"/>
+        <v>0.49442417537230893</v>
       </c>
       <c r="I123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.34729679444034101</v>
+        <f t="shared" si="48"/>
+        <v>0.34834400579289798</v>
       </c>
       <c r="J123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.38000999612295283</v>
+        <f t="shared" si="48"/>
+        <v>0.38115584828282195</v>
       </c>
       <c r="K123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.32502847488751863</v>
+        <f t="shared" si="48"/>
+        <v>0.32600854010624603</v>
       </c>
       <c r="L123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.29553237207772143</v>
+        <f t="shared" si="48"/>
+        <v>0.29642349707525156</v>
       </c>
       <c r="M123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.27589195291859731</v>
+        <f t="shared" si="48"/>
+        <v>0.2767238557458061</v>
       </c>
       <c r="N123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.16846424935786589</v>
+        <f t="shared" si="48"/>
+        <v>0.16897222316370489</v>
       </c>
       <c r="O123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.13163041716341178</v>
+        <f t="shared" si="48"/>
+        <v>0.13202732513780721</v>
       </c>
       <c r="P123" s="160">
-        <f t="shared" si="47"/>
-        <v>0.10396064169677659</v>
+        <f t="shared" si="48"/>
+        <v>0.10427411641334981</v>
       </c>
       <c r="Q123" s="160" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -15582,53 +15579,53 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7218927498279393E-2</v>
+        <v>5.7190791493898586E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
-        <f t="shared" ref="G124" si="48">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10414293624333019</v>
+        <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
+        <v>0.10409172650839658</v>
       </c>
       <c r="H124" s="74">
-        <f t="shared" ref="H124" si="49">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.17296063494512326</v>
+        <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
+        <v>0.17287558579451362</v>
       </c>
       <c r="I124" s="74">
-        <f t="shared" ref="I124" si="50">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12185852436503193</v>
+        <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
+        <v>0.12179860342409021</v>
       </c>
       <c r="J124" s="74">
-        <f t="shared" ref="J124" si="51">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.13333684074489571</v>
+        <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
+        <v>0.13327127562336433</v>
       </c>
       <c r="K124" s="74">
-        <f t="shared" ref="K124" si="52">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11404507890790126</v>
+        <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
+        <v>0.11398900003714897</v>
       </c>
       <c r="L124" s="74">
-        <f t="shared" ref="L124" si="53">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10369556915007769</v>
+        <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
+        <v>0.10364457939694111</v>
       </c>
       <c r="M124" s="74">
-        <f t="shared" ref="M124" si="54">IF(M$4="","",M123/Market_Price)</f>
-        <v>9.6804194006525374E-2</v>
+        <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
+        <v>9.6756592918114032E-2</v>
       </c>
       <c r="N124" s="74">
-        <f t="shared" ref="N124" si="55">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.911026293258452E-2</v>
+        <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
+        <v>5.9081196910386324E-2</v>
       </c>
       <c r="O124" s="74">
-        <f t="shared" ref="O124" si="56">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.6186111285407644E-2</v>
+        <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
+        <v>4.6163400397834689E-2</v>
       </c>
       <c r="P124" s="74">
-        <f t="shared" ref="P124" si="57">IF(P$4="","",P123/Market_Price)</f>
-        <v>3.6477418139219855E-2</v>
+        <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
+        <v>3.6459481263409026E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
-        <f t="shared" ref="Q124" si="58">IF(Q$4="","",Q123/Market_Price)</f>
+        <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15639,43 +15636,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5220399173817815E-2</v>
+        <v>7.4957390785098166E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14760639071219714</v>
+        <v>0.14709028445096567</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1226220100251547</v>
+        <v>0.12219326173835346</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13455783065218924</v>
+        <v>0.13408734872683192</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11454167952805411</v>
+        <v>0.11414118414508888</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11121631740037266</v>
+        <v>0.11082744915771402</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3113920801915398E-2</v>
+        <v>9.2788347652258338E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3213156457422194E-2</v>
+        <v>8.2922201364913725E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7835965663411588E-2</v>
+        <v>6.7598776972280769E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5231472882893935E-2</v>
+        <v>5.5038355844841853E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16366,7 +16363,7 @@
     <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q25">
+  <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -16385,13 +16382,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U102"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="9" width="20.73046875" customWidth="1"/>
-    <col min="10" max="11" width="11.19921875" customWidth="1"/>
-    <col min="12" max="12" width="20.73046875" customWidth="1"/>
-    <col min="13" max="13" width="5.73046875" customWidth="1"/>
+    <col min="2" max="9" width="20.6640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="12" max="12" width="20.6640625" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
@@ -16418,10 +16415,10 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -16437,7 +16434,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16462,10 +16459,10 @@
       </c>
       <c r="C5" s="189">
         <f>Equity_Cost</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16484,20 +16481,20 @@
       </c>
       <c r="J5" s="313"/>
     </row>
-    <row r="6" spans="2:15" ht="13.35" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="137" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="291">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>4627636.4074077774</v>
+        <v>4787210.0766287353</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16508,7 +16505,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16519,14 +16516,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>1560745.9216088001</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16537,10 +16534,10 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I7" s="321">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>-2798</v>
       </c>
       <c r="J7" s="321"/>
@@ -16549,33 +16546,33 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
-        <v>6188382.3290165775</v>
+        <v>6347955.9982375354</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.73332465972800365</v>
+        <v>0.7355358690483047</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="H8" s="322" t="str">
-        <f>Normalized_FCF!B12</f>
+        <f>Normalized_FCF!B10</f>
         <v>Net Interest Income</v>
       </c>
       <c r="I8" s="321">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-4451.7949296527995</v>
       </c>
       <c r="J8" s="321"/>
@@ -16589,19 +16586,20 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0932867000000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
         <v>CNY/HKD</v>
       </c>
       <c r="F9" s="331"/>
-      <c r="H9" s="316" t="s">
-        <v>401</v>
-      </c>
-      <c r="I9" s="314">
-        <f>Normalized_FCF!C41</f>
-        <v>0.25</v>
+      <c r="H9" s="316" t="str">
+        <f>Normalized_FCF!B79</f>
+        <v>NCI’s Share of Profits</v>
+      </c>
+      <c r="I9" s="145">
+        <f>Normalized_FCF!C79</f>
+        <v>7.2924369950228912E-2</v>
       </c>
       <c r="J9" s="314"/>
       <c r="N9" s="312"/>
@@ -16609,40 +16607,45 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6745336.7386280699</v>
+        <v>6940135.8650583215</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
+      <c r="H10" s="316" t="s">
+        <v>401</v>
+      </c>
+      <c r="I10" s="314">
+        <f>Normalized_FCF!C41</f>
+        <v>0.25</v>
+      </c>
       <c r="N10" s="312"/>
       <c r="O10" s="312"/>
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E11" s="315" t="s">
-        <v>412</v>
-      </c>
+      <c r="E11" s="315"/>
       <c r="I11" s="315"/>
       <c r="J11" s="315"/>
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16670,12 +16673,12 @@
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16690,7 +16693,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16698,9 +16701,9 @@
       </c>
       <c r="J15" s="127"/>
     </row>
-    <row r="16" spans="2:15" ht="13.35" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
@@ -16714,7 +16717,7 @@
         <v>1.8613012126595999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.35" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="316" t="s">
         <v>398</v>
       </c>
@@ -16730,19 +16733,19 @@
         <v>0.24487456943110034</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="13.35" customHeight="1">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C18" s="314">
-        <f>Normalized_FCF!C75-Normalized_FCF!C76</f>
+        <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16753,7 +16756,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.8127548716814572</v>
+        <v>3.7172092119488189</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16783,23 +16786,23 @@
         <v>399</v>
       </c>
       <c r="G20" s="122" t="s">
-        <v>425</v>
+        <v>553</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J20" s="122" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K20" s="122" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="L20" s="123" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16835,20 +16838,20 @@
         <v>0</v>
       </c>
       <c r="I21" s="285">
-        <f>(G21+C21*H21)*(1-$I$9)</f>
-        <v>461657.35280235135</v>
+        <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
+        <v>353634.00488893088</v>
       </c>
       <c r="J21" s="307">
         <f>I21/C4-1</f>
-        <v>0.33014585174509259</v>
+        <v>1.8904609194863919E-2</v>
       </c>
       <c r="K21" s="120">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.93023255813953487</v>
+        <v>0.93240093240093236</v>
       </c>
       <c r="L21" s="285">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>429448.70028125704</v>
+        <v>329728.67588711501</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16884,20 +16887,20 @@
         <v>0</v>
       </c>
       <c r="I22" s="285">
-        <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,(G22+C22*H22)*(1-$I$9))</f>
-        <v>470351.39209909958</v>
+        <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
+        <v>360317.40430101112</v>
       </c>
       <c r="J22" s="307">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>1.8832234002066128E-2</v>
+        <v>1.8899198944907436E-2</v>
       </c>
       <c r="K22" s="120">
         <f t="shared" si="3"/>
-        <v>0.86533261222282321</v>
+        <v>0.86937149874212816</v>
       </c>
       <c r="L22" s="285">
         <f t="shared" si="4"/>
-        <v>407010.39878775523</v>
+        <v>313249.68180004339</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16933,20 +16936,20 @@
         <v>0</v>
       </c>
       <c r="I23" s="285">
-        <f t="shared" si="9"/>
-        <v>479207.25365470693</v>
+        <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
+        <v>367125.20190739498</v>
       </c>
       <c r="J23" s="307">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>1.8828181875012895E-2</v>
+        <v>1.8893890567374783E-2</v>
       </c>
       <c r="K23" s="120">
         <f t="shared" si="3"/>
-        <v>0.80496056950960304</v>
+        <v>0.81060279602995633</v>
       </c>
       <c r="L23" s="285">
         <f t="shared" si="4"/>
-        <v>385742.94381502568</v>
+        <v>297592.71515919664</v>
       </c>
       <c r="N23" s="283"/>
       <c r="O23" s="283"/>
@@ -16991,19 +16994,19 @@
       </c>
       <c r="I24" s="285">
         <f t="shared" si="9"/>
-        <v>488227.9494688405</v>
+        <v>374059.71313318203</v>
       </c>
       <c r="J24" s="307">
         <f t="shared" si="10"/>
-        <v>1.8824205487994128E-2</v>
+        <v>1.888868208926775E-2</v>
       </c>
       <c r="K24" s="120">
         <f t="shared" si="3"/>
-        <v>0.7488005297763749</v>
+        <v>0.75580680282513402</v>
       </c>
       <c r="L24" s="285">
         <f t="shared" si="4"/>
-        <v>365585.34721390094</v>
+        <v>282716.87584887713</v>
       </c>
       <c r="N24" s="283"/>
       <c r="O24" s="283"/>
@@ -17048,19 +17051,19 @@
       </c>
       <c r="I25" s="285">
         <f t="shared" si="9"/>
-        <v>497416.54760355293</v>
+        <v>381123.29650050681</v>
       </c>
       <c r="J25" s="307">
         <f t="shared" si="10"/>
-        <v>1.8820303394570193E-2</v>
+        <v>1.8883571577807956E-2</v>
       </c>
       <c r="K25" s="120">
         <f t="shared" si="3"/>
-        <v>0.69655863235011617</v>
+        <v>0.70471496766912267</v>
       </c>
       <c r="L25" s="285">
         <f t="shared" si="4"/>
-        <v>346479.7901070473</v>
+        <v>268583.29157130409</v>
       </c>
       <c r="N25" s="283"/>
       <c r="O25" s="283"/>
@@ -18354,7 +18357,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18385,20 +18388,20 @@
         <v>0</v>
       </c>
       <c r="I51" s="285">
-        <f>(G51+C51*H51)*(1-$I$9)/Equity_Cost</f>
-        <v>6632220.634714039</v>
+        <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
+        <v>6860917.8979800409</v>
       </c>
       <c r="J51" s="424">
-        <f>(G51+C51*H51)*(1-$I$9)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>0</v>
+        <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
+        <v>0.3051328852653632</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.69655863235011617</v>
+        <v>0.70471496766912267</v>
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>4619730.5347606307</v>
+        <v>4834991.5346555095</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18406,12 +18409,12 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="466" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>6553997.7149656173</v>
+        <v>6326862.7749220459</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18435,7 +18438,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>6553997.7149656173</v>
+        <v>6326862.7749220459</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18470,19 +18473,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>3830618.2677422226</v>
+        <v>3630838.2556157489</v>
       </c>
       <c r="C56" s="119">
-        <v>6312534.8411528505</v>
+        <v>6086994.4152860995</v>
       </c>
       <c r="D56" s="119">
-        <v>6593598.4508047383</v>
+        <v>6366213.8999612015</v>
       </c>
       <c r="E56" s="119">
-        <v>6885113.4641138613</v>
+        <v>6655990.1498973938</v>
       </c>
       <c r="F56" s="119">
-        <v>8510136.1520837117</v>
+        <v>8274101.7929545501</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18496,19 +18499,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>2921205.4176215502</v>
+        <v>2540950.1592130046</v>
       </c>
       <c r="C57" s="119">
-        <v>6510862.2946270742</v>
+        <v>5966291.1106500607</v>
       </c>
       <c r="D57" s="119">
-        <v>7018094.3896210985</v>
+        <v>6456665.8272715379</v>
       </c>
       <c r="E57" s="119">
-        <v>7566229.1216981253</v>
+        <v>6987698.7565780096</v>
       </c>
       <c r="F57" s="119">
-        <v>11036586.904876387</v>
+        <v>10370013.444046695</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18522,19 +18525,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>2547153.9935679105</v>
+        <v>2087418.1413647812</v>
       </c>
       <c r="C58" s="285">
-        <v>6656055.8644519309</v>
+        <v>5876890.6976534557</v>
       </c>
       <c r="D58" s="119">
-        <v>7344555.968901623</v>
+        <v>6527043.0589371845</v>
       </c>
       <c r="E58" s="119">
-        <v>8116231.6251595933</v>
+        <v>7258690.687409536</v>
       </c>
       <c r="F58" s="119">
-        <v>13622341.429429997</v>
+        <v>12540240.857644578</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18557,19 +18560,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>2393302.5631444342</v>
+        <v>1898691.1593082014</v>
       </c>
       <c r="C59" s="285">
-        <v>6762350.642856</v>
+        <v>5810675.1630575862</v>
       </c>
       <c r="D59" s="119">
-        <v>7595623.5363405654</v>
+        <v>6581800.927389523</v>
       </c>
       <c r="E59" s="119">
-        <v>8560359.9467529915</v>
+        <v>7480079.6568145631</v>
       </c>
       <c r="F59" s="119">
-        <v>16268791.772409685</v>
+        <v>14787419.084015667</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18592,19 +18595,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>2330021.7917819507</v>
+        <v>1820156.7397865697</v>
       </c>
       <c r="C60" s="285">
-        <v>6840168.0002610078</v>
+        <v>5761631.7987726415</v>
       </c>
       <c r="D60" s="119">
-        <v>7788708.8101379536</v>
+        <v>6624405.9586827243</v>
       </c>
       <c r="E60" s="119">
-        <v>8918994.616231706</v>
+        <v>7660945.1003863513</v>
       </c>
       <c r="F60" s="119">
-        <v>18977362.656208631</v>
+        <v>17114276.605691038</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18627,19 +18630,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>2303993.7203288055</v>
+        <v>1787476.436300603</v>
       </c>
       <c r="C61" s="285">
-        <v>6897137.3190217018</v>
+        <v>5725307.2173120286</v>
       </c>
       <c r="D61" s="119">
-        <v>7937202.3943062043</v>
+        <v>6657555.3259389494</v>
       </c>
       <c r="E61" s="119">
-        <v>9208592.9595453255</v>
+        <v>7808704.533777874</v>
       </c>
       <c r="F61" s="119">
-        <v>21749512.24595052</v>
+        <v>19523638.650338739</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18736,23 +18739,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18768,23 +18771,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.5331607501817044</v>
+        <v>2.4466483151826011</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.6993022735845349</v>
+        <v>3.6041659677414901</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.831361485180897</v>
+        <v>3.7357542957789076</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.968331343618944</v>
+        <v>3.8723177318099768</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>4.7318567792500152</v>
+        <v>4.6348884597644684</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18800,23 +18803,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>2.1058683513141241</v>
+        <v>1.9330145602875946</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.7924874681252261</v>
+        <v>3.5472818786381484</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>4.0308131291535103</v>
+        <v>3.7783817574561569</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>4.2883571088111019</v>
+        <v>4.0286427139275878</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>5.9189229204842633</v>
+        <v>5.6226329583343846</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18832,23 +18835,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.9301183272601357</v>
+        <v>1.71927761420904</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.8607074286661165</v>
+        <v>3.5051499662260679</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>4.1842028149605275</v>
+        <v>3.8115485769478568</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>4.5467786706529427</v>
+        <v>4.1563536261199987</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>7.1338532500178751</v>
+        <v>6.6454003957451757</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18864,23 +18867,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.8578304254934821</v>
+        <v>1.6303358698559551</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.9106505879752747</v>
+        <v>3.4739444380813791</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>4.3021682287487737</v>
+        <v>3.8373544277283647</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>4.7554546926747285</v>
+        <v>4.2606880509321945</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>8.3773018282798493</v>
+        <v>7.7044325974353232</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18896,23 +18899,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.8280976230659836</v>
+        <v>1.5933247960397221</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.9472134816211133</v>
+        <v>3.4508316731713835</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>4.3928903576651859</v>
+        <v>3.8574329865022188</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.9239610737076198</v>
+        <v>4.3459248722344439</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>9.6499380685614362</v>
+        <v>8.801015420854073</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18928,23 +18931,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.8158681971373358</v>
+        <v>1.5779234836976495</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.9739808149305986</v>
+        <v>3.4337129146197625</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>4.4626608472588574</v>
+        <v>3.8730553554705618</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>5.0600303746924622</v>
+        <v>4.4155597575447247</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>10.952447097396263</v>
+        <v>9.9364803167259215</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18967,7 +18970,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18991,7 +18994,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>4.7318567792500152</v>
+        <v>4.6348884597644684</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -19019,7 +19022,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.968331343618944</v>
+        <v>3.8723177318099768</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19047,7 +19050,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.831361485180897</v>
+        <v>3.7357542957789076</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19075,7 +19078,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.6993022735845349</v>
+        <v>3.6041659677414901</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19103,7 +19106,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.5331607501817044</v>
+        <v>2.4466483151826011</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19226,11 +19229,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="7" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
@@ -19383,7 +19386,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19413,35 +19416,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C21" s="154" t="s">
         <v>382</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19452,7 +19455,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.968331343618944</v>
+        <v>3.8723177318099768</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19465,7 +19468,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19476,7 +19479,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.831361485180897</v>
+        <v>3.7357542957789076</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19488,7 +19491,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19499,7 +19502,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.6993022735845349</v>
+        <v>3.6041659677414901</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19511,11 +19514,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.832343614549234</v>
+        <v>3.736749317377638</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19525,33 +19528,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C28" s="154" t="s">
         <v>382</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C29" s="333">
         <v>0.08</v>
@@ -19562,7 +19565,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>4.7318567792500152</v>
+        <v>4.6348884597644684</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19574,7 +19577,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C30" s="333">
         <v>-0.1</v>
@@ -19585,7 +19588,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.5331607501817044</v>
+        <v>2.4466483151826011</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19601,12 +19604,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19617,7 +19620,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
@@ -19630,62 +19633,62 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20873884600524042</v>
+        <v>0.19236735001465252</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.19641531968495621</v>
+        <v>0.1652240082412598</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.8123601295658958</v>
+        <v>3.7171512243872273</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19773,7 +19776,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.8127548716814572</v>
+        <v>3.7172092119488189</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19836,7 +19839,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.22558241189177669</v>
+        <v>0.23205797163039402</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19879,13 +19882,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19898,10 +19901,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19914,11 +19917,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.0918299750704499</v>
+        <v>2.0395891491836635</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>2.2971084387192842</v>
+        <v>2.2448676128324978</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19926,7 +19929,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.3974576481102664</v>
+        <v>0.39607848125614953</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19939,11 +19942,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.4399104829221732</v>
+        <v>2.3789767836078255</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.6691584829221733</v>
+        <v>2.6082247836078256</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19951,12 +19954,12 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.29986717093641835</v>
+        <v>0.29832696434410155</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19969,10 +19972,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -19985,11 +19988,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>3.0533499674189768</v>
+        <v>2.9770963875772463</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>3.3233281305004532</v>
+        <v>3.2470745506587226</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19997,7 +20000,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.12836564574768028</v>
+        <v>0.12647516846209983</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20006,23 +20009,23 @@
       </c>
       <c r="C67" s="120">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
-        <v>0.28585397512168731</v>
+        <v>0.28684217103797521</v>
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>3.2989595496513973</v>
+        <v>3.2315853309966602</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.5848135247730846</v>
+        <v>3.5184275020346356</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>5.9686545095287591E-2</v>
+        <v>5.346129612613526E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20043,10 +20046,10 @@
   <dimension ref="A2:J167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="352" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="352" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="352" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="352" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="352" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="352" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="352" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="352" customWidth="1"/>
     <col min="7" max="16384" width="9" style="352"/>
   </cols>
   <sheetData>
@@ -20066,7 +20069,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -20075,7 +20078,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -20083,7 +20086,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -20099,7 +20102,7 @@
         <v>1448.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
@@ -20133,14 +20136,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.20873884600524042</v>
+        <v>0.19236735001465252</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20158,7 +20161,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6611.6107526999995</v>
+        <v>6634.8093869200002</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20166,14 +20169,14 @@
       <c r="D11" s="358"/>
       <c r="E11" s="358"/>
     </row>
-    <row r="12" spans="1:10" ht="24.6" customHeight="1">
-      <c r="B12" s="469" t="s">
-        <v>507</v>
-      </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="472" t="s">
+        <v>505</v>
+      </c>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20211,12 +20214,12 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0900000000000001</v>
+        <v>1.0932867000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
@@ -20237,7 +20240,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.8123601295658958</v>
+        <v>3.7171512243872273</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>365</v>
@@ -20289,10 +20292,10 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>2.2971084387192842</v>
+        <v>2.2448676128324978</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20305,10 +20308,10 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.6691584829221733</v>
+        <v>2.6082247836078256</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20321,10 +20324,10 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>3.3233281305004532</v>
+        <v>3.2470745506587226</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20337,14 +20340,14 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.5848135247730846</v>
+        <v>3.5184275020346356</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="13.9">
@@ -20358,22 +20361,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
-        <v>508</v>
-      </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B30" s="470" t="s">
-        <v>509</v>
-      </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="B29" s="472" t="s">
+        <v>506</v>
+      </c>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="475" t="s">
+        <v>507</v>
+      </c>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20386,7 +20389,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="468" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C33" s="468"/>
       <c r="D33" s="468"/>
@@ -20410,9 +20413,9 @@
       <c r="B35" s="381"/>
       <c r="C35" s="383"/>
     </row>
-    <row r="36" spans="2:6" ht="24.6" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="468" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C36" s="468"/>
       <c r="D36" s="468"/>
@@ -20424,7 +20427,7 @@
         <v>199</v>
       </c>
       <c r="C37" s="382">
-        <f>Normalized_FCF!C9</f>
+        <f>Normalized_FCF!C15</f>
         <v>173178.99999999997</v>
       </c>
       <c r="D37" s="352" t="str">
@@ -20437,7 +20440,7 @@
         <v>200</v>
       </c>
       <c r="C38" s="382">
-        <f>Normalized_FCF!C10</f>
+        <f>Normalized_FCF!C16</f>
         <v>-173178.99999999997</v>
       </c>
       <c r="D38" s="352" t="str">
@@ -20447,7 +20450,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="468" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C40" s="468"/>
       <c r="D40" s="468"/>
@@ -20459,7 +20462,7 @@
         <v>202</v>
       </c>
       <c r="C41" s="382">
-        <f>Normalized_FCF!C11</f>
+        <f>Normalized_FCF!C9</f>
         <v>-2798</v>
       </c>
       <c r="D41" s="352" t="str">
@@ -20469,7 +20472,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="468" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C43" s="468"/>
       <c r="D43" s="468"/>
@@ -20511,7 +20514,7 @@
         <v>203</v>
       </c>
       <c r="C46" s="382">
-        <f>Normalized_FCF!C12</f>
+        <f>Normalized_FCF!C10</f>
         <v>-4451.7949296527995</v>
       </c>
       <c r="D46" s="352" t="str">
@@ -20521,7 +20524,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20529,7 +20532,7 @@
         <v>223</v>
       </c>
       <c r="C49" s="382">
-        <f>Normalized_FCF!C15</f>
+        <f>Normalized_FCF!C13</f>
         <v>-106049.44824717694</v>
       </c>
       <c r="D49" s="352" t="str">
@@ -20539,7 +20542,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="468" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C51" s="468"/>
       <c r="D51" s="468"/>
@@ -20548,10 +20551,10 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C52" s="382">
-        <f>Normalized_FCF!C14</f>
+        <f>Normalized_FCF!C12</f>
         <v>-151040.72626758672</v>
       </c>
       <c r="D52" s="352" t="str">
@@ -20561,12 +20564,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="468" t="s">
-        <v>516</v>
-      </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+        <v>514</v>
+      </c>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20582,22 +20585,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
-        <v>517</v>
-      </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="B57" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
-        <v>518</v>
-      </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="B58" s="472" t="s">
+        <v>516</v>
+      </c>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20631,7 +20634,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.7218927498279393E-2</v>
+        <v>5.7190791493898586E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20641,7 +20644,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>5.5859649122807019E-2</v>
+        <v>5.5664335664335672E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>376</v>
@@ -20682,7 +20685,7 @@
       </c>
       <c r="C67" s="392">
         <f>Normalized_FCF!C116</f>
-        <v>0.1338533079637913</v>
+        <v>0.41544958439449353</v>
       </c>
       <c r="D67" s="392">
         <f>Normalized_FCF!G116</f>
@@ -20719,7 +20722,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20732,22 +20735,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
-        <v>519</v>
-      </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="B73" s="472" t="s">
+        <v>517</v>
+      </c>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
-        <v>488</v>
-      </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="B74" s="475" t="s">
+        <v>486</v>
+      </c>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20755,13 +20758,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
-        <v>520</v>
-      </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="B77" s="472" t="s">
+        <v>518</v>
+      </c>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20782,7 +20785,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.333836664975874E-2</v>
+        <v>-6.3529352163215411E-2</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20809,7 +20812,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20827,7 +20830,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20844,7 +20847,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.70843074207219081</v>
+        <v>0.71056688823729974</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20853,7 +20856,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20875,7 +20878,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8232284305571493E-2</v>
+        <v>8.8498332974220231E-2</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20884,11 +20887,11 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>0.73332465972800365</v>
+        <v>0.7355358690483047</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20897,7 +20900,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20910,33 +20913,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
-        <v>523</v>
-      </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="B96" s="472" t="s">
+        <v>521</v>
+      </c>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
-        <v>524</v>
-      </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="B97" s="475" t="s">
+        <v>522</v>
+      </c>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
-        <v>525</v>
-      </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="B98" s="475" t="s">
+        <v>523</v>
+      </c>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20954,7 +20957,7 @@
       </c>
       <c r="C101" s="377">
         <f>E25+C103</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -20964,7 +20967,7 @@
       </c>
       <c r="C102" s="392">
         <f>E25</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -20980,7 +20983,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20999,23 +21002,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
-        <v>526</v>
-      </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="B107" s="472" t="s">
+        <v>524</v>
+      </c>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
-        <v>545</v>
-      </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="B108" s="472" t="s">
+        <v>543</v>
+      </c>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21023,17 +21026,17 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>0.40638898525639144</v>
+        <v>0.40761437853881549</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -21047,7 +21050,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.907643904662621</v>
+        <v>2.991613988669684</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21059,13 +21062,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
-        <v>527</v>
-      </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="B114" s="472" t="s">
+        <v>525</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21073,7 +21076,7 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21110,7 +21113,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.73 HKD</v>
+        <v>4.63 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21133,7 +21136,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.97 HKD</v>
+        <v>3.87 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21155,7 +21158,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.83 HKD</v>
+        <v>3.74 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21177,7 +21180,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.7 HKD</v>
+        <v>3.6 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21199,7 +21202,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.53 HKD</v>
+        <v>2.45 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21208,7 +21211,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="468" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C124" s="468"/>
       <c r="D124" s="468"/>
@@ -21221,7 +21224,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.8123601295658958</v>
+        <v>3.7171512243872273</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21229,17 +21232,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
-        <v>529</v>
-      </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="B127" s="470" t="s">
+        <v>527</v>
+      </c>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21248,22 +21251,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
-        <v>530</v>
-      </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B132" s="469" t="s">
-        <v>531</v>
-      </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="B131" s="471" t="s">
+        <v>528</v>
+      </c>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="472" t="s">
+        <v>529</v>
+      </c>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21294,28 +21297,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21328,11 +21331,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>2.0918299750704499</v>
+        <v>2.0395891491836635</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>2.2971084387192842</v>
+        <v>2.2448676128324978</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21349,11 +21352,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.4399104829221732</v>
+        <v>2.3789767836078255</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.6691584829221733</v>
+        <v>2.6082247836078256</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21362,21 +21365,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21389,11 +21392,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>3.0533499674189768</v>
+        <v>2.9770963875772463</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>3.3233281305004532</v>
+        <v>3.2470745506587226</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21406,24 +21409,24 @@
       </c>
       <c r="C145" s="418">
         <f>Scenarios!C67</f>
-        <v>0.28585397512168731</v>
+        <v>0.28684217103797521</v>
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>3.2989595496513973</v>
+        <v>3.2315853309966602</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.5848135247730846</v>
+        <v>3.5184275020346356</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
-        <v>7.4999999999999997E-2</v>
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21432,13 +21435,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
-        <v>532</v>
-      </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="B149" s="473" t="s">
+        <v>530</v>
+      </c>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21446,13 +21449,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
-        <v>533</v>
-      </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="B152" s="474" t="s">
+        <v>531</v>
+      </c>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21471,12 +21474,12 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" ht="24.6" customHeight="1">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="468" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C158" s="468"/>
       <c r="D158" s="468"/>
@@ -21485,30 +21488,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21528,15 +21531,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21551,12 +21551,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21578,7 +21581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B02FF19-DDA5-42CE-8835-37E1F78886A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEBD1D6-843C-45EB-98C9-9C3413DFFADA}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3213AE-84E2-4C66-A74A-64B020FB4FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D711203-465A-4991-9C6C-03C5488DB09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="556">
   <si>
     <t>Sales</t>
   </si>
@@ -1793,9 +1793,6 @@
   </si>
   <si>
     <t>报告货币:</t>
-  </si>
-  <si>
-    <t>估值输出</t>
   </si>
   <si>
     <t>目标价格</t>
@@ -5050,7 +5047,7 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{07C6F35C-38E6-4C10-90D6-CF6B1E223929}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{887CAECA-5945-42F9-B8D2-0BD44543E946}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5155,7 +5152,7 @@
         </row>
         <row r="8">
           <cell r="C8">
-            <v>2.85</v>
+            <v>2.86</v>
           </cell>
         </row>
         <row r="9">
@@ -5165,7 +5162,7 @@
         </row>
         <row r="16">
           <cell r="E16">
-            <v>1.0900000000000001</v>
+            <v>1.0932867000000002</v>
           </cell>
         </row>
         <row r="17">
@@ -5183,7 +5180,7 @@
         </row>
         <row r="101">
           <cell r="C101">
-            <v>7.4999999999999997E-2</v>
+            <v>7.2499999999999995E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -5443,7 +5440,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5451,13 +5448,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>325</v>
@@ -5465,16 +5462,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5482,14 +5479,14 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>309</v>
@@ -5499,35 +5496,35 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C9" s="48">
         <v>2319863422</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E9" s="311">
         <f>Scenarios!F34</f>
-        <v>0.19236735001465252</v>
+        <v>0.10536763573195662</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6634.8093869200002</v>
+        <v>6681.2066553599998</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5536,7 +5533,7 @@
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
       <c r="B12" s="460" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C12" s="460"/>
       <c r="D12" s="460"/>
@@ -5555,10 +5552,10 @@
         <v>320</v>
       </c>
       <c r="C15" s="427" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E15" s="260" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5570,18 +5567,18 @@
         <v>321</v>
       </c>
       <c r="C16" s="427" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5590,7 +5587,7 @@
         <v>275</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5600,10 +5597,10 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.7171512243872273</v>
+        <v>3.1837177895497697</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E18" s="428">
         <v>6</v>
@@ -5618,7 +5615,7 @@
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E19" s="429">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5631,7 +5628,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C21" s="261" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5650,10 +5647,10 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>2.2448676128324978</v>
+        <v>1.9521743701233303</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5665,10 +5662,10 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.6082247836078256</v>
+        <v>2.2668273853118528</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E23" s="453">
         <v>0.25</v>
@@ -5680,10 +5677,10 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>3.2470745506587226</v>
+        <v>2.8198434115410738</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E24" s="453">
         <v>0.1174</v>
@@ -5695,10 +5692,10 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.5184275020346356</v>
+        <v>3.0546756773108341</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E25" s="454">
         <v>7.2499999999999995E-2</v>
@@ -5720,7 +5717,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="460" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C29" s="460"/>
       <c r="D29" s="460"/>
@@ -5992,7 +5989,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.7190791493898586E-2</v>
+        <v>5.6784874852264029E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6002,7 +5999,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.5664335664335672E-2</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6080,7 +6077,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="203" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6094,7 +6091,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
       <c r="B73" s="460" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C73" s="460"/>
       <c r="D73" s="460"/>
@@ -6104,7 +6101,7 @@
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
       <c r="B74" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6147,7 +6144,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3529352163215411E-2</v>
+        <v>-6.3519555054392343E-2</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6180,7 +6177,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="192"/>
       <c r="B83" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6218,7 +6215,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71056688823729974</v>
+        <v>0.71045730895003978</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6255,7 +6252,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8498332974220231E-2</v>
+        <v>8.8484685301620306E-2</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6268,11 +6265,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="192"/>
       <c r="B92" s="44" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>0.7355358690483047</v>
+        <v>0.7354224391972678</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6281,7 +6278,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="203" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6294,7 +6291,7 @@
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
       <c r="B96" s="460" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C96" s="460"/>
       <c r="D96" s="460"/>
@@ -6303,7 +6300,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="464" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C97" s="464"/>
       <c r="D97" s="464"/>
@@ -6312,7 +6309,7 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="464" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C98" s="464"/>
       <c r="D98" s="464"/>
@@ -6326,7 +6323,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C101" s="215">
         <f>E25+C103</f>
@@ -6386,16 +6383,16 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>0.40761437853881549</v>
+        <v>0.40755151873797674</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6408,7 +6405,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6417,7 +6414,7 @@
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
       <c r="B114" s="460" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C114" s="460"/>
       <c r="D114" s="460"/>
@@ -6426,7 +6423,7 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6461,7 +6458,7 @@
       </c>
       <c r="E118" s="211" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.63 HKD</v>
+        <v>3.92 HKD</v>
       </c>
       <c r="F118" s="212">
         <f>DCF!F74</f>
@@ -6483,7 +6480,7 @@
       </c>
       <c r="E119" s="211" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.31 HKD</v>
       </c>
       <c r="F119" s="202">
         <f>DCF!F75</f>
@@ -6505,7 +6502,7 @@
       </c>
       <c r="E120" s="211" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.74 HKD</v>
+        <v>3.2 HKD</v>
       </c>
       <c r="F120" s="202">
         <f>DCF!F76</f>
@@ -6527,7 +6524,7 @@
       </c>
       <c r="E121" s="211" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.6 HKD</v>
+        <v>3.09 HKD</v>
       </c>
       <c r="F121" s="202">
         <f>DCF!F77</f>
@@ -6549,7 +6546,7 @@
       </c>
       <c r="E122" s="211" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.45 HKD</v>
+        <v>2.16 HKD</v>
       </c>
       <c r="F122" s="202">
         <f>DCF!F78</f>
@@ -6558,7 +6555,7 @@
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="461" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C124" s="461"/>
       <c r="D124" s="461"/>
@@ -6571,7 +6568,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.7171512243872273</v>
+        <v>3.1837177895497697</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6580,7 +6577,7 @@
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="463" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C127" s="463"/>
       <c r="D127" s="463"/>
@@ -6589,7 +6586,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="203" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6608,7 +6605,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="460" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C132" s="460"/>
       <c r="D132" s="460"/>
@@ -6644,28 +6641,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="193" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C138" s="218"/>
       <c r="D138" s="219"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="349" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6678,11 +6675,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>2.0395891491836635</v>
+        <v>1.7468959064744962</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>2.2448676128324978</v>
+        <v>1.9521743701233303</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6699,11 +6696,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.3789767836078255</v>
+        <v>2.0375793853118527</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.6082247836078256</v>
+        <v>2.2668273853118528</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6719,21 +6716,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="349" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6746,11 +6743,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>2.9770963875772463</v>
+        <v>2.5498652484595974</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>3.2470745506587226</v>
+        <v>2.8198434115410738</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6767,11 +6764,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>3.2315853309966602</v>
+        <v>2.7678335062728587</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.5184275020346356</v>
+        <v>3.0546756773108341</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6780,7 +6777,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="203" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6790,7 +6787,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="459" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C149" s="460"/>
       <c r="D149" s="460"/>
@@ -6833,7 +6830,7 @@
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
       <c r="B158" s="461" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C158" s="461"/>
       <c r="D158" s="461"/>
@@ -7607,7 +7604,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9731,7 +9728,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G10" s="18">
         <v>26801</v>
@@ -10332,11 +10329,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0223389478807432</v>
+        <v>2.0220270751152438</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.40761437853881549</v>
+        <v>0.40755151873797674</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10742,11 +10739,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>147379.42030680002</v>
+        <v>147356.69235240002</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.3529352163215411E-2</v>
+        <v>6.3519555054392343E-2</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10759,11 +10756,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1648418.1329060739</v>
+        <v>1648163.9239257504</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.71056688823729985</v>
+        <v>0.71045730895003978</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10776,11 +10773,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>205304.04557487002</v>
+        <v>205272.38483840998</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>8.8498332974220245E-2</v>
+        <v>8.8484685301620306E-2</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10793,11 +10790,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>2001101.5987877438</v>
+        <v>2000793.0011165603</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>0.86259457337473555</v>
+        <v>0.86246154930605246</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -10918,7 +10915,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10928,7 +10925,7 @@
       <c r="E3" s="242"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11217,7 +11214,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C9" s="308">
         <f>C61</f>
@@ -11608,7 +11605,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C16" s="274">
         <f>-C4*C82</f>
@@ -12311,7 +12308,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="306" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C35" s="284">
         <f>G35</f>
@@ -12379,7 +12376,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="306" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12452,7 +12449,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="239" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -14019,7 +14016,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="240" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -14380,16 +14377,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.5664335664335672E-2</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.5664335664335672E-2</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5664335664335672E-2</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15522,50 +15519,50 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16356566367254996</v>
+        <v>0.16354043957452041</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.29770233781401423</v>
+        <v>0.297656427977047</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.49442417537230893</v>
+        <v>0.49434792829460483</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.34834400579289798</v>
+        <v>0.34829028630707898</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.38115584828282195</v>
+        <v>0.38109706875498128</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.32600854010624603</v>
+        <v>0.32595826505957992</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.29642349707525156</v>
+        <v>0.29637778445329532</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.2767238557458061</v>
+        <v>0.27668118108226292</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>0.16897222316370489</v>
+        <v>0.16894616529907941</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>0.13202732513780721</v>
+        <v>0.13200696468979459</v>
       </c>
       <c r="P123" s="160">
         <f t="shared" si="48"/>
-        <v>0.10427411641334981</v>
+        <v>0.10425803589574423</v>
       </c>
       <c r="Q123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15579,50 +15576,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.7190791493898586E-2</v>
+        <v>5.6784874852264029E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10409172650839658</v>
+        <v>0.1033529263809191</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.17287558579451362</v>
+        <v>0.17164858621340445</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12179860342409021</v>
+        <v>0.12093412718995798</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.13327127562336433</v>
+        <v>0.13232537109547962</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11398900003714897</v>
+        <v>0.11317995314568748</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10364457939694111</v>
+        <v>0.10290895293517199</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>9.6756592918114032E-2</v>
+        <v>9.6069854542452399E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.9081196910386324E-2</v>
+        <v>5.8661862951069239E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.6163400397834689E-2</v>
+        <v>4.5835751628400902E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>3.6459481263409026E-2</v>
+        <v>3.6200706908244527E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15636,43 +15633,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4957390785098166E-2</v>
+        <v>7.4436853349090545E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14709028445096567</v>
+        <v>0.14606882414227843</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12219326173835346</v>
+        <v>0.12134469742072601</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13408734872683192</v>
+        <v>0.1331561865828956</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11414118414508888</v>
+        <v>0.11334853703297022</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11082744915771402</v>
+        <v>0.11005781409411879</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2788347652258338E-2</v>
+        <v>9.2143984126895437E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2922201364913725E-2</v>
+        <v>8.2346352744324045E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7598776972280769E-2</v>
+        <v>6.7129341021084379E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5038355844841853E-2</v>
+        <v>5.4656145040363792E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16415,15 +16412,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C4" s="283">
         <f>Normalized_FCF!C19</f>
@@ -16434,7 +16431,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F4" s="283">
         <f>-BS!G31</f>
@@ -16445,7 +16442,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="316" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I4" s="313">
         <f>Normalized_FCF!C4</f>
@@ -16462,7 +16459,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F5" s="283">
         <f>BS!D66</f>
@@ -16473,7 +16470,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="316" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I5" s="313">
         <f>Normalized_FCF!C7</f>
@@ -16494,7 +16491,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F6" s="292">
         <f>BS!H42</f>
@@ -16505,7 +16502,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="316" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I6" s="313">
         <f>I7+I8</f>
@@ -16516,14 +16513,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="326" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C7" s="283">
         <f>F7</f>
         <v>1560745.9216088001</v>
       </c>
       <c r="E7" s="141" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F7" s="291">
         <f>SUM(F4:F6)</f>
@@ -16534,7 +16531,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="320" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I7" s="321">
         <f>Normalized_FCF!C9</f>
@@ -16546,7 +16543,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="137" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C8" s="291">
         <f>C6+C7</f>
@@ -16557,11 +16554,11 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="141" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.7355358690483047</v>
+        <v>0.7354224391972678</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16586,7 +16583,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16607,18 +16604,18 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6940135.8650583215</v>
+        <v>6939065.5996770188</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="H10" s="316" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I10" s="314">
         <f>Normalized_FCF!C41</f>
@@ -16629,11 +16626,11 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="137" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16645,7 +16642,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16660,25 +16657,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C14" s="317" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F14" s="317" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="140" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C15" s="149">
         <f>Scenarios!C45</f>
@@ -16693,7 +16690,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I15" s="127">
         <f>Terminal_Growth</f>
@@ -16703,14 +16700,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C16" s="148">
         <f>Scenarios!C46</f>
         <v>1.8613012126595999E-2</v>
       </c>
       <c r="E16" s="316" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F16" s="319">
         <f>Scenarios!C41</f>
@@ -16719,33 +16716,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="316" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C17" s="314">
         <f>Normalized_FCF!C32</f>
         <v>0.24487456943110034</v>
       </c>
       <c r="E17" s="316" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F17" s="319">
         <f>Scenarios!C40</f>
         <v>0.24487456943110034</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="316" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C18" s="314">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="316" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F18" s="145">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16756,7 +16753,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.7172092119488189</v>
+        <v>3.1839948734252541</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16768,41 +16765,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="122" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B20" s="122" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="122" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D20" s="122" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="122" t="s">
+        <v>397</v>
+      </c>
+      <c r="F20" s="122" t="s">
         <v>398</v>
       </c>
-      <c r="F20" s="122" t="s">
-        <v>399</v>
-      </c>
       <c r="G20" s="122" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="122" t="s">
+        <v>424</v>
+      </c>
+      <c r="J20" s="122" t="s">
+        <v>536</v>
+      </c>
+      <c r="K20" s="122" t="s">
+        <v>537</v>
+      </c>
+      <c r="L20" s="123" t="s">
         <v>425</v>
-      </c>
-      <c r="J20" s="122" t="s">
-        <v>537</v>
-      </c>
-      <c r="K20" s="122" t="s">
-        <v>538</v>
-      </c>
-      <c r="L20" s="123" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18357,7 +18354,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="323" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B51" s="324">
         <f>C15+1</f>
@@ -18388,12 +18385,12 @@
         <v>0</v>
       </c>
       <c r="I51" s="285">
-        <f>(G51+C51*H51)*(1-$I$10)/Equity_Cost</f>
-        <v>6860917.8979800409</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
+        <v>5256873.055179405</v>
       </c>
       <c r="J51" s="424">
-        <f>(G51+C51*H51)*(1-$I$10)/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>0.3051328852653632</v>
+        <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
+        <v>0</v>
       </c>
       <c r="K51" s="120">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18401,7 +18398,7 @@
       </c>
       <c r="L51" s="285">
         <f>I51*K51</f>
-        <v>4834991.5346555095</v>
+        <v>3704597.1251214365</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18409,12 +18406,12 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="466" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K52" s="466"/>
       <c r="L52" s="325">
         <f>SUM(L21:L51)</f>
-        <v>6326862.7749220459</v>
+        <v>5196468.3653879724</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18438,7 +18435,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="126">
         <f>L52</f>
-        <v>6326862.7749220459</v>
+        <v>5196468.3653879724</v>
       </c>
       <c r="B55" s="124">
         <f>C78</f>
@@ -18473,19 +18470,19 @@
       </c>
       <c r="B56" s="119">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>3630838.2556157489</v>
+        <v>3022147.8593235333</v>
       </c>
       <c r="C56" s="119">
-        <v>6086994.4152860995</v>
+        <v>5003589.5754031707</v>
       </c>
       <c r="D56" s="119">
-        <v>6366213.8999612015</v>
+        <v>5228102.5320490673</v>
       </c>
       <c r="E56" s="119">
-        <v>6655990.1498973938</v>
+        <v>5460984.3145793369</v>
       </c>
       <c r="F56" s="119">
-        <v>8274101.7929545501</v>
+        <v>6759485.3060527015</v>
       </c>
       <c r="G56" s="303"/>
       <c r="H56" s="303"/>
@@ -18499,19 +18496,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="119">
-        <v>2540950.1592130046</v>
+        <v>2287657.5646921531</v>
       </c>
       <c r="C57" s="119">
-        <v>5966291.1106500607</v>
+        <v>5163853.7588301506</v>
       </c>
       <c r="D57" s="119">
-        <v>6456665.8272715379</v>
+        <v>5571144.3156508002</v>
       </c>
       <c r="E57" s="119">
-        <v>6987698.7565780096</v>
+        <v>6011429.4281804338</v>
       </c>
       <c r="F57" s="119">
-        <v>10370013.444046695</v>
+        <v>8801692.4610277433</v>
       </c>
       <c r="G57" s="303"/>
       <c r="H57" s="303"/>
@@ -18525,19 +18522,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="119">
-        <v>2087418.1413647812</v>
+        <v>1982016.2181047595</v>
       </c>
       <c r="C58" s="285">
-        <v>5876890.6976534557</v>
+        <v>5282555.4317473797</v>
       </c>
       <c r="D58" s="119">
-        <v>6527043.0589371845</v>
+        <v>5838052.1836579088</v>
       </c>
       <c r="E58" s="119">
-        <v>7258690.687409536</v>
+        <v>6461119.852689568</v>
       </c>
       <c r="F58" s="119">
-        <v>12540240.857644578</v>
+        <v>10916311.151974525</v>
       </c>
       <c r="G58" s="303"/>
       <c r="H58" s="303"/>
@@ -18560,19 +18557,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="119">
-        <v>1898691.1593082014</v>
+        <v>1854830.5582988143</v>
       </c>
       <c r="C59" s="285">
-        <v>5810675.1630575862</v>
+        <v>5370473.3111640792</v>
       </c>
       <c r="D59" s="119">
-        <v>6581800.927389523</v>
+        <v>6045723.1246614326</v>
       </c>
       <c r="E59" s="119">
-        <v>7480079.6568145631</v>
+        <v>6828497.9488856494</v>
       </c>
       <c r="F59" s="119">
-        <v>14787419.084015667</v>
+        <v>13105908.910070773</v>
       </c>
       <c r="G59" s="303"/>
       <c r="H59" s="303"/>
@@ -18595,19 +18592,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="119">
-        <v>1820156.7397865697</v>
+        <v>1801905.1532746346</v>
       </c>
       <c r="C60" s="285">
-        <v>5761631.7987726415</v>
+        <v>5435590.7887123432</v>
       </c>
       <c r="D60" s="119">
-        <v>6624405.9586827243</v>
+        <v>6207304.0479189698</v>
       </c>
       <c r="E60" s="119">
-        <v>7660945.1003863513</v>
+        <v>7128630.3471060041</v>
       </c>
       <c r="F60" s="119">
-        <v>17114276.605691038</v>
+        <v>15373144.304700494</v>
       </c>
       <c r="G60" s="303"/>
       <c r="H60" s="303"/>
@@ -18630,19 +18627,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="119">
-        <v>1787476.436300603</v>
+        <v>1779881.4557819511</v>
       </c>
       <c r="C61" s="285">
-        <v>5725307.2173120286</v>
+        <v>5483820.8633044679</v>
       </c>
       <c r="D61" s="119">
-        <v>6657555.3259389494</v>
+        <v>6333024.0674585113</v>
       </c>
       <c r="E61" s="119">
-        <v>7808704.533777874</v>
+        <v>7373825.8484007353</v>
       </c>
       <c r="F61" s="119">
-        <v>19523638.650338739</v>
+        <v>17720770.171440102</v>
       </c>
       <c r="G61" s="303"/>
       <c r="H61" s="303"/>
@@ -18739,23 +18736,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18771,23 +18768,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.4466483151826011</v>
+        <v>2.1594564985190621</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.6041659677414901</v>
+        <v>3.0931105159932479</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.7357542957789076</v>
+        <v>3.1989008716955518</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.8723177318099768</v>
+        <v>3.3086346125830368</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>4.6348884597644684</v>
+        <v>3.9204874152897475</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18803,23 +18800,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>1.9330145602875946</v>
+        <v>1.8133651606748227</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.5472818786381484</v>
+        <v>3.1686268925283456</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>3.7783817574561569</v>
+        <v>3.3605419317490162</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>4.0286427139275878</v>
+        <v>3.5680039836536737</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>5.6226329583343846</v>
+        <v>4.8827740671169266</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18835,23 +18832,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.71927761420904</v>
+        <v>1.6693471616432172</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.5051499662260679</v>
+        <v>3.2245590417814416</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>3.8115485769478568</v>
+        <v>3.4863087414603608</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>4.1563536261199987</v>
+        <v>3.7798978123014955</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>6.6454003957451757</v>
+        <v>5.8791809864860944</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18867,23 +18864,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.6303358698559551</v>
+        <v>1.6094173634163622</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.4739444380813791</v>
+        <v>3.2659858880313637</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>3.8373544277283647</v>
+        <v>3.5841631506045313</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>4.2606880509321945</v>
+        <v>3.9530061266475451</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>7.7044325974353232</v>
+        <v>6.9109179923788613</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18899,23 +18896,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.5933247960397221</v>
+        <v>1.5844789478039965</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.4508316731713835</v>
+        <v>3.2966692001002205</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>3.8574329865022188</v>
+        <v>3.6602999740711688</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.3459248722344439</v>
+        <v>4.094428312876178</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>8.801015420854073</v>
+        <v>7.9792378009190337</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18931,23 +18928,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.5779234836976495</v>
+        <v>1.5741013962076951</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.4337129146197625</v>
+        <v>3.3193951791389127</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>3.8730553554705618</v>
+        <v>3.7195391635802428</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>4.4155597575447247</v>
+        <v>4.2099642698476334</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>9.9364803167259215</v>
+        <v>9.0854375463975217</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18970,7 +18967,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G73" s="332"/>
       <c r="H73" s="332"/>
@@ -18994,7 +18991,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>4.6348884597644684</v>
+        <v>3.9204874152897475</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -19022,7 +19019,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.8723177318099768</v>
+        <v>3.3086346125830368</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19050,7 +19047,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.7357542957789076</v>
+        <v>3.1989008716955518</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19078,7 +19075,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.6041659677414901</v>
+        <v>3.0931105159932479</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19106,7 +19103,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.4466483151826011</v>
+        <v>2.1594564985190621</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19386,7 +19383,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19416,35 +19413,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E20" s="328"/>
       <c r="F20" s="328"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="154" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C21" s="154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D21" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E21" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G21" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="310" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C22" s="333">
         <v>0.03</v>
@@ -19455,7 +19452,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.8723177318099768</v>
+        <v>3.3086346125830368</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19468,7 +19465,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="310" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C23" s="333">
         <v>0.02</v>
@@ -19479,7 +19476,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.7357542957789076</v>
+        <v>3.1989008716955518</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19491,7 +19488,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="310" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C24" s="333">
         <v>0.01</v>
@@ -19502,7 +19499,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.6041659677414901</v>
+        <v>3.0931105159932479</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19514,11 +19511,11 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="142" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.736749317377638</v>
+        <v>3.199689548732588</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19528,33 +19525,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="154" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C28" s="154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D28" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E28" s="155" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="155" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G28" s="155" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="310" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C29" s="333">
         <v>0.08</v>
@@ -19565,7 +19562,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>4.6348884597644684</v>
+        <v>3.9204874152897475</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19577,7 +19574,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="323" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C30" s="333">
         <v>-0.1</v>
@@ -19588,7 +19585,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.4466483151826011</v>
+        <v>2.1594564985190621</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19604,12 +19601,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="146" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C33" s="156">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19620,7 +19617,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F33" s="223">
         <f>Holding_Period</f>
@@ -19633,62 +19630,62 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19236735001465252</v>
+        <v>0.10536763573195662</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.1652240082412598</v>
+        <v>8.4113616411952266E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.7171512243872273</v>
+        <v>3.1837177895497697</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F36" s="340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19707,19 +19704,19 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="139">
         <f>DCF!C17</f>
         <v>0.24487456943110034</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C41" s="139">
         <f>DCF!C16</f>
@@ -19776,7 +19773,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.7172092119488189</v>
+        <v>3.1839948734252541</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19839,7 +19836,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.23205797163039402</v>
+        <v>0.27089761289050018</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19882,13 +19879,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E60" s="422"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="154" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>103</v>
@@ -19901,10 +19898,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G61" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19917,11 +19914,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.0395891491836635</v>
+        <v>1.7468959064744962</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>2.2448676128324978</v>
+        <v>1.9521743701233303</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19929,7 +19926,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.39607848125614953</v>
+        <v>0.38682556081724817</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19942,11 +19939,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.3789767836078255</v>
+        <v>2.0375793853118527</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.6082247836078256</v>
+        <v>2.2668273853118528</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19954,12 +19951,12 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.29832696434410155</v>
+        <v>0.28799361779097277</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="154" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>103</v>
@@ -19972,10 +19969,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G65" s="155" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -19988,11 +19985,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>2.9770963875772463</v>
+        <v>2.5498652484595974</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>3.2470745506587226</v>
+        <v>2.8198434115410738</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -20000,7 +19997,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.12647516846209983</v>
+        <v>0.11436936187414026</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20013,11 +20010,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>3.2315853309966602</v>
+        <v>2.7678335062728587</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.5184275020346356</v>
+        <v>3.0546756773108341</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -20025,7 +20022,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>5.346129612613526E-2</v>
+        <v>4.0531894083861042E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20069,7 +20066,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -20078,7 +20075,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -20086,7 +20083,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -20095,14 +20092,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="352" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C5" s="364" t="str">
         <f>Thesis!C5</f>
         <v>1448.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
@@ -20121,7 +20118,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="352" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C7" s="361" t="str">
         <f>Market_currency</f>
@@ -20132,23 +20129,23 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="360" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.19236735001465252</v>
+        <v>0.10536763573195662</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="360" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C9" s="362">
         <f>Common_Shares</f>
@@ -20157,11 +20154,11 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="360" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6634.8093869200002</v>
+        <v>6681.2066553599998</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20171,7 +20168,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
       <c r="B12" s="472" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C12" s="472"/>
       <c r="D12" s="472"/>
@@ -20180,7 +20177,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C14" s="357"/>
       <c r="D14" s="358"/>
@@ -20194,7 +20191,7 @@
         <v>N</v>
       </c>
       <c r="D15" s="360" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E15" s="353" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20210,16 +20207,16 @@
         <v>N</v>
       </c>
       <c r="D16" s="360" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0932867000000002</v>
+        <v>1.0931181000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
@@ -20240,10 +20237,10 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.7171512243872273</v>
+        <v>3.1837177895497697</v>
       </c>
       <c r="D18" s="359" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E18" s="436">
         <f>Thesis!E18</f>
@@ -20259,7 +20256,7 @@
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D19" s="352" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E19" s="437">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20272,14 +20269,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="356" t="s">
-        <v>342</v>
+        <v>499</v>
       </c>
       <c r="C21" s="370" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="371" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E21" s="372">
         <f>Holding_Period</f>
@@ -20288,14 +20285,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="352" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>2.2448676128324978</v>
+        <v>1.9521743701233303</v>
       </c>
       <c r="D22" s="374" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E22" s="375">
         <f>Thesis!E22</f>
@@ -20304,14 +20301,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="352" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.6082247836078256</v>
+        <v>2.2668273853118528</v>
       </c>
       <c r="D23" s="374" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E23" s="377">
         <f>Thesis!E23</f>
@@ -20320,14 +20317,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>3.2470745506587226</v>
+        <v>2.8198434115410738</v>
       </c>
       <c r="D24" s="374" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E24" s="377">
         <f>Thesis!E24</f>
@@ -20336,14 +20333,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="352" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.5184275020346356</v>
+        <v>3.0546756773108341</v>
       </c>
       <c r="D25" s="374" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E25" s="377">
         <f>Thesis!E25</f>
@@ -20352,7 +20349,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="354" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B27" s="354"/>
       <c r="C27" s="354"/>
@@ -20362,7 +20359,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="472" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C29" s="472"/>
       <c r="D29" s="472"/>
@@ -20371,7 +20368,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="475" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C30" s="475"/>
       <c r="D30" s="475"/>
@@ -20380,7 +20377,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C32" s="379">
         <f>scaling_factor</f>
@@ -20389,7 +20386,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="468" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C33" s="468"/>
       <c r="D33" s="468"/>
@@ -20415,7 +20412,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="468" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C36" s="468"/>
       <c r="D36" s="468"/>
@@ -20450,7 +20447,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="468" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C40" s="468"/>
       <c r="D40" s="468"/>
@@ -20472,7 +20469,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="468" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C43" s="468"/>
       <c r="D43" s="468"/>
@@ -20524,7 +20521,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20542,7 +20539,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="468" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C51" s="468"/>
       <c r="D51" s="468"/>
@@ -20551,7 +20548,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="381" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C52" s="382">
         <f>Normalized_FCF!C12</f>
@@ -20564,7 +20561,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="468" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C54" s="474"/>
       <c r="D54" s="474"/>
@@ -20586,7 +20583,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="472" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C57" s="472"/>
       <c r="D57" s="472"/>
@@ -20595,7 +20592,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="472" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C58" s="472"/>
       <c r="D58" s="472"/>
@@ -20604,7 +20601,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C60" s="382">
         <f>Normalized_FCF!G19</f>
@@ -20634,7 +20631,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.7190791493898586E-2</v>
+        <v>5.6784874852264029E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20644,10 +20641,10 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>5.5664335664335672E-2</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="E63" s="381" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F63" s="389">
         <f>Normalized_FCF!C90</f>
@@ -20656,13 +20653,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="378" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C65" s="390" t="s">
         <v>328</v>
       </c>
       <c r="D65" s="390" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20722,7 +20719,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="354" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B71" s="354"/>
       <c r="C71" s="354"/>
@@ -20736,7 +20733,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
       <c r="B73" s="472" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C73" s="472"/>
       <c r="D73" s="472"/>
@@ -20745,7 +20742,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="475" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C74" s="475"/>
       <c r="D74" s="475"/>
@@ -20754,12 +20751,12 @@
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="472" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C77" s="472"/>
       <c r="D77" s="472"/>
@@ -20785,7 +20782,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3529352163215411E-2</v>
+        <v>-6.3519555054392343E-2</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20812,7 +20809,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20830,7 +20827,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="391" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C85" s="399">
         <f>BS!C66</f>
@@ -20847,7 +20844,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71056688823729974</v>
+        <v>0.71045730895003978</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20856,7 +20853,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20878,7 +20875,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8498332974220231E-2</v>
+        <v>8.8484685301620306E-2</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20887,11 +20884,11 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="381" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>0.7355358690483047</v>
+        <v>0.7354224391972678</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20900,7 +20897,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="354" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B94" s="354"/>
       <c r="C94" s="354"/>
@@ -20914,7 +20911,7 @@
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
       <c r="B96" s="472" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C96" s="472"/>
       <c r="D96" s="472"/>
@@ -20924,7 +20921,7 @@
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
       <c r="B97" s="475" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C97" s="475"/>
       <c r="D97" s="475"/>
@@ -20934,7 +20931,7 @@
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
       <c r="B98" s="475" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C98" s="475"/>
       <c r="D98" s="475"/>
@@ -20947,7 +20944,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="394"/>
       <c r="B100" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -20983,7 +20980,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -20996,14 +20993,14 @@
     <row r="106" spans="1:6">
       <c r="A106" s="394"/>
       <c r="B106" s="402" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C106" s="401"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
       <c r="B107" s="472" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C107" s="472"/>
       <c r="D107" s="472"/>
@@ -21013,7 +21010,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
       <c r="B108" s="472" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C108" s="472"/>
       <c r="D108" s="472"/>
@@ -21026,17 +21023,17 @@
     <row r="110" spans="1:6">
       <c r="A110" s="394"/>
       <c r="B110" s="378" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="394"/>
       <c r="B111" s="384" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>0.40761437853881549</v>
+        <v>0.40755151873797674</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -21046,11 +21043,11 @@
     <row r="112" spans="1:6">
       <c r="A112" s="394"/>
       <c r="B112" s="381" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.991613988669684</v>
+        <v>2.9911526402251361</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21063,7 +21060,7 @@
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
       <c r="B114" s="472" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C114" s="472"/>
       <c r="D114" s="472"/>
@@ -21076,25 +21073,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="394"/>
       <c r="B116" s="378" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="394"/>
       <c r="B117" s="351" t="s">
+        <v>380</v>
+      </c>
+      <c r="C117" s="351" t="s">
         <v>381</v>
-      </c>
-      <c r="C117" s="351" t="s">
-        <v>382</v>
       </c>
       <c r="D117" s="351" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="351" t="s">
+        <v>382</v>
+      </c>
+      <c r="F117" s="351" t="s">
         <v>383</v>
-      </c>
-      <c r="F117" s="351" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21113,7 +21110,7 @@
       </c>
       <c r="E118" s="407" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>4.63 HKD</v>
+        <v>3.92 HKD</v>
       </c>
       <c r="F118" s="408">
         <f>DCF!F74</f>
@@ -21136,7 +21133,7 @@
       </c>
       <c r="E119" s="407" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>3.87 HKD</v>
+        <v>3.31 HKD</v>
       </c>
       <c r="F119" s="412">
         <f>DCF!F75</f>
@@ -21158,7 +21155,7 @@
       </c>
       <c r="E120" s="407" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>3.74 HKD</v>
+        <v>3.2 HKD</v>
       </c>
       <c r="F120" s="412">
         <f>DCF!F76</f>
@@ -21180,7 +21177,7 @@
       </c>
       <c r="E121" s="407" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>3.6 HKD</v>
+        <v>3.09 HKD</v>
       </c>
       <c r="F121" s="412">
         <f>DCF!F77</f>
@@ -21202,7 +21199,7 @@
       </c>
       <c r="E122" s="407" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>2.45 HKD</v>
+        <v>2.16 HKD</v>
       </c>
       <c r="F122" s="412">
         <f>DCF!F78</f>
@@ -21211,7 +21208,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="468" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C124" s="468"/>
       <c r="D124" s="468"/>
@@ -21224,7 +21221,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.7171512243872273</v>
+        <v>3.1837177895497697</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21233,7 +21230,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="470" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C127" s="470"/>
       <c r="D127" s="470"/>
@@ -21242,7 +21239,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B129" s="354"/>
       <c r="C129" s="354"/>
@@ -21252,7 +21249,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="471" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C131" s="471"/>
       <c r="D131" s="471"/>
@@ -21261,7 +21258,7 @@
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="472" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C132" s="472"/>
       <c r="D132" s="472"/>
@@ -21270,12 +21267,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="352" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C135" s="414">
         <f>E21</f>
@@ -21284,7 +21281,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="352" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C136" s="415">
         <f>Scenarios!C58</f>
@@ -21297,28 +21294,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="378" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C138" s="416"/>
       <c r="D138" s="416"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="349" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C139" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E139" s="350" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21331,11 +21328,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>2.0395891491836635</v>
+        <v>1.7468959064744962</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>2.2448676128324978</v>
+        <v>1.9521743701233303</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21352,11 +21349,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.3789767836078255</v>
+        <v>2.0375793853118527</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.6082247836078256</v>
+        <v>2.2668273853118528</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21365,21 +21362,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="349" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C143" s="349" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E143" s="350" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21392,11 +21389,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>2.9770963875772463</v>
+        <v>2.5498652484595974</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>3.2470745506587226</v>
+        <v>2.8198434115410738</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21413,11 +21410,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>3.2315853309966602</v>
+        <v>2.7678335062728587</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.5184275020346356</v>
+        <v>3.0546756773108341</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21426,7 +21423,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="354" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B147" s="354"/>
       <c r="C147" s="354"/>
@@ -21436,7 +21433,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="473" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C149" s="472"/>
       <c r="D149" s="472"/>
@@ -21445,12 +21442,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="474" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C152" s="474"/>
       <c r="D152" s="474"/>
@@ -21459,27 +21456,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="421" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="421" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="468" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C158" s="468"/>
       <c r="D158" s="468"/>
@@ -21488,12 +21485,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C161" s="469"/>
       <c r="D161" s="469"/>
@@ -21502,7 +21499,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="469" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C162" s="469"/>
       <c r="D162" s="469"/>
@@ -21511,22 +21508,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="421" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="421" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="421" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -21581,7 +21578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FEBD1D6-843C-45EB-98C9-9C3413DFFADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3014C6F-A00B-4AA1-99CB-6E416F4B862E}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D711203-465A-4991-9C6C-03C5488DB09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44978B2-9208-4A33-857E-F26A7B6B5025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3827,6 +3827,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -4990,30 +4991,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5023,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5032,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5510,13 +5511,6 @@
       <c r="C9" s="48">
         <v>2319863422</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E9" s="311">
-        <f>Scenarios!F34</f>
-        <v>0.10536763573195662</v>
-      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
@@ -5526,19 +5520,26 @@
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>6681.2066553599998</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E10" s="311">
+        <f>Scenarios!F34</f>
+        <v>0.10536763573195662</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5716,22 +5717,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5743,13 +5744,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5769,13 +5770,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5804,13 +5805,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5826,13 +5827,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5896,13 +5897,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5918,7 +5919,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5940,22 +5941,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6090,13 +6091,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6115,13 +6116,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6290,31 +6291,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6364,22 +6365,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6413,13 +6414,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6554,13 +6555,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6595,22 +6596,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6786,13 +6787,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6829,13 +6830,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6843,22 +6844,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6882,6 +6883,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6898,18 +6911,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20167,13 +20168,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20358,22 +20359,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20563,10 +20564,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20582,22 +20583,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20732,22 +20733,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20755,13 +20756,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20910,33 +20911,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20999,23 +21000,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21059,13 +21060,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21229,13 +21230,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21248,22 +21249,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21432,13 +21433,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21446,13 +21447,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21489,22 +21490,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21528,12 +21529,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21548,15 +21552,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44978B2-9208-4A33-857E-F26A7B6B5025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E169711-9B0E-4F55-88D0-FFD613DBB8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4991,30 +4991,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,25 +5024,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5500,7 +5500,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6681.2066553599998</v>
+        <v>6797.1998264599997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>0.10536763573195662</v>
+        <v>9.5641708584119842E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5533,13 +5533,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5574,7 +5574,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.1837177895497697</v>
+        <v>3.18363594800869</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>1.9521743701233303</v>
+        <v>1.9521294639279505</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.2668273853118528</v>
+        <v>2.2667750067255619</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>2.8198434115410738</v>
+        <v>2.8197778639909221</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.0546756773108341</v>
+        <v>3.0546045266076063</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5717,22 +5717,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5770,13 +5770,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5805,13 +5805,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5827,13 +5827,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5897,13 +5897,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5919,7 +5919,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5941,22 +5941,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.6784874852264029E-2</v>
+        <v>5.5814414866273775E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.527777777777778E-2</v>
+        <v>5.4334470989761095E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6091,13 +6091,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6116,13 +6116,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3519555054392343E-2</v>
+        <v>-6.3517922202921837E-2</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71045730895003978</v>
+        <v>0.71043904573549643</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8484685301620306E-2</v>
+        <v>8.8482410689520327E-2</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>0.7354224391972678</v>
+        <v>0.73540353422209503</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6291,31 +6291,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6365,22 +6365,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>0.40755151873797674</v>
+        <v>0.40754104210450359</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6414,13 +6414,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6555,13 +6555,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.1837177895497697</v>
+        <v>3.18363594800869</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6596,22 +6596,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6676,11 +6676,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>1.7468959064744962</v>
+        <v>1.7468510002791164</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>1.9521743701233303</v>
+        <v>1.9521294639279505</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6697,11 +6697,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.0375793853118527</v>
+        <v>2.0375270067255618</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.2668273853118528</v>
+        <v>2.2667750067255619</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6744,11 +6744,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>2.5498652484595974</v>
+        <v>2.5497997009094457</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>2.8198434115410738</v>
+        <v>2.8197778639909221</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6765,11 +6765,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>2.7678335062728587</v>
+        <v>2.7677623555696309</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.0546756773108341</v>
+        <v>3.0546045266076063</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6787,13 +6787,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6830,13 +6830,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6844,22 +6844,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6883,18 +6883,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6911,6 +6899,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10330,11 +10330,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0220270751152438</v>
+        <v>2.0219750963209937</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.40755151873797674</v>
+        <v>0.40754104210450359</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10740,11 +10740,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>147356.69235240002</v>
+        <v>147352.90436000002</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.3519555054392343E-2</v>
+        <v>6.3517922202921837E-2</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10757,11 +10757,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1648163.9239257504</v>
+        <v>1648121.5557623634</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.71045730895003978</v>
+        <v>0.71043904573549654</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10774,11 +10774,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>205272.38483840998</v>
+        <v>205267.108049</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>8.8484685301620306E-2</v>
+        <v>8.8482410689520327E-2</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10791,11 +10791,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>2000793.0011165603</v>
+        <v>2000741.5681713633</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>0.86246154930605246</v>
+        <v>0.86243937862793874</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -14378,16 +14378,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.527777777777778E-2</v>
+        <v>5.4334470989761095E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.527777777777778E-2</v>
+        <v>5.4334470989761095E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.527777777777778E-2</v>
+        <v>5.4334470989761095E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15520,50 +15520,50 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16354043957452041</v>
+        <v>0.16353623555818214</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.297656427977047</v>
+        <v>0.29764877633755249</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.49434792829460483</v>
+        <v>0.49433522044832079</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.34829028630707898</v>
+        <v>0.34828133305944253</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.38109706875498128</v>
+        <v>0.38108727216700783</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.32595826505957992</v>
+        <v>0.32594988588513557</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.29637778445329532</v>
+        <v>0.29637016568296926</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.27668118108226292</v>
+        <v>0.27667406863833904</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>0.16894616529907941</v>
+        <v>0.16894182232164184</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>0.13200696468979459</v>
+        <v>0.13200357128179246</v>
       </c>
       <c r="P123" s="160">
         <f t="shared" si="48"/>
-        <v>0.10425803589574423</v>
+        <v>0.10425535580947663</v>
       </c>
       <c r="Q123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15577,50 +15577,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.6784874852264029E-2</v>
+        <v>5.5814414866273775E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.1033529263809191</v>
+        <v>0.10158661308448889</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.17164858621340445</v>
+        <v>0.16871509230318116</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.12093412718995798</v>
+        <v>0.11886734916704522</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.13232537109547962</v>
+        <v>0.13006391541536103</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11317995314568748</v>
+        <v>0.1112456948413432</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10290895293517199</v>
+        <v>0.10115022719555264</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>9.6069854542452399E-2</v>
+        <v>9.4428009774177146E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.8661862951069239E-2</v>
+        <v>5.765932502445114E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.5835751628400902E-2</v>
+        <v>4.5052413406755108E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>3.6200706908244527E-2</v>
+        <v>3.5582032699480078E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15634,43 +15634,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4436853349090545E-2</v>
+        <v>7.3166599878969535E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14606882414227843</v>
+        <v>0.14357618209206888</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12134469742072601</v>
+        <v>0.11927396879579893</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1331561865828956</v>
+        <v>0.13088389670946735</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11334853703297022</v>
+        <v>0.11141426165698096</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11005781409411879</v>
+        <v>0.10817969439967989</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2143984126895437E-2</v>
+        <v>9.0571561189576405E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2346352744324045E-2</v>
+        <v>8.094112488179292E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7129341021084379E-2</v>
+        <v>6.5983789126526624E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4656145040363792E-2</v>
+        <v>5.3723446319538466E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.7354224391972678</v>
+        <v>0.73540353422209503</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6939065.5996770188</v>
+        <v>6938887.2221134687</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1839948734252541</v>
+        <v>3.1839130247613787</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18737,23 +18737,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18769,23 +18769,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.1594564985190621</v>
+        <v>2.1594009869255677</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.0931105159932479</v>
+        <v>3.0930310036281163</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.1989008716955518</v>
+        <v>3.1988186398539105</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.3086346125830368</v>
+        <v>3.308549559895122</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>3.9204874152897475</v>
+        <v>3.9203866341423401</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18801,23 +18801,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>1.8133651606748227</v>
+        <v>1.8133185458021801</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.1686268925283456</v>
+        <v>3.1685454389180907</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>3.3605419317490162</v>
+        <v>3.3604555447170186</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>3.5680039836536737</v>
+        <v>3.5679122635440712</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>4.8827740671169266</v>
+        <v>4.8826485491593647</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18833,23 +18833,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.6693471616432172</v>
+        <v>1.6693042489375889</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.2245590417814416</v>
+        <v>3.2244761503636949</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>3.4863087414603608</v>
+        <v>3.4862191214315321</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>3.7798978123014955</v>
+        <v>3.7798006451897939</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>5.8791809864860944</v>
+        <v>5.8790298546132256</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18865,23 +18865,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.6094173634163622</v>
+        <v>1.6093759912829102</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.2659858880313637</v>
+        <v>3.2659019316835054</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>3.5841631506045313</v>
+        <v>3.5840710151028574</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>3.9530061266475451</v>
+        <v>3.9529045095650375</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>6.9109179923788613</v>
+        <v>6.9107403383855868</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18897,23 +18897,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.5844789478039965</v>
+        <v>1.5844382167444402</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.2966692001002205</v>
+        <v>3.2965844549985492</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>3.6602999740711688</v>
+        <v>3.6602058813749898</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.094428312876178</v>
+        <v>4.0943230603553467</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>7.9792378009190337</v>
+        <v>7.9790326843975841</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18929,23 +18929,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.5741013962076951</v>
+        <v>1.5740609319163863</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3193951791389127</v>
+        <v>3.3193098498368605</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>3.7195391635802428</v>
+        <v>3.7194435480648687</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>4.2099642698476334</v>
+        <v>4.2098560473271363</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>9.0854375463975217</v>
+        <v>9.0852039935956306</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.9204874152897475</v>
+        <v>3.9203866341423401</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3086346125830368</v>
+        <v>3.308549559895122</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1989008716955518</v>
+        <v>3.1988186398539105</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0931105159932479</v>
+        <v>3.0930310036281163</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19104,7 +19104,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1594564985190621</v>
+        <v>2.1594009869255677</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.3086346125830368</v>
+        <v>3.308549559895122</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.1989008716955518</v>
+        <v>3.1988186398539105</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19500,7 +19500,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.0931105159932479</v>
+        <v>3.0930310036281163</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.199689548732588</v>
+        <v>3.1996072966169939</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>3.9204874152897475</v>
+        <v>3.9203866341423401</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.1594564985190621</v>
+        <v>2.1594009869255677</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10536763573195662</v>
+        <v>9.5641708584119842E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>8.4113616411952266E-2</v>
+        <v>8.4114964645625137E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.1837177895497697</v>
+        <v>3.18363594800869</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.1839948734252541</v>
+        <v>3.1839130247613787</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19915,11 +19915,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>1.7468959064744962</v>
+        <v>1.7468510002791164</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>1.9521743701233303</v>
+        <v>1.9521294639279505</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38682556081724817</v>
+        <v>0.38682390329554661</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19940,11 +19940,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.0375793853118527</v>
+        <v>2.0375270067255618</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.2668273853118528</v>
+        <v>2.2667750067255619</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28799361779097277</v>
+        <v>0.28799176672716265</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19986,11 +19986,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>2.5498652484595974</v>
+        <v>2.5497997009094457</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>2.8198434115410738</v>
+        <v>2.8197778639909221</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.11436936187414026</v>
+        <v>0.11436718212418728</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20011,11 +20011,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>2.7678335062728587</v>
+        <v>2.7677623555696309</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.0546756773108341</v>
+        <v>3.0546045266076063</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>4.0531894083861042E-2</v>
+        <v>4.0529577975707554E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20134,14 +20134,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>535</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>0.10536763573195662</v>
+        <v>9.5641708584119842E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6681.2066553599998</v>
+        <v>6797.1998264599997</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20168,13 +20168,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
+      <c r="B12" s="472" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0931181000000001</v>
+        <v>1.0930900000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.1837177895497697</v>
+        <v>3.18363594800869</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>1.9521743701233303</v>
+        <v>1.9521294639279505</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.2668273853118528</v>
+        <v>2.2667750067255619</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>2.8198434115410738</v>
+        <v>2.8197778639909221</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.0546756773108341</v>
+        <v>3.0546045266076063</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20359,22 +20359,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
+      <c r="B30" s="475" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20564,10 +20564,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20583,22 +20583,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
+      <c r="B58" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.6784874852264029E-2</v>
+        <v>5.5814414866273775E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>5.527777777777778E-2</v>
+        <v>5.4334470989761095E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20733,22 +20733,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
+      <c r="B73" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20756,13 +20756,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
+      <c r="B77" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3519555054392343E-2</v>
+        <v>-6.3517922202921837E-2</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71045730895003978</v>
+        <v>0.71043904573549643</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8484685301620306E-2</v>
+        <v>8.8482410689520327E-2</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>0.7354224391972678</v>
+        <v>0.73540353422209503</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20911,33 +20911,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
+      <c r="B96" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
+      <c r="B97" s="475" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
+      <c r="B98" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -21000,23 +21000,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
+      <c r="B107" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
+      <c r="B108" s="472" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>0.40755151873797674</v>
+        <v>0.40754104210450359</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.9911526402251361</v>
+        <v>2.9910757488177118</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21060,13 +21060,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
+      <c r="B114" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.1837177895497697</v>
+        <v>3.18363594800869</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21230,13 +21230,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="470" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21249,22 +21249,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
+      <c r="B132" s="472" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21329,11 +21329,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>1.7468959064744962</v>
+        <v>1.7468510002791164</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>1.9521743701233303</v>
+        <v>1.9521294639279505</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21350,11 +21350,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.0375793853118527</v>
+        <v>2.0375270067255618</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.2668273853118528</v>
+        <v>2.2667750067255619</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21390,11 +21390,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>2.5498652484595974</v>
+        <v>2.5497997009094457</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>2.8198434115410738</v>
+        <v>2.8197778639909221</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21411,11 +21411,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>2.7678335062728587</v>
+        <v>2.7677623555696309</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.0546756773108341</v>
+        <v>3.0546045266076063</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21433,13 +21433,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="473" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21447,13 +21447,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
+      <c r="B152" s="474" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21490,22 +21490,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21529,15 +21529,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21552,12 +21549,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E169711-9B0E-4F55-88D0-FFD613DBB8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AB1152-C29E-41EE-BFF4-4886BD2332CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4991,30 +4991,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5033,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5500,7 +5500,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6797.1998264599997</v>
+        <v>6820.3984606800004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>534</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>9.5641708584119842E-2</v>
+        <v>9.3762070644753601E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5533,13 +5533,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5574,7 +5574,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.18363594800869</v>
+        <v>3.1838405518613895</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>1.9521294639279505</v>
+        <v>1.9522417294164001</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.2667750067255619</v>
+        <v>2.2669059531912894</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>2.8197778639909221</v>
+        <v>2.8199417328663015</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.0546045266076063</v>
+        <v>3.0547824033656759</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5717,22 +5717,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5744,13 +5744,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5770,13 +5770,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5805,13 +5805,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5827,13 +5827,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5897,13 +5897,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5919,7 +5919,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5941,22 +5941,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.5814414866273775E-2</v>
+        <v>5.5628144761574079E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.4334470989761095E-2</v>
+        <v>5.4149659863945585E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6091,13 +6091,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6116,13 +6116,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3517922202921837E-2</v>
+        <v>-6.3522004331598117E-2</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71043904573549643</v>
+        <v>0.7104847037718548</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8482410689520327E-2</v>
+        <v>8.8488097219770301E-2</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>0.73540353422209503</v>
+        <v>0.73545079666002711</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6291,31 +6291,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6365,22 +6365,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>0.40754104210450359</v>
+        <v>0.40756723368818643</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6414,13 +6414,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6555,13 +6555,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.18363594800869</v>
+        <v>3.1838405518613895</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6596,22 +6596,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6676,11 +6676,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>1.7468510002791164</v>
+        <v>1.746963265767566</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>1.9521294639279505</v>
+        <v>1.9522417294164001</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6697,11 +6697,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.0375270067255618</v>
+        <v>2.0376579531912893</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.2667750067255619</v>
+        <v>2.2669059531912894</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6744,11 +6744,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>2.5497997009094457</v>
+        <v>2.5499635697848251</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>2.8197778639909221</v>
+        <v>2.8199417328663015</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6765,11 +6765,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>2.7677623555696309</v>
+        <v>2.7679402323277005</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.0546045266076063</v>
+        <v>3.0547824033656759</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6787,13 +6787,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6830,13 +6830,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6844,22 +6844,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6883,6 +6883,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6899,18 +6911,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10330,11 +10330,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0219750963209937</v>
+        <v>2.0221050433066186</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.40754104210450359</v>
+        <v>0.40756723368818643</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10740,11 +10740,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>147352.90436000002</v>
+        <v>147362.37434100002</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.3517922202921837E-2</v>
+        <v>6.3522004331598117E-2</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10757,11 +10757,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1648121.5557623634</v>
+        <v>1648227.4761708314</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.71043904573549654</v>
+        <v>0.7104847037718548</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10774,11 +10774,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>205267.108049</v>
+        <v>205280.30002252501</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>8.8482410689520327E-2</v>
+        <v>8.8488097219770301E-2</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10791,11 +10791,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>2000741.5681713633</v>
+        <v>2000870.1505343565</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>0.86243937862793874</v>
+        <v>0.86249480532322331</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -14378,16 +14378,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4334470989761095E-2</v>
+        <v>5.4149659863945585E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.4334470989761095E-2</v>
+        <v>5.4149659863945585E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4334470989761095E-2</v>
+        <v>5.4149659863945585E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15520,50 +15520,50 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16353623555818214</v>
+        <v>0.16354674559902779</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.29764877633755249</v>
+        <v>0.29766790543628885</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.49433522044832079</v>
+        <v>0.4943669900640309</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.34828133305944253</v>
+        <v>0.34830371617853373</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.38108727216700783</v>
+        <v>0.38111176363694144</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.32594988588513557</v>
+        <v>0.32597083382124648</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.29637016568296926</v>
+        <v>0.29638921260878437</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.27667406863833904</v>
+        <v>0.2766918497481487</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>0.16894182232164184</v>
+        <v>0.16895267976523579</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>0.13200357128179246</v>
+        <v>0.13201205480179773</v>
       </c>
       <c r="P123" s="160">
         <f t="shared" si="48"/>
-        <v>0.10425535580947663</v>
+        <v>0.10426205602514563</v>
       </c>
       <c r="Q123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15577,50 +15577,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5814414866273775E-2</v>
+        <v>5.5628144761574079E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10158661308448889</v>
+        <v>0.10124758688309145</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.16871509230318116</v>
+        <v>0.1681520374367452</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11886734916704522</v>
+        <v>0.11847065176140603</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.13006391541536103</v>
+        <v>0.12962985157719098</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1112456948413432</v>
+        <v>0.11087443327253281</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10115022719555264</v>
+        <v>0.10081265734992666</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>9.4428009774177146E-2</v>
+        <v>9.4112874063996155E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.765932502445114E-2</v>
+        <v>5.7466897879331902E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.5052413406755108E-2</v>
+        <v>4.4902059456393785E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>3.5582032699480078E-2</v>
+        <v>3.5463284362294435E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15634,43 +15634,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.3166599878969535E-2</v>
+        <v>7.2917733892986641E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14357618209206888</v>
+        <v>0.14308782773121151</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11927396879579893</v>
+        <v>0.11886827502438466</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13088389670946735</v>
+        <v>0.13043871338732629</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11141426165698096</v>
+        <v>0.11103530158331776</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10817969439967989</v>
+        <v>0.10781173625546329</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0571561189576405E-2</v>
+        <v>9.0263494654917981E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.094112488179292E-2</v>
+        <v>8.0665814933215382E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5983789126526624E-2</v>
+        <v>6.5759354469633671E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3723446319538466E-2</v>
+        <v>5.3540713508927792E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.73540353422209503</v>
+        <v>0.73545079666002711</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6938887.2221134687</v>
+        <v>6939333.1660223445</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16631,7 +16631,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1839130247613787</v>
+        <v>3.1841176464210679</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18737,23 +18737,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18769,23 +18769,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.1594009869255677</v>
+        <v>2.1595397659093036</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.0930310036281163</v>
+        <v>3.093229784540946</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.1988186398539105</v>
+        <v>3.1990242194580145</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.308549559895122</v>
+        <v>3.3087621916149095</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>3.9203866341423401</v>
+        <v>3.9206385870108584</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18801,23 +18801,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>1.8133185458021801</v>
+        <v>1.8134350829837871</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.1685454389180907</v>
+        <v>3.1687490729437284</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>3.3604555447170186</v>
+        <v>3.3606715122970132</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>3.5679122635440712</v>
+        <v>3.5681415638180778</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>4.8826485491593647</v>
+        <v>4.8829623440532695</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18833,23 +18833,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.6693042489375889</v>
+        <v>1.6694115307016595</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.2244761503636949</v>
+        <v>3.2246833789080629</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>3.4862191214315321</v>
+        <v>3.4864431715036037</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>3.7798006451897939</v>
+        <v>3.7800435629690479</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>5.8790298546132256</v>
+        <v>5.8794076842953986</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18865,23 +18865,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.6093759912829102</v>
+        <v>1.6094794216165402</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.2659019316835054</v>
+        <v>3.2661118225531514</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>3.5840710151028574</v>
+        <v>3.5843013538570418</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>3.9529045095650375</v>
+        <v>3.953158552271308</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>6.9107403383855868</v>
+        <v>6.911184473368774</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18897,23 +18897,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.5844382167444402</v>
+        <v>1.5845400443933313</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.2965844549985492</v>
+        <v>3.2967963177527269</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>3.6602058813749898</v>
+        <v>3.6604411131154384</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.0943230603553467</v>
+        <v>4.0945861916574255</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>7.9790326843975841</v>
+        <v>7.979545475701209</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18929,23 +18929,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.5740609319163863</v>
+        <v>1.5741620926446587</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3193098498368605</v>
+        <v>3.3195231730919916</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>3.7194435480648687</v>
+        <v>3.7196825868533048</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>4.2098560473271363</v>
+        <v>4.2101266036283791</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>9.0852039935956306</v>
+        <v>9.0857878756003601</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.9203866341423401</v>
+        <v>3.9206385870108584</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -19020,7 +19020,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.308549559895122</v>
+        <v>3.3087621916149095</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1988186398539105</v>
+        <v>3.1990242194580145</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19076,7 +19076,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.0930310036281163</v>
+        <v>3.093229784540946</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19104,7 +19104,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1594009869255677</v>
+        <v>2.1595397659093036</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.308549559895122</v>
+        <v>3.3087621916149095</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.1988186398539105</v>
+        <v>3.1990242194580145</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19500,7 +19500,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.0930310036281163</v>
+        <v>3.093229784540946</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.1996072966169939</v>
+        <v>3.1998129269059796</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>3.9203866341423401</v>
+        <v>3.9206385870108584</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.1594009869255677</v>
+        <v>2.1595397659093036</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19631,7 +19631,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>9.5641708584119842E-2</v>
+        <v>9.3762070644753601E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>8.4114964645625137E-2</v>
+        <v>8.4111594191453282E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.18363594800869</v>
+        <v>3.1838405518613895</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.1839130247613787</v>
+        <v>3.1841176464210679</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19837,7 +19837,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.27089761289050018</v>
+        <v>0.27089761289050024</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19915,11 +19915,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>1.7468510002791164</v>
+        <v>1.746963265767566</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>1.9521294639279505</v>
+        <v>1.9522417294164001</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38682390329554661</v>
+        <v>0.38682804694002393</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19940,11 +19940,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.0375270067255618</v>
+        <v>2.0376579531912893</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.2667750067255619</v>
+        <v>2.2669059531912894</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28799176672716265</v>
+        <v>0.28799639420825474</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19986,11 +19986,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>2.5497997009094457</v>
+        <v>2.5499635697848251</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>2.8197778639909221</v>
+        <v>2.8199417328663015</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.11436718212418728</v>
+        <v>0.11437263128895325</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20011,11 +20011,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>2.7677623555696309</v>
+        <v>2.7679402323277005</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.0546045266076063</v>
+        <v>3.0547824033656759</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -20023,7 +20023,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>4.0529577975707554E-2</v>
+        <v>4.0535368022830642E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20134,14 +20134,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>535</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>9.5641708584119842E-2</v>
+        <v>9.3762070644753601E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6797.1998264599997</v>
+        <v>6820.3984606800004</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20168,13 +20168,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0930900000000001</v>
+        <v>1.0931602500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.18363594800869</v>
+        <v>3.1838405518613895</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>1.9521294639279505</v>
+        <v>1.9522417294164001</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.2667750067255619</v>
+        <v>2.2669059531912894</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>2.8197778639909221</v>
+        <v>2.8199417328663015</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.0546045266076063</v>
+        <v>3.0547824033656759</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20359,22 +20359,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20564,10 +20564,10 @@
       <c r="B54" s="468" t="s">
         <v>513</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20583,22 +20583,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.5814414866273775E-2</v>
+        <v>5.5628144761574079E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>5.4334470989761095E-2</v>
+        <v>5.4149659863945585E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20733,22 +20733,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20756,13 +20756,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>517</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3517922202921837E-2</v>
+        <v>-6.3522004331598117E-2</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.71043904573549643</v>
+        <v>0.7104847037718548</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20876,7 +20876,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8482410689520327E-2</v>
+        <v>8.8488097219770301E-2</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>0.73540353422209503</v>
+        <v>0.73545079666002711</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20911,33 +20911,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>520</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>522</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -21000,23 +21000,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>542</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>0.40754104210450359</v>
+        <v>0.40756723368818643</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.9910757488177118</v>
+        <v>2.9912679773362729</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21060,13 +21060,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.18363594800869</v>
+        <v>3.1838405518613895</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21230,13 +21230,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21249,22 +21249,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>528</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21329,11 +21329,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>1.7468510002791164</v>
+        <v>1.746963265767566</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>1.9521294639279505</v>
+        <v>1.9522417294164001</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21350,11 +21350,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.0375270067255618</v>
+        <v>2.0376579531912893</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.2667750067255619</v>
+        <v>2.2669059531912894</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21390,11 +21390,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>2.5497997009094457</v>
+        <v>2.5499635697848251</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>2.8197778639909221</v>
+        <v>2.8199417328663015</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21411,11 +21411,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>2.7677623555696309</v>
+        <v>2.7679402323277005</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.0546045266076063</v>
+        <v>3.0547824033656759</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21433,13 +21433,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>529</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21447,13 +21447,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>530</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21490,22 +21490,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21529,12 +21529,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21549,15 +21552,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AB1152-C29E-41EE-BFF4-4886BD2332CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD19FD-8297-418B-9A96-F26330ECE697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -2530,9 +2530,6 @@
   </si>
   <si>
     <t xml:space="preserve">Taxes = </t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <r>
@@ -4991,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,25 +5021,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5441,7 +5438,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="438" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F3" s="439">
         <v>45930</v>
@@ -5449,13 +5446,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="431" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C4" s="430" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E4" s="440" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F4" s="441" t="s">
         <v>325</v>
@@ -5466,13 +5463,13 @@
         <v>351</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E5" s="443" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F5" s="442" t="s">
-        <v>503</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5521,7 +5518,7 @@
         <v>6820.3984606800004</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
@@ -5533,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5553,7 +5550,7 @@
         <v>320</v>
       </c>
       <c r="C15" s="427" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>355</v>
@@ -5568,7 +5565,7 @@
         <v>321</v>
       </c>
       <c r="C16" s="427" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>356</v>
@@ -5579,7 +5576,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C17" s="425">
         <v>0</v>
@@ -5588,7 +5585,7 @@
         <v>275</v>
       </c>
       <c r="E17" s="228" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5717,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
+      <c r="B30" s="464" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5744,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5770,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5805,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5827,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5897,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5919,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="461" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5941,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6091,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6116,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="460" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6291,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
+      <c r="B97" s="464" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
+      <c r="B98" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6365,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="460" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6414,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="460" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6555,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6596,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
+      <c r="B131" s="465" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="460" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6787,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="465" t="s">
+      <c r="B149" s="459" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6830,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="461" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6844,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="464" t="s">
+      <c r="B161" s="458" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="464"/>
-      <c r="D161" s="464"/>
-      <c r="E161" s="464"/>
-      <c r="F161" s="464"/>
+      <c r="C161" s="458"/>
+      <c r="D161" s="458"/>
+      <c r="E161" s="458"/>
+      <c r="F161" s="458"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="464" t="s">
+      <c r="B162" s="458" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="464"/>
-      <c r="D162" s="464"/>
-      <c r="E162" s="464"/>
-      <c r="F162" s="464"/>
+      <c r="C162" s="458"/>
+      <c r="D162" s="458"/>
+      <c r="E162" s="458"/>
+      <c r="F162" s="458"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6883,18 +6880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6911,6 +6896,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7605,7 +7602,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -14017,7 +14014,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="240" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -16784,7 +16781,7 @@
         <v>398</v>
       </c>
       <c r="G20" s="122" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H20" s="122" t="str">
         <f>B18</f>
@@ -16794,10 +16791,10 @@
         <v>424</v>
       </c>
       <c r="J20" s="122" t="s">
+        <v>535</v>
+      </c>
+      <c r="K20" s="122" t="s">
         <v>536</v>
-      </c>
-      <c r="K20" s="122" t="s">
-        <v>537</v>
       </c>
       <c r="L20" s="123" t="s">
         <v>425</v>
@@ -20067,7 +20064,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="445" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F3" s="446">
         <f>Thesis!F3</f>
@@ -20076,7 +20073,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="432" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C4" s="433" t="str">
         <f>Thesis!C4</f>
@@ -20084,7 +20081,7 @@
       </c>
       <c r="D4" s="358"/>
       <c r="E4" s="444" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F4" s="447" t="str">
         <f>Thesis!F4</f>
@@ -20100,11 +20097,11 @@
         <v>1448.HK</v>
       </c>
       <c r="E5" s="448" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F5" s="449" t="str">
         <f>Thesis!F5</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -20137,7 +20134,7 @@
         <v>2.94</v>
       </c>
       <c r="D8" s="352" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
@@ -20168,13 +20165,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="469" t="s">
-        <v>504</v>
-      </c>
-      <c r="C12" s="469"/>
-      <c r="D12" s="469"/>
-      <c r="E12" s="469"/>
-      <c r="F12" s="469"/>
+      <c r="B12" s="472" t="s">
+        <v>503</v>
+      </c>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20217,7 +20214,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="352" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C17" s="434">
         <f>Terminal_Growth</f>
@@ -20359,22 +20356,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="469" t="s">
+      <c r="B29" s="472" t="s">
+        <v>504</v>
+      </c>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="475" t="s">
         <v>505</v>
       </c>
-      <c r="C29" s="469"/>
-      <c r="D29" s="469"/>
-      <c r="E29" s="469"/>
-      <c r="F29" s="469"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="470" t="s">
-        <v>506</v>
-      </c>
-      <c r="C30" s="470"/>
-      <c r="D30" s="470"/>
-      <c r="E30" s="470"/>
-      <c r="F30" s="470"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
+      <c r="E30" s="475"/>
+      <c r="F30" s="475"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20387,7 +20384,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="468" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C33" s="468"/>
       <c r="D33" s="468"/>
@@ -20413,7 +20410,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="468" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C36" s="468"/>
       <c r="D36" s="468"/>
@@ -20448,7 +20445,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="468" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C40" s="468"/>
       <c r="D40" s="468"/>
@@ -20470,7 +20467,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="468" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C43" s="468"/>
       <c r="D43" s="468"/>
@@ -20522,7 +20519,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="352" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20540,7 +20537,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="468" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C51" s="468"/>
       <c r="D51" s="468"/>
@@ -20562,12 +20559,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="468" t="s">
-        <v>513</v>
-      </c>
-      <c r="C54" s="471"/>
-      <c r="D54" s="471"/>
-      <c r="E54" s="471"/>
-      <c r="F54" s="471"/>
+        <v>512</v>
+      </c>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20583,22 +20580,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="469" t="s">
+      <c r="B57" s="472" t="s">
+        <v>513</v>
+      </c>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C57" s="469"/>
-      <c r="D57" s="469"/>
-      <c r="E57" s="469"/>
-      <c r="F57" s="469"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="469" t="s">
-        <v>515</v>
-      </c>
-      <c r="C58" s="469"/>
-      <c r="D58" s="469"/>
-      <c r="E58" s="469"/>
-      <c r="F58" s="469"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20733,22 +20730,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="469" t="s">
-        <v>516</v>
-      </c>
-      <c r="C73" s="469"/>
-      <c r="D73" s="469"/>
-      <c r="E73" s="469"/>
-      <c r="F73" s="469"/>
+      <c r="B73" s="472" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="470" t="s">
+      <c r="B74" s="475" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="470"/>
-      <c r="D74" s="470"/>
-      <c r="E74" s="470"/>
-      <c r="F74" s="470"/>
+      <c r="C74" s="475"/>
+      <c r="D74" s="475"/>
+      <c r="E74" s="475"/>
+      <c r="F74" s="475"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20756,13 +20753,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="469" t="s">
-        <v>517</v>
-      </c>
-      <c r="C77" s="469"/>
-      <c r="D77" s="469"/>
-      <c r="E77" s="469"/>
-      <c r="F77" s="469"/>
+      <c r="B77" s="472" t="s">
+        <v>516</v>
+      </c>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20810,7 +20807,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="352" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20854,7 +20851,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="352" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20911,33 +20908,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="469" t="s">
-        <v>520</v>
-      </c>
-      <c r="C96" s="469"/>
-      <c r="D96" s="469"/>
-      <c r="E96" s="469"/>
-      <c r="F96" s="469"/>
+      <c r="B96" s="472" t="s">
+        <v>519</v>
+      </c>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="470" t="s">
-        <v>521</v>
-      </c>
-      <c r="C97" s="470"/>
-      <c r="D97" s="470"/>
-      <c r="E97" s="470"/>
-      <c r="F97" s="470"/>
+      <c r="B97" s="475" t="s">
+        <v>520</v>
+      </c>
+      <c r="C97" s="475"/>
+      <c r="D97" s="475"/>
+      <c r="E97" s="475"/>
+      <c r="F97" s="475"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="470" t="s">
-        <v>522</v>
-      </c>
-      <c r="C98" s="470"/>
-      <c r="D98" s="470"/>
-      <c r="E98" s="470"/>
-      <c r="F98" s="470"/>
+      <c r="B98" s="475" t="s">
+        <v>521</v>
+      </c>
+      <c r="C98" s="475"/>
+      <c r="D98" s="475"/>
+      <c r="E98" s="475"/>
+      <c r="F98" s="475"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20981,7 +20978,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="394"/>
       <c r="B104" s="381" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C104" s="377">
         <v>0</v>
@@ -21000,23 +20997,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="469" t="s">
-        <v>523</v>
-      </c>
-      <c r="C107" s="469"/>
-      <c r="D107" s="469"/>
-      <c r="E107" s="469"/>
-      <c r="F107" s="469"/>
+      <c r="B107" s="472" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="469" t="s">
-        <v>542</v>
-      </c>
-      <c r="C108" s="469"/>
-      <c r="D108" s="469"/>
-      <c r="E108" s="469"/>
-      <c r="F108" s="469"/>
+      <c r="B108" s="472" t="s">
+        <v>541</v>
+      </c>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21060,13 +21057,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="469" t="s">
-        <v>524</v>
-      </c>
-      <c r="C114" s="469"/>
-      <c r="D114" s="469"/>
-      <c r="E114" s="469"/>
-      <c r="F114" s="469"/>
+      <c r="B114" s="472" t="s">
+        <v>523</v>
+      </c>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21209,7 +21206,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="468" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C124" s="468"/>
       <c r="D124" s="468"/>
@@ -21230,13 +21227,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
-        <v>526</v>
-      </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="B127" s="470" t="s">
+        <v>525</v>
+      </c>
+      <c r="C127" s="470"/>
+      <c r="D127" s="470"/>
+      <c r="E127" s="470"/>
+      <c r="F127" s="470"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21249,22 +21246,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="471" t="s">
+        <v>526</v>
+      </c>
+      <c r="C131" s="471"/>
+      <c r="D131" s="471"/>
+      <c r="E131" s="471"/>
+      <c r="F131" s="471"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="469" t="s">
-        <v>528</v>
-      </c>
-      <c r="C132" s="469"/>
-      <c r="D132" s="469"/>
-      <c r="E132" s="469"/>
-      <c r="F132" s="469"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21433,13 +21430,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
-        <v>529</v>
-      </c>
-      <c r="C149" s="469"/>
-      <c r="D149" s="469"/>
-      <c r="E149" s="469"/>
-      <c r="F149" s="469"/>
+      <c r="B149" s="473" t="s">
+        <v>528</v>
+      </c>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21447,13 +21444,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="471" t="s">
-        <v>530</v>
-      </c>
-      <c r="C152" s="471"/>
-      <c r="D152" s="471"/>
-      <c r="E152" s="471"/>
-      <c r="F152" s="471"/>
+      <c r="B152" s="474" t="s">
+        <v>529</v>
+      </c>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21472,7 +21469,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="352" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
@@ -21486,30 +21483,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="352" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="469" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="469"/>
+      <c r="D161" s="469"/>
+      <c r="E161" s="469"/>
+      <c r="F161" s="469"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="469" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="469"/>
+      <c r="D162" s="469"/>
+      <c r="E162" s="469"/>
+      <c r="F162" s="469"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21529,15 +21526,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21552,12 +21546,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1448.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1448.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD19FD-8297-418B-9A96-F26330ECE697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD51B56-00F9-49CD-B764-50ECC7FBBBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4988,30 +4988,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5021,6 +5021,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5030,16 +5039,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5497,7 +5497,7 @@
         <v>352</v>
       </c>
       <c r="C8" s="47">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6820.3984606800004</v>
+        <v>6866.79572912</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>533</v>
       </c>
       <c r="E10" s="311">
         <f>Scenarios!F34</f>
-        <v>9.3762070644753601E-2</v>
+        <v>9.0084070295280566E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5530,13 +5530,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="458" t="s">
         <v>357</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5571,7 +5571,7 @@
         <v>356</v>
       </c>
       <c r="E16" s="426">
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C18" s="259">
         <f>C125</f>
-        <v>3.1838405518613895</v>
+        <v>3.1845771257311086</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>349</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C22" s="262">
         <f>E140</f>
-        <v>1.9522417294164001</v>
+        <v>1.9526458851748194</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>411</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C23" s="263">
         <f>E141</f>
-        <v>2.2669059531912894</v>
+        <v>2.2673773604679095</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>412</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C24" s="263">
         <f>E144</f>
-        <v>2.8199417328663015</v>
+        <v>2.8205316608176689</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>413</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C25" s="263">
         <f>E145</f>
-        <v>3.0547824033656759</v>
+        <v>3.0554227596947281</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>414</v>
@@ -5714,22 +5714,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="458" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="460" t="s">
         <v>267</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="460"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="193" t="s">
@@ -5741,13 +5741,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5767,13 +5767,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5802,13 +5802,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5894,13 +5894,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5916,7 +5916,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="459" t="s">
         <v>266</v>
       </c>
       <c r="C54" s="462"/>
@@ -5938,22 +5938,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>5.5628144761574079E-2</v>
+        <v>5.526506140070004E-2</v>
       </c>
       <c r="F62" s="264"/>
     </row>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.4149659863945585E-2</v>
+        <v>5.378378378378379E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>323</v>
@@ -6088,13 +6088,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="192"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="458" t="s">
         <v>484</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="192"/>
@@ -6113,13 +6113,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="192"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="458" t="s">
         <v>272</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="192"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="C79" s="204">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3522004331598117E-2</v>
+        <v>-6.3536699994832718E-2</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C86" s="204">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.7104847037718548</v>
+        <v>0.71064907270274469</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C90" s="204">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8488097219770301E-2</v>
+        <v>8.8508568728670176E-2</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C92" s="220">
         <f>DCF!F8</f>
-        <v>0.73545079666002711</v>
+        <v>0.7356209414365823</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6288,31 +6288,31 @@
       <c r="A95" s="192"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="458" t="s">
         <v>491</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="460"/>
+      <c r="D97" s="460"/>
+      <c r="E97" s="460"/>
+      <c r="F97" s="460"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="460"/>
+      <c r="D98" s="460"/>
+      <c r="E98" s="460"/>
+      <c r="F98" s="460"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="193" t="s">
@@ -6362,22 +6362,22 @@
       <c r="C106" s="117"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="458" t="s">
         <v>285</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="193" t="s">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C111" s="220">
         <f>BS!D47</f>
-        <v>0.40756723368818643</v>
+        <v>0.40766152338944456</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C112" s="220">
         <f>DCF!C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6411,13 +6411,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="458" t="s">
         <v>497</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="193" t="s">
@@ -6552,13 +6552,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="194" t="s">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C125" s="198">
         <f>Scenarios!C36</f>
-        <v>3.1838405518613895</v>
+        <v>3.1845771257311086</v>
       </c>
       <c r="D125" s="195" t="str">
         <f>Market_currency</f>
@@ -6593,22 +6593,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="461" t="s">
         <v>286</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="461"/>
+      <c r="D131" s="461"/>
+      <c r="E131" s="461"/>
+      <c r="F131" s="461"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="458" t="s">
         <v>361</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="193" t="s">
@@ -6673,11 +6673,11 @@
       </c>
       <c r="D140" s="342">
         <f>Scenarios!D62</f>
-        <v>1.746963265767566</v>
+        <v>1.7473674215259853</v>
       </c>
       <c r="E140" s="343">
         <f>Scenarios!E62</f>
-        <v>1.9522417294164001</v>
+        <v>1.9526458851748194</v>
       </c>
       <c r="F140" s="344">
         <f>E22</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="D141" s="342">
         <f>Scenarios!D63</f>
-        <v>2.0376579531912893</v>
+        <v>2.0381293604679094</v>
       </c>
       <c r="E141" s="343">
         <f>Scenarios!E63</f>
-        <v>2.2669059531912894</v>
+        <v>2.2673773604679095</v>
       </c>
       <c r="F141" s="344">
         <f>Scenarios!F63</f>
@@ -6741,11 +6741,11 @@
       </c>
       <c r="D144" s="342">
         <f>Scenarios!D66</f>
-        <v>2.5499635697848251</v>
+        <v>2.5505534977361926</v>
       </c>
       <c r="E144" s="343">
         <f>Scenarios!E66</f>
-        <v>2.8199417328663015</v>
+        <v>2.8205316608176689</v>
       </c>
       <c r="F144" s="344">
         <f>E24</f>
@@ -6762,11 +6762,11 @@
       </c>
       <c r="D145" s="342">
         <f>Scenarios!D67</f>
-        <v>2.7679402323277005</v>
+        <v>2.7685805886567527</v>
       </c>
       <c r="E145" s="343">
         <f>Scenarios!E67</f>
-        <v>3.0547824033656759</v>
+        <v>3.0554227596947281</v>
       </c>
       <c r="F145" s="344">
         <f>Scenarios!F67</f>
@@ -6784,13 +6784,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="459" t="s">
+      <c r="B149" s="465" t="s">
         <v>362</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="193" t="s">
@@ -6827,13 +6827,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="459" t="s">
         <v>444</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6841,22 +6841,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="458" t="s">
+      <c r="B161" s="464" t="s">
         <v>295</v>
       </c>
-      <c r="C161" s="458"/>
-      <c r="D161" s="458"/>
-      <c r="E161" s="458"/>
-      <c r="F161" s="458"/>
+      <c r="C161" s="464"/>
+      <c r="D161" s="464"/>
+      <c r="E161" s="464"/>
+      <c r="F161" s="464"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="458" t="s">
+      <c r="B162" s="464" t="s">
         <v>296</v>
       </c>
-      <c r="C162" s="458"/>
-      <c r="D162" s="458"/>
-      <c r="E162" s="458"/>
-      <c r="F162" s="458"/>
+      <c r="C162" s="464"/>
+      <c r="D162" s="464"/>
+      <c r="E162" s="464"/>
+      <c r="F162" s="464"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6880,6 +6880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6896,18 +6908,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10327,11 +10327,11 @@
       </c>
       <c r="C47" s="135">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.0221050433066186</v>
+        <v>2.0225728524548678</v>
       </c>
       <c r="D47" s="135">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.40756723368818643</v>
+        <v>0.40766152338944456</v>
       </c>
       <c r="F47" s="227"/>
     </row>
@@ -10737,11 +10737,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>147362.37434100002</v>
+        <v>147396.46627260002</v>
       </c>
       <c r="D86" s="204">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.3522004331598117E-2</v>
+        <v>6.3536699994832718E-2</v>
       </c>
       <c r="E86" s="218" t="str">
         <f>Market_currency</f>
@@ -10754,11 +10754,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>1648227.4761708314</v>
+        <v>1648608.7896413163</v>
       </c>
       <c r="D87" s="204">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.7104847037718548</v>
+        <v>0.71064907270274469</v>
       </c>
       <c r="E87" s="218" t="str">
         <f>Market_currency</f>
@@ -10771,11 +10771,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>205280.30002252501</v>
+        <v>205327.79112721499</v>
       </c>
       <c r="D88" s="204">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>8.8488097219770301E-2</v>
+        <v>8.8508568728670176E-2</v>
       </c>
       <c r="E88" s="218" t="str">
         <f>Market_currency</f>
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C89" s="163">
         <f>SUM(C86:C88)</f>
-        <v>2000870.1505343565</v>
+        <v>2001333.0470411312</v>
       </c>
       <c r="D89" s="220">
         <f>SUM(D86:D88)</f>
-        <v>0.86249480532322331</v>
+        <v>0.86269434142624757</v>
       </c>
       <c r="E89" s="218" t="str">
         <f>Market_currency</f>
@@ -14375,16 +14375,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.4149659863945585E-2</v>
+        <v>5.378378378378379E-2</v>
       </c>
       <c r="E92" s="242"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.4149659863945585E-2</v>
+        <v>5.378378378378379E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4149659863945585E-2</v>
+        <v>5.378378378378379E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15517,50 +15517,50 @@
       </c>
       <c r="C123" s="160">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.16354674559902779</v>
+        <v>0.1635845817460721</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="239"/>
       <c r="F123" s="26"/>
       <c r="G123" s="160">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.29766790543628885</v>
+        <v>0.29773677019173966</v>
       </c>
       <c r="H123" s="160">
         <f t="shared" si="48"/>
-        <v>0.4943669900640309</v>
+        <v>0.49448136068058701</v>
       </c>
       <c r="I123" s="160">
         <f t="shared" si="48"/>
-        <v>0.34830371617853373</v>
+        <v>0.34838429540726218</v>
       </c>
       <c r="J123" s="160">
         <f t="shared" si="48"/>
-        <v>0.38111176363694144</v>
+        <v>0.38119993292870247</v>
       </c>
       <c r="K123" s="160">
         <f t="shared" si="48"/>
-        <v>0.32597083382124648</v>
+        <v>0.32604624639124558</v>
       </c>
       <c r="L123" s="160">
         <f t="shared" si="48"/>
-        <v>0.29638921260878437</v>
+        <v>0.29645778154171876</v>
       </c>
       <c r="M123" s="160">
         <f t="shared" si="48"/>
-        <v>0.2766918497481487</v>
+        <v>0.2767558617434635</v>
       </c>
       <c r="N123" s="160">
         <f t="shared" si="48"/>
-        <v>0.16895267976523579</v>
+        <v>0.16899176656217396</v>
       </c>
       <c r="O123" s="160">
         <f t="shared" si="48"/>
-        <v>0.13201205480179773</v>
+        <v>0.13204259547381667</v>
       </c>
       <c r="P123" s="160">
         <f t="shared" si="48"/>
-        <v>0.10426205602514563</v>
+        <v>0.10428617680155398</v>
       </c>
       <c r="Q123" s="160" t="str">
         <f t="shared" si="48"/>
@@ -15574,50 +15574,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.5628144761574079E-2</v>
+        <v>5.526506140070004E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="239"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>0.10124758688309145</v>
+        <v>0.10058674668639854</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>0.1681520374367452</v>
+        <v>0.16705451374344157</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.11847065176140603</v>
+        <v>0.11769739709704803</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.12962985157719098</v>
+        <v>0.12878376112456164</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11087443327253281</v>
+        <v>0.11015075891596135</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10081265734992666</v>
+        <v>0.10015465592625634</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>9.4112874063996155E-2</v>
+        <v>9.3498601940359291E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>5.7466897879331902E-2</v>
+        <v>5.7091813027761472E-2</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>4.4902059456393785E-2</v>
+        <v>4.4608984957370493E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>3.5463284362294435E-2</v>
+        <v>3.5231816487011479E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15631,43 +15631,43 @@
       <c r="C125" s="152"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2917733892986641E-2</v>
+        <v>7.2425046501817816E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14308782773121151</v>
+        <v>0.14212101808437899</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11886827502438466</v>
+        <v>0.11806511100394963</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13043871338732629</v>
+        <v>0.12955737072930382</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11103530158331776</v>
+        <v>0.11028506305910615</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10781173625546329</v>
+        <v>0.10708327857806152</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0263494654917981E-2</v>
+        <v>8.9653606177519884E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0665814933215382E-2</v>
+        <v>8.0120775643126099E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5759354469633671E-2</v>
+        <v>6.5315034507001019E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3540713508927792E-2</v>
+        <v>5.3178951931164765E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.73545079666002711</v>
+        <v>0.7356209414365823</v>
       </c>
       <c r="G8" s="302" t="str">
         <f>Market_currency</f>
@@ -16581,7 +16581,7 @@
       </c>
       <c r="C9" s="191">
         <f>Exchange_Rate</f>
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="C10" s="291">
         <f>C8*Exchange_Rate</f>
-        <v>6939333.1660223445</v>
+        <v>6940938.5640942995</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="I18" s="130">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>3.1841176464210679</v>
+        <v>3.1848542843959486</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18734,23 +18734,23 @@
       </c>
       <c r="B65" s="120">
         <f>C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="C65" s="120">
         <f>C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="D65" s="120">
         <f>C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="E65" s="120">
         <f>C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="F65" s="120">
         <f>C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="G65" s="304"/>
       <c r="H65" s="304"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B66" s="120">
         <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>2.1595397659093036</v>
+        <v>2.1600393702507517</v>
       </c>
       <c r="C66" s="120">
         <f t="shared" si="12"/>
-        <v>3.093229784540946</v>
+        <v>3.0939453958271321</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="12"/>
-        <v>3.1990242194580145</v>
+        <v>3.1997643060327876</v>
       </c>
       <c r="E66" s="120">
         <f t="shared" si="12"/>
-        <v>3.3087621916149095</v>
+        <v>3.309527665806145</v>
       </c>
       <c r="F66" s="120">
         <f t="shared" si="12"/>
-        <v>3.9206385870108584</v>
+        <v>3.9215456173375238</v>
       </c>
       <c r="G66" s="304"/>
       <c r="H66" s="304"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B67" s="120">
         <f t="shared" si="12"/>
-        <v>1.8134350829837871</v>
+        <v>1.8138546168375715</v>
       </c>
       <c r="C67" s="120">
         <f t="shared" si="12"/>
-        <v>3.1687490729437284</v>
+        <v>3.1694821554360231</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="12"/>
-        <v>3.3606715122970132</v>
+        <v>3.3614489955849942</v>
       </c>
       <c r="E67" s="120">
         <f t="shared" si="12"/>
-        <v>3.5681415638180778</v>
+        <v>3.5689670448045021</v>
       </c>
       <c r="F67" s="120">
         <f t="shared" si="12"/>
-        <v>4.8829623440532695</v>
+        <v>4.8840920056713273</v>
       </c>
       <c r="G67" s="304"/>
       <c r="H67" s="304"/>
@@ -18830,23 +18830,23 @@
       </c>
       <c r="B68" s="120">
         <f t="shared" si="12"/>
-        <v>1.6694115307016595</v>
+        <v>1.6697977450523134</v>
       </c>
       <c r="C68" s="120">
         <f t="shared" si="12"/>
-        <v>3.2246833789080629</v>
+        <v>3.2254294016677871</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="12"/>
-        <v>3.4864431715036037</v>
+        <v>3.487249751763061</v>
       </c>
       <c r="E68" s="120">
         <f t="shared" si="12"/>
-        <v>3.7800435629690479</v>
+        <v>3.7809180669743618</v>
       </c>
       <c r="F68" s="120">
         <f t="shared" si="12"/>
-        <v>5.8794076842953986</v>
+        <v>5.8807678711512219</v>
       </c>
       <c r="G68" s="304"/>
       <c r="H68" s="304"/>
@@ -18862,23 +18862,23 @@
       </c>
       <c r="B69" s="120">
         <f t="shared" si="12"/>
-        <v>1.6094794216165402</v>
+        <v>1.6098517708176083</v>
       </c>
       <c r="C69" s="120">
         <f t="shared" si="12"/>
-        <v>3.2661118225531514</v>
+        <v>3.2668674296838747</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="12"/>
-        <v>3.5843013538570418</v>
+        <v>3.5851305733721039</v>
       </c>
       <c r="E69" s="120">
         <f t="shared" si="12"/>
-        <v>3.953158552271308</v>
+        <v>3.9540731060138805</v>
       </c>
       <c r="F69" s="120">
         <f t="shared" si="12"/>
-        <v>6.911184473368774</v>
+        <v>6.9127833593082464</v>
       </c>
       <c r="G69" s="304"/>
       <c r="H69" s="304"/>
@@ -18894,23 +18894,23 @@
       </c>
       <c r="B70" s="120">
         <f t="shared" si="12"/>
-        <v>1.5845400443933313</v>
+        <v>1.584906623929339</v>
       </c>
       <c r="C70" s="120">
         <f t="shared" si="12"/>
-        <v>3.2967963177527269</v>
+        <v>3.2975590236677652</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="12"/>
-        <v>3.6604411131154384</v>
+        <v>3.661287947381052</v>
       </c>
       <c r="E70" s="120">
         <f t="shared" si="12"/>
-        <v>4.0945861916574255</v>
+        <v>4.0955334643449115</v>
       </c>
       <c r="F70" s="120">
         <f t="shared" si="12"/>
-        <v>7.979545475701209</v>
+        <v>7.9813915243942573</v>
       </c>
       <c r="G70" s="304"/>
       <c r="H70" s="304"/>
@@ -18926,23 +18926,23 @@
       </c>
       <c r="B71" s="120">
         <f t="shared" si="12"/>
-        <v>1.5741620926446587</v>
+        <v>1.5745262712664387</v>
       </c>
       <c r="C71" s="120">
         <f t="shared" si="12"/>
-        <v>3.3195231730919916</v>
+        <v>3.3202911368104626</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="12"/>
-        <v>3.7196825868533048</v>
+        <v>3.7205431264916746</v>
       </c>
       <c r="E71" s="120">
         <f t="shared" si="12"/>
-        <v>4.2101266036283791</v>
+        <v>4.2111006063128507</v>
       </c>
       <c r="F71" s="120">
         <f t="shared" si="12"/>
-        <v>9.0857878756003601</v>
+        <v>9.0878898508173886</v>
       </c>
       <c r="G71" s="304"/>
       <c r="H71" s="304"/>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="E74" s="128">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>3.9206385870108584</v>
+        <v>3.9215456173375238</v>
       </c>
       <c r="F74" s="131">
         <f>Scenarios!F29</f>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="E75" s="128">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>3.3087621916149095</v>
+        <v>3.309527665806145</v>
       </c>
       <c r="F75" s="131">
         <f>Scenarios!F22*(1-F$74-F$78)</f>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="E76" s="128">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>3.1990242194580145</v>
+        <v>3.1997643060327876</v>
       </c>
       <c r="F76" s="131">
         <f>Scenarios!F23*(1-F$74-F$78)</f>
@@ -19073,7 +19073,7 @@
       </c>
       <c r="E77" s="128">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>3.093229784540946</v>
+        <v>3.0939453958271321</v>
       </c>
       <c r="F77" s="131">
         <f>Scenarios!F24*(1-F$74-F$78)</f>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="E78" s="128">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>2.1595397659093036</v>
+        <v>2.1600393702507517</v>
       </c>
       <c r="F78" s="131">
         <f>Scenarios!F30</f>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="E22" s="335">
         <f>DCF!E75</f>
-        <v>3.3087621916149095</v>
+        <v>3.309527665806145</v>
       </c>
       <c r="F22" s="337">
         <f>1-F23-F24</f>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="E23" s="335">
         <f>DCF!E76</f>
-        <v>3.1990242194580145</v>
+        <v>3.1997643060327876</v>
       </c>
       <c r="F23" s="336">
         <v>0.6</v>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="E24" s="335">
         <f>DCF!E77</f>
-        <v>3.093229784540946</v>
+        <v>3.0939453958271321</v>
       </c>
       <c r="F24" s="336">
         <v>0.2</v>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C25" s="451">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>3.1998129269059796</v>
+        <v>3.2005531959463278</v>
       </c>
       <c r="D25" s="142" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E29" s="335">
         <f>DCF!E74</f>
-        <v>3.9206385870108584</v>
+        <v>3.9215456173375238</v>
       </c>
       <c r="F29" s="336">
         <v>0.05</v>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="E30" s="335">
         <f>DCF!E78</f>
-        <v>2.1595397659093036</v>
+        <v>2.1600393702507517</v>
       </c>
       <c r="F30" s="336">
         <v>0.05</v>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="C34" s="147">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="F34" s="339">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>9.3762070644753601E-2</v>
+        <v>9.0084070295280566E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="C35" s="329">
         <f>DCF!C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="F35" s="339">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>8.4111594191453282E-2</v>
+        <v>8.4099464143756297E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C36" s="330">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>3.1838405518613895</v>
+        <v>3.1845771257311086</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="C47" s="147">
         <f>DCF!I18</f>
-        <v>3.1841176464210679</v>
+        <v>3.1848542843959486</v>
       </c>
       <c r="D47" s="147" t="str">
         <f>Market_currency</f>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="F53" s="256">
         <f>BS!D89/C36</f>
-        <v>0.27089761289050024</v>
+        <v>0.27089761289050018</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19912,11 +19912,11 @@
       </c>
       <c r="D62" s="120">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>1.746963265767566</v>
+        <v>1.7473674215259853</v>
       </c>
       <c r="E62" s="341">
         <f>C62+D62</f>
-        <v>1.9522417294164001</v>
+        <v>1.9526458851748194</v>
       </c>
       <c r="F62" s="309">
         <f>Thesis!E22</f>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="G62" s="450">
         <f>(1-E62/C36)</f>
-        <v>0.38682804694002393</v>
+        <v>0.38684295965150006</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19937,11 +19937,11 @@
       </c>
       <c r="D63" s="120">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>2.0376579531912893</v>
+        <v>2.0381293604679094</v>
       </c>
       <c r="E63" s="341">
         <f>C63+D63</f>
-        <v>2.2669059531912894</v>
+        <v>2.2673773604679095</v>
       </c>
       <c r="F63" s="309">
         <f>Thesis!E23</f>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="G63" s="450">
         <f>(1-E63/C36)</f>
-        <v>0.28799639420825474</v>
+        <v>0.28801304821676454</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19983,11 +19983,11 @@
       </c>
       <c r="D66" s="120">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>2.5499635697848251</v>
+        <v>2.5505534977361926</v>
       </c>
       <c r="E66" s="341">
         <f>C66+D66</f>
-        <v>2.8199417328663015</v>
+        <v>2.8205316608176689</v>
       </c>
       <c r="F66" s="309">
         <f>Thesis!E24</f>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="G66" s="450">
         <f>(1-E66/C47)</f>
-        <v>0.11437263128895325</v>
+        <v>0.1143922424844559</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20008,11 +20008,11 @@
       </c>
       <c r="D67" s="120">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>2.7679402323277005</v>
+        <v>2.7685805886567527</v>
       </c>
       <c r="E67" s="341">
         <f>C67+D67</f>
-        <v>3.0547824033656759</v>
+        <v>3.0554227596947281</v>
       </c>
       <c r="F67" s="309">
         <f>Thesis!E25</f>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="G67" s="450">
         <f>(1-E67/C36)</f>
-        <v>4.0535368022830642E-2</v>
+        <v>4.0556206032136721E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20131,14 +20131,14 @@
       </c>
       <c r="C8" s="365">
         <f>Market_Price</f>
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="D8" s="352" t="s">
         <v>534</v>
       </c>
       <c r="E8" s="369">
         <f>Scenarios!F34</f>
-        <v>9.3762070644753601E-2</v>
+        <v>9.0084070295280566E-2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="C10" s="366">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6820.3984606800004</v>
+        <v>6866.79572912</v>
       </c>
       <c r="E10" s="362"/>
     </row>
@@ -20165,13 +20165,13 @@
       <c r="E11" s="358"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
+      <c r="B12" s="469" t="s">
         <v>503</v>
       </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="C12" s="469"/>
+      <c r="D12" s="469"/>
+      <c r="E12" s="469"/>
+      <c r="F12" s="469"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="356" t="s">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="E16" s="435">
         <f>Exchange_Rate</f>
-        <v>1.0931602500000002</v>
+        <v>1.0934131500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="C18" s="368">
         <f>C125</f>
-        <v>3.1838405518613895</v>
+        <v>3.1845771257311086</v>
       </c>
       <c r="D18" s="359" t="s">
         <v>364</v>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C22" s="373">
         <f>E140</f>
-        <v>1.9522417294164001</v>
+        <v>1.9526458851748194</v>
       </c>
       <c r="D22" s="374" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C23" s="376">
         <f>E141</f>
-        <v>2.2669059531912894</v>
+        <v>2.2673773604679095</v>
       </c>
       <c r="D23" s="374" t="s">
         <v>447</v>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="C24" s="376">
         <f>E144</f>
-        <v>2.8199417328663015</v>
+        <v>2.8205316608176689</v>
       </c>
       <c r="D24" s="374" t="s">
         <v>449</v>
@@ -20335,7 +20335,7 @@
       </c>
       <c r="C25" s="376">
         <f>E145</f>
-        <v>3.0547824033656759</v>
+        <v>3.0554227596947281</v>
       </c>
       <c r="D25" s="374" t="s">
         <v>448</v>
@@ -20356,22 +20356,22 @@
       <c r="F27" s="354"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="469" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
+      <c r="C29" s="469"/>
+      <c r="D29" s="469"/>
+      <c r="E29" s="469"/>
+      <c r="F29" s="469"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="475" t="s">
+      <c r="B30" s="470" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
-      <c r="E30" s="475"/>
-      <c r="F30" s="475"/>
+      <c r="C30" s="470"/>
+      <c r="D30" s="470"/>
+      <c r="E30" s="470"/>
+      <c r="F30" s="470"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="378" t="s">
@@ -20561,10 +20561,10 @@
       <c r="B54" s="468" t="s">
         <v>512</v>
       </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+      <c r="C54" s="471"/>
+      <c r="D54" s="471"/>
+      <c r="E54" s="471"/>
+      <c r="F54" s="471"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="381" t="s">
@@ -20580,22 +20580,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="469" t="s">
         <v>513</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
+      <c r="C57" s="469"/>
+      <c r="D57" s="469"/>
+      <c r="E57" s="469"/>
+      <c r="F57" s="469"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
+      <c r="B58" s="469" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="469"/>
+      <c r="D58" s="469"/>
+      <c r="E58" s="469"/>
+      <c r="F58" s="469"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="381" t="s">
@@ -20629,7 +20629,7 @@
       </c>
       <c r="C62" s="387">
         <f>Normalized_FCF!C124</f>
-        <v>5.5628144761574079E-2</v>
+        <v>5.526506140070004E-2</v>
       </c>
       <c r="F62" s="388"/>
     </row>
@@ -20639,7 +20639,7 @@
       </c>
       <c r="C63" s="387">
         <f>Normalized_FCF!C92</f>
-        <v>5.4149659863945585E-2</v>
+        <v>5.378378378378379E-2</v>
       </c>
       <c r="E63" s="381" t="s">
         <v>375</v>
@@ -20730,22 +20730,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="395"/>
-      <c r="B73" s="472" t="s">
+      <c r="B73" s="469" t="s">
         <v>515</v>
       </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="C73" s="469"/>
+      <c r="D73" s="469"/>
+      <c r="E73" s="469"/>
+      <c r="F73" s="469"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="475" t="s">
+      <c r="B74" s="470" t="s">
         <v>485</v>
       </c>
-      <c r="C74" s="475"/>
-      <c r="D74" s="475"/>
-      <c r="E74" s="475"/>
-      <c r="F74" s="475"/>
+      <c r="C74" s="470"/>
+      <c r="D74" s="470"/>
+      <c r="E74" s="470"/>
+      <c r="F74" s="470"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="378" t="s">
@@ -20753,13 +20753,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
+      <c r="B77" s="469" t="s">
         <v>516</v>
       </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="C77" s="469"/>
+      <c r="D77" s="469"/>
+      <c r="E77" s="469"/>
+      <c r="F77" s="469"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="352" t="s">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="C79" s="396">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.3522004331598117E-2</v>
+        <v>-6.3536699994832718E-2</v>
       </c>
       <c r="D79" s="352" t="str">
         <f>Market_currency</f>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="C86" s="396">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.7104847037718548</v>
+        <v>0.71064907270274469</v>
       </c>
       <c r="D86" s="352" t="str">
         <f>Market_currency</f>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="C90" s="396">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.8488097219770301E-2</v>
+        <v>8.8508568728670176E-2</v>
       </c>
       <c r="D90" s="352" t="str">
         <f>Market_currency</f>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C92" s="396">
         <f>DCF!F8</f>
-        <v>0.73545079666002711</v>
+        <v>0.7356209414365823</v>
       </c>
       <c r="D92" s="352" t="str">
         <f>Market_currency</f>
@@ -20908,33 +20908,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="394"/>
-      <c r="B96" s="472" t="s">
+      <c r="B96" s="469" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="C96" s="469"/>
+      <c r="D96" s="469"/>
+      <c r="E96" s="469"/>
+      <c r="F96" s="469"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="394"/>
-      <c r="B97" s="475" t="s">
+      <c r="B97" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C97" s="475"/>
-      <c r="D97" s="475"/>
-      <c r="E97" s="475"/>
-      <c r="F97" s="475"/>
+      <c r="C97" s="470"/>
+      <c r="D97" s="470"/>
+      <c r="E97" s="470"/>
+      <c r="F97" s="470"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="394"/>
-      <c r="B98" s="475" t="s">
+      <c r="B98" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C98" s="475"/>
-      <c r="D98" s="475"/>
-      <c r="E98" s="475"/>
-      <c r="F98" s="475"/>
+      <c r="C98" s="470"/>
+      <c r="D98" s="470"/>
+      <c r="E98" s="470"/>
+      <c r="F98" s="470"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="394"/>
@@ -20997,23 +20997,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="394"/>
-      <c r="B107" s="472" t="s">
+      <c r="B107" s="469" t="s">
         <v>522</v>
       </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="C107" s="469"/>
+      <c r="D107" s="469"/>
+      <c r="E107" s="469"/>
+      <c r="F107" s="469"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="394"/>
-      <c r="B108" s="472" t="s">
+      <c r="B108" s="469" t="s">
         <v>541</v>
       </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="C108" s="469"/>
+      <c r="D108" s="469"/>
+      <c r="E108" s="469"/>
+      <c r="F108" s="469"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="394"/>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="C111" s="403">
         <f>BS!D47</f>
-        <v>0.40756723368818643</v>
+        <v>0.40766152338944456</v>
       </c>
       <c r="D111" s="352" t="str">
         <f>Market_currency</f>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="C112" s="403">
         <f>DCF!C11</f>
-        <v>2.9912679773362729</v>
+        <v>2.9919600000030946</v>
       </c>
       <c r="D112" s="352" t="str">
         <f>Market_currency</f>
@@ -21057,13 +21057,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="394"/>
-      <c r="B114" s="472" t="s">
+      <c r="B114" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="C114" s="469"/>
+      <c r="D114" s="469"/>
+      <c r="E114" s="469"/>
+      <c r="F114" s="469"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="394"/>
@@ -21219,7 +21219,7 @@
       </c>
       <c r="C125" s="413">
         <f>Scenarios!C36</f>
-        <v>3.1838405518613895</v>
+        <v>3.1845771257311086</v>
       </c>
       <c r="D125" s="352" t="str">
         <f>Market_currency</f>
@@ -21227,13 +21227,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="470" t="s">
+      <c r="B127" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="470"/>
-      <c r="D127" s="470"/>
-      <c r="E127" s="470"/>
-      <c r="F127" s="470"/>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="354" t="s">
@@ -21246,22 +21246,22 @@
       <c r="F129" s="354"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="471" t="s">
+      <c r="B131" s="474" t="s">
         <v>526</v>
       </c>
-      <c r="C131" s="471"/>
-      <c r="D131" s="471"/>
-      <c r="E131" s="471"/>
-      <c r="F131" s="471"/>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
+      <c r="B132" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="469"/>
+      <c r="D132" s="469"/>
+      <c r="E132" s="469"/>
+      <c r="F132" s="469"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="378" t="s">
@@ -21326,11 +21326,11 @@
       </c>
       <c r="D140" s="418">
         <f>Scenarios!D62</f>
-        <v>1.746963265767566</v>
+        <v>1.7473674215259853</v>
       </c>
       <c r="E140" s="419">
         <f>Scenarios!E62</f>
-        <v>1.9522417294164001</v>
+        <v>1.9526458851748194</v>
       </c>
       <c r="F140" s="420">
         <f>E22</f>
@@ -21347,11 +21347,11 @@
       </c>
       <c r="D141" s="418">
         <f>Scenarios!D63</f>
-        <v>2.0376579531912893</v>
+        <v>2.0381293604679094</v>
       </c>
       <c r="E141" s="419">
         <f>Scenarios!E63</f>
-        <v>2.2669059531912894</v>
+        <v>2.2673773604679095</v>
       </c>
       <c r="F141" s="420">
         <f>Scenarios!F63</f>
@@ -21387,11 +21387,11 @@
       </c>
       <c r="D144" s="418">
         <f>Scenarios!D66</f>
-        <v>2.5499635697848251</v>
+        <v>2.5505534977361926</v>
       </c>
       <c r="E144" s="419">
         <f>Scenarios!E66</f>
-        <v>2.8199417328663015</v>
+        <v>2.8205316608176689</v>
       </c>
       <c r="F144" s="420">
         <f>E24</f>
@@ -21408,11 +21408,11 @@
       </c>
       <c r="D145" s="418">
         <f>Scenarios!D67</f>
-        <v>2.7679402323277005</v>
+        <v>2.7685805886567527</v>
       </c>
       <c r="E145" s="419">
         <f>Scenarios!E67</f>
-        <v>3.0547824033656759</v>
+        <v>3.0554227596947281</v>
       </c>
       <c r="F145" s="420">
         <f>Scenarios!F67</f>
@@ -21430,13 +21430,13 @@
       <c r="F147" s="354"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="475" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="C149" s="469"/>
+      <c r="D149" s="469"/>
+      <c r="E149" s="469"/>
+      <c r="F149" s="469"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="378" t="s">
@@ -21444,13 +21444,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
+      <c r="B152" s="471" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="C152" s="471"/>
+      <c r="D152" s="471"/>
+      <c r="E152" s="471"/>
+      <c r="F152" s="471"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="421" t="s">
@@ -21487,22 +21487,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="469" t="s">
+      <c r="B161" s="472" t="s">
         <v>390</v>
       </c>
-      <c r="C161" s="469"/>
-      <c r="D161" s="469"/>
-      <c r="E161" s="469"/>
-      <c r="F161" s="469"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="469" t="s">
+      <c r="B162" s="472" t="s">
         <v>391</v>
       </c>
-      <c r="C162" s="469"/>
-      <c r="D162" s="469"/>
-      <c r="E162" s="469"/>
-      <c r="F162" s="469"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="352" t="s">
@@ -21526,12 +21526,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21546,15 +21549,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
